--- a/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
+++ b/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3EAE65A-ACD2-48BA-9AC2-63B6260D2DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F3F5E34-4BB5-4A90-9CBF-E27F3841EE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{779C8823-CA4B-49F6-97D4-A80D91889F77}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{04D9FD9F-5FC0-43B9-B26F-415613FCA9CB}"/>
   </bookViews>
   <sheets>
     <sheet name="Mode d'emploi" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="301">
   <si>
     <t>Dossier d'exploitation quotidien - ERP_CRM_FACTORY</t>
   </si>
@@ -51,16 +51,19 @@
     <t>Ce classeur est fait pour la personne qui manipule le systeme au quotidien - pas pour un architecte ou un developpeur. Chaque commande de ce classeur est PRETE A COPIER-COLLER telle quelle dans un terminal connecte a la machine du serveur (SSH). Aucune connaissance de programmation n'est necessaire pour l'utiliser.</t>
   </si>
   <si>
-    <t>DEUX ENDROITS A CONNAITRE, JAMAIS A CONFONDRE :</t>
-  </si>
-  <si>
-    <t>1) LE POSTE DE PILOTAGE : $HOME/erp_crm_factory - c'est ici que vivent toutes les commandes (dossier bin/) et l'historique des traitements (dossier state/). Avant TOUTE commande de ce classeur, toujours commencer par : cd $HOME/erp_crm_factory</t>
-  </si>
-  <si>
-    <t>2) L'ESPACE CENTRAL D'ECHANGE : /opt/odoo/operations - c'est ici, et seulement ici, qu'atterrissent tous les fichiers produits par les traitements (rapports, alertes, propositions) - exactement comme un espace SM2/ADI dans une architecture bancaire reelle (RCV = recu, SND = produit/a recuperer, ARC = archive, TMP = transit technique, jamais a toucher). Voir la feuille 'Espace central d'echange' pour le detail complet par module.</t>
-  </si>
-  <si>
-    <t>COMMENT LIRE LA FEUILLE 'Jobs et cycles' : chaque ligne est un traitement reel. La colonne 'Ou recuperer le resultat' donne le chemin exact SOUS /opt/odoo/ (a completer avec la date du jour, format annee-mois-jour). Les colonnes 'Commande historique' et 'Commande relancer' sont deja pretes - juste remplacer &lt;JOB_ID&gt; n'est PAS necessaire, l'identifiant est deja ecrit dans la commande.</t>
+    <t>PLUSIEURS REPERES REELS SUR CETTE MACHINE, JAMAIS UN SEUL - chacun designe un endroit different, jamais interchangeable :</t>
+  </si>
+  <si>
+    <t>$HOME/erp_crm_factory : LE POSTE DE PILOTAGE. Vivent ici les commandes (dossier bin/) et l'historique des traitements (dossier state/). C'est le SEUL repere qui existe avant meme d'avoir touche a quoi que ce soit - c'est pour ca qu'on y va en premier chaque jour.</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR : L'ESPACE CENTRAL D'ECHANGE (vaut $ODOO_HOME/operations, defini une seule fois dans vars.conf - jamais une valeur devinee ou recopiee a la main). C'est ici, et seulement ici, qu'atterrissent tous les fichiers produits par les traitements (rapports, alertes, propositions) - exactement comme un espace SM2/ADI dans une architecture bancaire reelle (RCV = recu, SND = produit/a recuperer, ARC = archive, TMP = transit technique, jamais a toucher). Voir la feuille 'Espace central d'echange' pour le detail complet par module.</t>
+  </si>
+  <si>
+    <t>ETAPE 0, OBLIGATOIRE UNE FOIS PAR SESSION DE TERMINAL, AVANT TOUTE AUTRE COMMANDE DE CE CLASSEUR : cd $HOME/erp_crm_factory puis source vars.conf - cette deuxieme commande charge $OPERATIONS_DIR (et les autres reperes internes) dans le terminal, pour que toutes les commandes de ce classeur fonctionnent telles quelles, copiees-collees mot pour mot. Voir la feuille 'Checklist quotidienne', etape 1.</t>
+  </si>
+  <si>
+    <t>COMMENT LIRE LA FEUILLE 'Jobs et cycles' : chaque ligne est un traitement reel. La colonne 'Ou recuperer le resultat' donne le chemin exact (a completer avec la date du jour, format annee-mois-jour). Les colonnes 'Commande historique' et 'Commande relancer' sont deja pretes - l'identifiant du traitement est deja ecrit dedans, rien a remplacer.</t>
   </si>
   <si>
     <t>EN CAS DE DOUTE : la feuille 'Depannage niveau 1' liste les situations les plus frequentes avec la commande exacte a taper. La feuille 'Glossaire Control-M' traduit en langage clair chaque action possible sur un traitement.</t>
@@ -78,13 +81,13 @@
     <t>Commande a taper</t>
   </si>
   <si>
-    <t>1. Se positionner</t>
-  </si>
-  <si>
-    <t>Toujours commencer ici, avant toute autre commande de la journee</t>
-  </si>
-  <si>
-    <t>cd $HOME/erp_crm_factory</t>
+    <t>1. Se positionner et charger les reperes</t>
+  </si>
+  <si>
+    <t>Obligatoire une fois par session de terminal - sans le 'source', $OPERATIONS_DIR n'existe pas encore et les commandes plus bas ne marcheront pas</t>
+  </si>
+  <si>
+    <t>cd $HOME/erp_crm_factory &amp;&amp; source vars.conf</t>
   </si>
   <si>
     <t>2. Verifier le plan du jour</t>
@@ -120,7 +123,7 @@
     <t>Aller consulter les rapports/alertes du jour dans l'espace central (voir feuille Jobs et cycles pour le chemin exact de chacun)</t>
   </si>
   <si>
-    <t>ls -la /opt/odoo/operations/&lt;module&gt;/snd/</t>
+    <t>ls -la $OPERATIONS_DIR/&lt;module&gt;/snd/</t>
   </si>
   <si>
     <t>6. Fin de journee</t>
@@ -150,7 +153,7 @@
     <t>Ce que ca fait</t>
   </si>
   <si>
-    <t>Ou recuperer le resultat (sous /opt/odoo/)</t>
+    <t>Ou recuperer le resultat (via $OPERATIONS_DIR)</t>
   </si>
   <si>
     <t>Commande historique</t>
@@ -174,7 +177,7 @@
     <t>Repere les devis pas encore confirmes depuis plus de 5 jours</t>
   </si>
   <si>
-    <t>operations/vt/snd/relance_devis_AAAAMMJJ.csv</t>
+    <t>$OPERATIONS_DIR/vt/snd/relance_devis_AAAAMMJJ.csv</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFCVTRL</t>
@@ -213,7 +216,7 @@
     <t>Ecrit le nombre de commandes confirmees et le chiffre d'affaires du jour</t>
   </si>
   <si>
-    <t>operations/vt/snd/rapport_eod_AAAAMMJJ.txt</t>
+    <t>$OPERATIONS_DIR/vt/snd/rapport_eod_AAAAMMJJ.txt</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFCVTRP</t>
@@ -237,7 +240,7 @@
     <t>Alerte si un devis envoye au client reste sans reponse depuis plus de 2h</t>
   </si>
   <si>
-    <t>operations/vt/snd/suivi_jour_devis_AAAAMMJJ_HHMM.csv (uniquement s'il y a une alerte)</t>
+    <t>$OPERATIONS_DIR/vt/snd/suivi_jour_devis_AAAAMMJJ_HHMM.csv (uniquement s'il y a une alerte)</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFJVTSV</t>
@@ -261,7 +264,7 @@
     <t>Fait passer la date comptable de reference au jour suivant</t>
   </si>
   <si>
-    <t>state/valeur_comptable_courante.txt (juste la date - pas un rapport)</t>
+    <t>$STATE_DIR/valeur_comptable_courante.txt (juste la date - pas un rapport)</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFCEOD1</t>
@@ -285,7 +288,7 @@
     <t>Apres 15h toute nouvelle commande fournisseur passe automatiquement a la date du lendemain</t>
   </si>
   <si>
-    <t>state/cutoff_achat_date_valeur.txt (juste la date - pas un rapport)</t>
+    <t>$STATE_DIR/cutoff_achat_date_valeur.txt (juste la date - pas un rapport)</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFCCUT1</t>
@@ -303,7 +306,7 @@
     <t>Liste les lignes de releve bancaire pas encore rapprochees depuis plus de 2 jours</t>
   </si>
   <si>
-    <t>operations/cp/snd/reconciliation_bancaire_AAAAMMJJ.csv</t>
+    <t>$OPERATIONS_DIR/cp/snd/reconciliation_bancaire_AAAAMMJJ.csv</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFCCPRB1</t>
@@ -321,7 +324,7 @@
     <t>Liste les factures client en retard de paiement</t>
   </si>
   <si>
-    <t>operations/cp/snd/relance_factures_AAAAMMJJ.csv</t>
+    <t>$OPERATIONS_DIR/cp/snd/relance_factures_AAAAMMJJ.csv</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFCCPFI1</t>
@@ -345,7 +348,7 @@
     <t>Chiffre d'affaires facture - montant encaisse - impayes du mois qui vient de finir</t>
   </si>
   <si>
-    <t>operations/cp/snd/cloture_mensuelle_AAAAMM.txt</t>
+    <t>$OPERATIONS_DIR/cp/snd/cloture_mensuelle_AAAAMM.txt</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFCCPEM1</t>
@@ -369,7 +372,7 @@
     <t>TVA collectee - deductible - nette du trimestre qui vient de finir (calcul de pilotage - a verifier avant transmission officielle)</t>
   </si>
   <si>
-    <t>operations/cp/snd/declaration_tva_AAAAMM.txt</t>
+    <t>$OPERATIONS_DIR/cp/snd/declaration_tva_AAAAMM.txt</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFCCPEQ1</t>
@@ -387,7 +390,7 @@
     <t>Chiffre d'affaires du mois et repartition par commercial - base des commissions</t>
   </si>
   <si>
-    <t>operations/vt/snd/cloture_commerciale_AAAAMM.csv</t>
+    <t>$OPERATIONS_DIR/vt/snd/cloture_commerciale_AAAAMM.csv</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFCVTEM1</t>
@@ -405,7 +408,7 @@
     <t>Liste les pistes commerciales sans nouvelle depuis plus de 7 jours</t>
   </si>
   <si>
-    <t>operations/cr/snd/relance_pistes_AAAAMMJJ.csv</t>
+    <t>$OPERATIONS_DIR/cr/snd/relance_pistes_AAAAMMJJ.csv</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFCCRRL1</t>
@@ -423,7 +426,7 @@
     <t>Liste les produits sous leur seuil minimum de stock</t>
   </si>
   <si>
-    <t>operations/ah/snd/reappro_propose_AAAAMMJJ.csv</t>
+    <t>$OPERATIONS_DIR/ah/snd/reappro_propose_AAAAMMJJ.csv</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFCAHRA1</t>
@@ -447,7 +450,7 @@
     <t>Alerte des qu'un produit tombe a zero de stock</t>
   </si>
   <si>
-    <t>operations/st/snd/alerte_rupture_AAAAMMJJ_HHMM.csv (uniquement s'il y a une rupture)</t>
+    <t>$OPERATIONS_DIR/st/snd/alerte_rupture_AAAAMMJJ_HHMM.csv (uniquement s'il y a une rupture)</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFJSTRU</t>
@@ -462,7 +465,7 @@
     <t>Calcule la valeur totale du stock disponible</t>
   </si>
   <si>
-    <t>operations/st/snd/valorisation_stock_AAAAMMJJ.csv</t>
+    <t>$OPERATIONS_DIR/st/snd/valorisation_stock_AAAAMMJJ.csv</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFCSTIN1</t>
@@ -480,7 +483,7 @@
     <t>Rapport des sessions de caisse fermees dans la journee</t>
   </si>
   <si>
-    <t>operations/ps/snd/cloture_caisse_AAAAMMJJ.csv</t>
+    <t>$OPERATIONS_DIR/ps/snd/cloture_caisse_AAAAMMJJ.csv</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFCPSCX1</t>
@@ -498,7 +501,7 @@
     <t>Liste les contrats (CDD/periode d'essai) qui arrivent a echeance sous 30 jours</t>
   </si>
   <si>
-    <t>operations/rh/snd/alerte_fin_contrat_AAAAMMJJ.csv</t>
+    <t>$OPERATIONS_DIR/rh/snd/alerte_fin_contrat_AAAAMMJJ.csv</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFCRHFC1</t>
@@ -516,7 +519,7 @@
     <t>Total des heures pointees par employe pour le mois qui vient de finir - base de la paie</t>
   </si>
   <si>
-    <t>operations/pn/snd/heures_travaillees_AAAAMM.csv</t>
+    <t>$OPERATIONS_DIR/pn/snd/heures_travaillees_AAAAMM.csv</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFCPNHM1</t>
@@ -534,7 +537,7 @@
     <t>Heures de travail passees par projet pour le mois qui vient de finir - base de la facture client</t>
   </si>
   <si>
-    <t>operations/pj/snd/facturation_temps_passe_AAAAMM.csv</t>
+    <t>$OPERATIONS_DIR/pj/snd/facturation_temps_passe_AAAAMM.csv</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFCPJFA1</t>
@@ -555,7 +558,7 @@
     <t>Deplace les fichiers traites de plus de 90 jours vers l'archive a froid - ne supprime jamais rien</t>
   </si>
   <si>
-    <t>operations_archive_froide/&lt;module&gt;/</t>
+    <t>$ODOO_HOME/operations_archive_froide/&lt;module&gt;/</t>
   </si>
   <si>
     <t>./bin/view_history.sh ECFCPRG1</t>
@@ -564,7 +567,7 @@
     <t>./bin/rerun_job.sh ECFCPRG1 "raison"</t>
   </si>
   <si>
-    <t>Espace central d'echange (/opt/odoo/operations) - meme logique qu'un espace SM2/ADI bancaire (RCV/SND/ARC)</t>
+    <t>Espace central d'echange ($OPERATIONS_DIR) - meme logique qu'un espace SM2/ADI bancaire (RCV/SND/ARC)</t>
   </si>
   <si>
     <t>Chaque module a EXACTEMENT 4 sous-dossiers, toujours les memes noms : rcv (fichiers RECUS, a traiter), snd (fichiers PRODUITS par les traitements - c'est ici qu'on va chercher les rapports), tmp (transit technique - ne jamais y toucher), arc (archive - fichiers deja traites, ranges automatiquement).</t>
@@ -594,13 +597,13 @@
     <t>Ventes</t>
   </si>
   <si>
-    <t>operations/vt/rcv</t>
-  </si>
-  <si>
-    <t>operations/vt/snd</t>
-  </si>
-  <si>
-    <t>operations/vt/arc</t>
+    <t>$OPERATIONS_DIR/vt/rcv</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/vt/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/vt/arc</t>
   </si>
   <si>
     <t>Devis - commandes - factures client</t>
@@ -612,13 +615,13 @@
     <t>Comptabilite</t>
   </si>
   <si>
-    <t>operations/cp/rcv</t>
-  </si>
-  <si>
-    <t>operations/cp/snd</t>
-  </si>
-  <si>
-    <t>operations/cp/arc</t>
+    <t>$OPERATIONS_DIR/cp/rcv</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/arc</t>
   </si>
   <si>
     <t>Reconciliation - factures - clotures - TVA</t>
@@ -630,13 +633,13 @@
     <t>CRM</t>
   </si>
   <si>
-    <t>operations/cr/rcv</t>
-  </si>
-  <si>
-    <t>operations/cr/snd</t>
-  </si>
-  <si>
-    <t>operations/cr/arc</t>
+    <t>$OPERATIONS_DIR/cr/rcv</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cr/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cr/arc</t>
   </si>
   <si>
     <t>Pistes et opportunites commerciales</t>
@@ -648,13 +651,13 @@
     <t>Achat</t>
   </si>
   <si>
-    <t>operations/ah/rcv</t>
-  </si>
-  <si>
-    <t>operations/ah/snd</t>
-  </si>
-  <si>
-    <t>operations/ah/arc</t>
+    <t>$OPERATIONS_DIR/ah/rcv</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/ah/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/ah/arc</t>
   </si>
   <si>
     <t>Commandes fournisseurs - reapprovisionnement</t>
@@ -666,13 +669,13 @@
     <t>Stock</t>
   </si>
   <si>
-    <t>operations/st/rcv</t>
-  </si>
-  <si>
-    <t>operations/st/snd</t>
-  </si>
-  <si>
-    <t>operations/st/arc</t>
+    <t>$OPERATIONS_DIR/st/rcv</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/st/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/st/arc</t>
   </si>
   <si>
     <t>Ruptures - valorisation</t>
@@ -684,13 +687,13 @@
     <t>Point de vente</t>
   </si>
   <si>
-    <t>operations/ps/rcv</t>
-  </si>
-  <si>
-    <t>operations/ps/snd</t>
-  </si>
-  <si>
-    <t>operations/ps/arc</t>
+    <t>$OPERATIONS_DIR/ps/rcv</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/ps/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/ps/arc</t>
   </si>
   <si>
     <t>Sessions de caisse</t>
@@ -702,13 +705,13 @@
     <t>RH</t>
   </si>
   <si>
-    <t>operations/rh/rcv</t>
-  </si>
-  <si>
-    <t>operations/rh/snd</t>
-  </si>
-  <si>
-    <t>operations/rh/arc</t>
+    <t>$OPERATIONS_DIR/rh/rcv</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/rh/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/rh/arc</t>
   </si>
   <si>
     <t>Contrats employes</t>
@@ -720,13 +723,13 @@
     <t>Presences</t>
   </si>
   <si>
-    <t>operations/pn/rcv</t>
-  </si>
-  <si>
-    <t>operations/pn/snd</t>
-  </si>
-  <si>
-    <t>operations/pn/arc</t>
+    <t>$OPERATIONS_DIR/pn/rcv</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/pn/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/pn/arc</t>
   </si>
   <si>
     <t>Pointages et heures travaillees</t>
@@ -738,13 +741,13 @@
     <t>Projets</t>
   </si>
   <si>
-    <t>operations/pj/rcv</t>
-  </si>
-  <si>
-    <t>operations/pj/snd</t>
-  </si>
-  <si>
-    <t>operations/pj/arc</t>
+    <t>$OPERATIONS_DIR/pj/rcv</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/pj/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/pj/arc</t>
   </si>
   <si>
     <t>Temps passe et facturation</t>
@@ -759,7 +762,7 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>operations_archive_froide/&lt;module&gt;</t>
+    <t>$ODOO_HOME/operations_archive_froide/&lt;module&gt;</t>
   </si>
   <si>
     <t>Destination finale apres 90 jours - tous les modules confondus</t>
@@ -1390,8 +1393,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5CB238-E544-4A15-9EF4-BC482BFE7EBC}">
-  <dimension ref="A1:F23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6A1330-6F9A-41DA-A42B-019B81A54DA6}">
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="100.77734375" customWidth="1"/>
@@ -1595,13 +1598,49 @@
       <c r="E23" s="3"/>
       <c r="F23" s="3"/>
     </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+    </row>
+    <row r="27" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A19:F19"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A25:F25"/>
     <mergeCell ref="A3:F3"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="A7:F7"/>
@@ -1615,7 +1654,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43C22106-D786-4C66-86CE-FCE371633958}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61FEC84C-A67F-4836-B5EF-B3BDD96FD60E}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1625,7 +1664,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -1637,79 +1676,79 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1721,7 +1760,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B774026E-B786-4D49-9067-EFA2F4EFA0BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA97462B-542B-4DE3-ABA6-CD19B35B8D24}">
   <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1737,7 +1776,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -1759,552 +1798,552 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D3" s="12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G3" s="12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F4" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H4" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F5" s="14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H5" s="14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F6" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="H6" s="14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F7" s="14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H7" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F8" s="14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F9" s="14" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H9" s="14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F10" s="14" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H10" s="14" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F11" s="14" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H11" s="14" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F12" s="14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H12" s="14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G13" s="14" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H13" s="14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F14" s="14" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G14" s="14" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H14" s="14" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G15" s="14" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H15" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F16" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G16" s="14" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G17" s="14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F18" s="14" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G18" s="14" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H18" s="14" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F19" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G19" s="14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H19" s="14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G20" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H20" s="14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F21" s="14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G21" s="14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H21" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G22" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H22" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F23" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G23" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H3" xr:uid="{B774026E-B786-4D49-9067-EFA2F4EFA0BE}"/>
+  <autoFilter ref="A3:H3" xr:uid="{EA97462B-542B-4DE3-ABA6-CD19B35B8D24}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
@@ -2313,7 +2352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52B144B2-099C-4F42-B6B6-A3B7C7500CD5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04E0E3CA-1914-4350-8240-440F3253541A}">
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2326,7 +2365,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -2336,7 +2375,7 @@
     </row>
     <row r="2" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -2354,226 +2393,226 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="E6" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E7" s="17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E8" s="17" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C9" s="17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D9" s="17" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E9" s="17" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C12" s="17" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C13" s="17" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C14" s="17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F4" xr:uid="{52B144B2-099C-4F42-B6B6-A3B7C7500CD5}"/>
+  <autoFilter ref="A4:F4" xr:uid="{04E0E3CA-1914-4350-8240-440F3253541A}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -2583,7 +2622,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67619A0C-D0FE-48A4-B92C-0CA4E0660CC2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59B566F-700D-4E60-B5B6-E06833E4C6EF}">
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2594,7 +2633,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -2606,134 +2645,134 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="11" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C14" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2745,7 +2784,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E5E4659-2F0F-4BDA-B582-270953BBB310}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0022BAD-B9AD-4D66-8448-665F7D427E46}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2755,7 +2794,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -2767,106 +2806,106 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="12" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C4" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C5" s="14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C6" s="14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>

--- a/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
+++ b/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8F3F5E34-4BB5-4A90-9CBF-E27F3841EE8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{33E0E5D2-0B51-4400-BD29-BE8408BF3613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{04D9FD9F-5FC0-43B9-B26F-415613FCA9CB}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{6479905D-314D-4816-92D7-ABB5F41C2D2D}"/>
   </bookViews>
   <sheets>
     <sheet name="Mode d'emploi" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Espace central d''echange'!$A$4:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Jobs et cycles'!$A$3:$H$3</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Checklist quotidienne'!$A$1:$C$9</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Depannage niveau 1'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Espace central d''echange'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Glossaire Control-M'!$A$1:$C$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Jobs et cycles'!$A$1:$H$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Mode d''emploi'!$A$1:$D$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -952,7 +958,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -961,61 +967,117 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFEBEBF5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFEBEBF5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFEBEBF5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF140A14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFBE82F0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFEBEBF5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFEBEBF5"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF140A14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFBE82F0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF64D296"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="13"/>
-      <color theme="1"/>
+      <color rgb="FFEBEBF5"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
-      <color theme="1"/>
+      <sz val="13"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFA5AABE"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1024,13 +1086,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFD6EC"/>
+        <fgColor rgb="FF1E0F32"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FF0F111A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF4FA3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF161925"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D2130"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1047,39 +1127,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1393,268 +1480,237 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A6A1330-6F9A-41DA-A42B-019B81A54DA6}">
-  <dimension ref="A1:F27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27A4A5D2-FE70-4CC2-83E0-612266143BE1}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="100.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-    </row>
-    <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-    </row>
-    <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-    </row>
-    <row r="15" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-    </row>
-    <row r="17" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-    </row>
-    <row r="19" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:4" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="1:4" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-    </row>
-    <row r="21" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A20" s="1"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+    </row>
+    <row r="21" spans="1:4" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="1:4" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-    </row>
-    <row r="25" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="3" t="s">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="1:4" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="1:4" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A28" s="1"/>
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A29" s="1"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A27:F27"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A25:F25"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="A11:F11"/>
-    <mergeCell ref="A13:F13"/>
+  <mergeCells count="14">
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A11:D11"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.3888888888888889" bottom="0.3888888888888889" header="0.16666666666666666" footer="0.16666666666666666"/>
+  <pageSetup paperSize="9" scale="72" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;LERP_CRM_FACTORY - Dossier d'exploitation quotidien&amp;RPage &amp;P / &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61FEC84C-A67F-4836-B5EF-B3BDD96FD60E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC73D44-817E-4F07-A00A-40AB6EB488E9}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1662,31 +1718,31 @@
     <col min="2" max="3" width="55.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
+      <c r="A1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="9" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="8" t="s">
@@ -1697,18 +1753,18 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="10" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="9" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -1719,18 +1775,18 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="10" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="9" t="s">
         <v>24</v>
       </c>
       <c r="B8" s="8" t="s">
@@ -1741,13 +1797,13 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="8" t="s">
+      <c r="B9" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="10" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1755,12 +1811,20 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.3888888888888889" bottom="0.3888888888888889" header="0.16666666666666666" footer="0.16666666666666666"/>
+  <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;LERP_CRM_FACTORY - Dossier d'exploitation quotidien&amp;RPage &amp;P / &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA97462B-542B-4DE3-ABA6-CD19B35B8D24}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED338C3A-DA4C-4D5F-A899-E433FCAE3C09}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1775,584 +1839,592 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="10"/>
-      <c r="H1" s="10"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="11"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="12" t="s">
+      <c r="D3" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="F3" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="15" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="14" t="s">
+      <c r="G4" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="14" t="s">
+      <c r="H4" s="17" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="E5" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="14" t="s">
+      <c r="H5" s="21" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="17" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="F6" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="17" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="H7" s="14" t="s">
+      <c r="H7" s="21" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="13" t="s">
+      <c r="E8" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="17" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="22" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="H9" s="14" t="s">
+      <c r="H9" s="21" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="16" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="17" t="s">
         <v>86</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="17" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="22" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="20" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="13" t="s">
+      <c r="E11" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="16" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="13" t="s">
+      <c r="E12" s="17" t="s">
         <v>100</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="17" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="22" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="20" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="23" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="E13" s="13" t="s">
+      <c r="E13" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="F13" s="14" t="s">
+      <c r="F13" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="21" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="16" t="s">
         <v>113</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="E14" s="13" t="s">
+      <c r="E14" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="F14" s="14" t="s">
+      <c r="F14" s="17" t="s">
         <v>115</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="17" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="13" t="s">
+      <c r="E15" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="F15" s="14" t="s">
+      <c r="F15" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="21" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="13" t="s">
+      <c r="E16" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="F16" s="14" t="s">
+      <c r="F16" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="17" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="11" t="s">
+      <c r="A17" s="22" t="s">
         <v>130</v>
       </c>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="E17" s="13" t="s">
+      <c r="E17" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="F17" s="14" t="s">
+      <c r="F17" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="21" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="13" t="s">
+      <c r="E18" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="F18" s="14" t="s">
+      <c r="F18" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="H18" s="14" t="s">
+      <c r="H18" s="17" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="20" t="s">
         <v>144</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="13" t="s">
+      <c r="E19" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="F19" s="14" t="s">
+      <c r="F19" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="H19" s="14" t="s">
+      <c r="H19" s="21" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="16" t="s">
         <v>150</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="13" t="s">
+      <c r="E20" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="17" t="s">
         <v>152</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="H20" s="14" t="s">
+      <c r="H20" s="17" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="B21" s="11" t="s">
+      <c r="B21" s="20" t="s">
         <v>156</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C21" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="E21" s="13" t="s">
+      <c r="E21" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="H21" s="14" t="s">
+      <c r="H21" s="21" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C22" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="16" t="s">
         <v>99</v>
       </c>
-      <c r="E22" s="13" t="s">
+      <c r="E22" s="17" t="s">
         <v>163</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="17" t="s">
         <v>164</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="H22" s="14" t="s">
+      <c r="H22" s="17" t="s">
         <v>166</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="22" t="s">
         <v>167</v>
       </c>
-      <c r="B23" s="11" t="s">
+      <c r="B23" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C23" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="20" t="s">
         <v>99</v>
       </c>
-      <c r="E23" s="13" t="s">
+      <c r="E23" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="H23" s="14" t="s">
+      <c r="H23" s="21" t="s">
         <v>173</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H3" xr:uid="{EA97462B-542B-4DE3-ABA6-CD19B35B8D24}"/>
+  <autoFilter ref="A3:H3" xr:uid="{ED338C3A-DA4C-4D5F-A899-E433FCAE3C09}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.3888888888888889" bottom="0.3888888888888889" header="0.16666666666666666" footer="0.16666666666666666"/>
+  <pageSetup paperSize="9" scale="57" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;LERP_CRM_FACTORY - Dossier d'exploitation quotidien&amp;RPage &amp;P / &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04E0E3CA-1914-4350-8240-440F3253541A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0B4B3E5-058D-4079-92A2-FA61E53B4DD5}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2364,265 +2436,273 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
     </row>
     <row r="2" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="15" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="16" t="s">
         <v>184</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="16" t="s">
         <v>185</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="16" t="s">
         <v>186</v>
       </c>
-      <c r="F5" s="11" t="s">
+      <c r="F5" s="16" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="22" t="s">
         <v>188</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="20" t="s">
         <v>190</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="D6" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="20" t="s">
         <v>192</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="20" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="16" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C7" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="D7" s="16" t="s">
         <v>197</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="16" t="s">
         <v>198</v>
       </c>
-      <c r="F7" s="11" t="s">
+      <c r="F7" s="16" t="s">
         <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="22" t="s">
         <v>200</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="20" t="s">
         <v>201</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="20" t="s">
         <v>202</v>
       </c>
-      <c r="D8" s="17" t="s">
+      <c r="D8" s="20" t="s">
         <v>203</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="20" t="s">
         <v>204</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="20" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="16" t="s">
         <v>207</v>
       </c>
-      <c r="C9" s="17" t="s">
+      <c r="C9" s="16" t="s">
         <v>208</v>
       </c>
-      <c r="D9" s="17" t="s">
+      <c r="D9" s="16" t="s">
         <v>209</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="16" t="s">
         <v>210</v>
       </c>
-      <c r="F9" s="11" t="s">
+      <c r="F9" s="16" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="22" t="s">
         <v>212</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="20" t="s">
         <v>213</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="20" t="s">
         <v>214</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="20" t="s">
         <v>216</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="20" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="E11" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="F11" s="11" t="s">
+      <c r="F11" s="16" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="22" t="s">
         <v>224</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="20" t="s">
         <v>225</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="C12" s="20" t="s">
         <v>226</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="20" t="s">
         <v>227</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="20" t="s">
         <v>228</v>
       </c>
-      <c r="F12" s="11" t="s">
+      <c r="F12" s="20" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="18" t="s">
         <v>230</v>
       </c>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="16" t="s">
         <v>231</v>
       </c>
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="16" t="s">
         <v>232</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="16" t="s">
         <v>233</v>
       </c>
-      <c r="E13" s="17" t="s">
+      <c r="E13" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="16" t="s">
         <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="22" t="s">
         <v>236</v>
       </c>
-      <c r="B14" s="11" t="s">
+      <c r="B14" s="20" t="s">
         <v>237</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="20" t="s">
         <v>238</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="E14" s="20" t="s">
         <v>239</v>
       </c>
-      <c r="F14" s="11" t="s">
+      <c r="F14" s="20" t="s">
         <v>240</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F4" xr:uid="{04E0E3CA-1914-4350-8240-440F3253541A}"/>
+  <autoFilter ref="A4:F4" xr:uid="{E0B4B3E5-058D-4079-92A2-FA61E53B4DD5}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.3888888888888889" bottom="0.3888888888888889" header="0.16666666666666666" footer="0.16666666666666666"/>
+  <pageSetup paperSize="9" scale="84" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;LERP_CRM_FACTORY - Dossier d'exploitation quotidien&amp;RPage &amp;P / &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59B566F-700D-4E60-B5B6-E06833E4C6EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D8A0890-527E-4B14-84E0-376AFCECB64D}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2632,146 +2712,146 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="25" t="s">
         <v>241</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="15" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="18" t="s">
         <v>245</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="17" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="22" t="s">
         <v>248</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="21" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="17" t="s">
         <v>252</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="17" t="s">
         <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="22" t="s">
         <v>254</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="21" t="s">
         <v>255</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="21" t="s">
         <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="18" t="s">
         <v>257</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="17" t="s">
         <v>258</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="17" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="22" t="s">
         <v>260</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="21" t="s">
         <v>261</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="21" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="18" t="s">
         <v>263</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="17" t="s">
         <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="22" t="s">
         <v>266</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="21" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="18" t="s">
         <v>269</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="17" t="s">
         <v>270</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="17" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="22" t="s">
         <v>272</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="21" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="18" t="s">
         <v>274</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="17" t="s">
         <v>275</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="17" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2779,12 +2859,20 @@
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.3888888888888889" bottom="0.3888888888888889" header="0.16666666666666666" footer="0.16666666666666666"/>
+  <pageSetup paperSize="9" scale="84" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;LERP_CRM_FACTORY - Dossier d'exploitation quotidien&amp;RPage &amp;P / &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0022BAD-B9AD-4D66-8448-665F7D427E46}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B070CCDC-2A03-4175-A6EE-99E734F702E1}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2793,128 +2881,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="25" t="s">
         <v>276</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="15" t="s">
         <v>277</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="15" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="17" t="s">
         <v>281</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="17" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="21" t="s">
         <v>283</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="21" t="s">
         <v>284</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="21" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="17" t="s">
         <v>285</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="17" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="21" t="s">
         <v>287</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="21" t="s">
         <v>288</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="C7" s="21" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="17" t="s">
         <v>289</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="17" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="21" t="s">
         <v>292</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="21" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="17" t="s">
         <v>294</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="17" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="21" t="s">
         <v>298</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="21" t="s">
         <v>299</v>
       </c>
     </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="1"/>
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+    </row>
     <row r="13" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="26" t="s">
         <v>300</v>
       </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A13:C13"/>
   </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.3888888888888889" bottom="0.3888888888888889" header="0.16666666666666666" footer="0.16666666666666666"/>
+  <pageSetup paperSize="9" scale="74" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;LERP_CRM_FACTORY - Dossier d'exploitation quotidien&amp;RPage &amp;P / &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
--- a/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
+++ b/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{33E0E5D2-0B51-4400-BD29-BE8408BF3613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13D53E85-6EF1-48F8-9471-880723650060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{6479905D-314D-4816-92D7-ABB5F41C2D2D}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{60B9C012-0860-4352-9EE5-2F90FE5111DB}"/>
   </bookViews>
   <sheets>
     <sheet name="Mode d'emploi" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Depannage niveau 1'!$A$1:$C$13</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Espace central d''echange'!$A$1:$F$14</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Glossaire Control-M'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Jobs et cycles'!$A$1:$H$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Jobs et cycles'!$A$1:$H$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Mode d''emploi'!$A$1:$D$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="302">
   <si>
     <t>Dossier d'exploitation quotidien - ERP_CRM_FACTORY</t>
   </si>
@@ -69,7 +69,7 @@
     <t>ETAPE 0, OBLIGATOIRE UNE FOIS PAR SESSION DE TERMINAL, AVANT TOUTE AUTRE COMMANDE DE CE CLASSEUR : cd $HOME/erp_crm_factory puis source vars.conf - cette deuxieme commande charge $OPERATIONS_DIR (et les autres reperes internes) dans le terminal, pour que toutes les commandes de ce classeur fonctionnent telles quelles, copiees-collees mot pour mot. Voir la feuille 'Checklist quotidienne', etape 1.</t>
   </si>
   <si>
-    <t>COMMENT LIRE LA FEUILLE 'Jobs et cycles' : chaque ligne est un traitement reel. La colonne 'Ou recuperer le resultat' donne le chemin exact (a completer avec la date du jour, format annee-mois-jour). Les colonnes 'Commande historique' et 'Commande relancer' sont deja pretes - l'identifiant du traitement est deja ecrit dedans, rien a remplacer.</t>
+    <t>COMMENT LIRE LA FEUILLE 'Jobs et cycles' : les traitements sont regroupes par famille (Ventes, Comptabilite, Achat...) - un petit '-' dans la marge de gauche permet de REPLIER une famille (ne montrer que son nom) ou de la DEPLIER (voir chacun de ses traitements). Chaque ligne de detail est un traitement reel. La colonne 'Ou recuperer le resultat' donne le chemin exact (a completer avec la date du jour, format annee-mois-jour). Les colonnes 'Commande historique' et 'Commande relancer' sont deja pretes - l'identifiant du traitement est deja ecrit dedans, rien a remplacer.</t>
   </si>
   <si>
     <t>EN CAS DE DOUTE : la feuille 'Depannage niveau 1' liste les situations les plus frequentes avec la commande exacte a taper. La feuille 'Glossaire Control-M' traduit en langage clair chaque action possible sur un traitement.</t>
@@ -141,7 +141,7 @@
     <t>(aucune commande - verification passive uniquement)</t>
   </si>
   <si>
-    <t>Tous les traitements reels d'exploitation - avec leurs commandes pretes a coller</t>
+    <t>Tous les traitements reels d'exploitation - groupes par famille (cliquez sur le -/+ dans la marge pour deroule/enrouler)</t>
   </si>
   <si>
     <t>JOB_ID</t>
@@ -168,6 +168,9 @@
     <t>Commande relancer</t>
   </si>
   <si>
+    <t>Ventes</t>
+  </si>
+  <si>
     <t>ECFCVTRL</t>
   </si>
   <si>
@@ -255,6 +258,33 @@
     <t>Rien a faire - se relance seul toutes les 15 min</t>
   </si>
   <si>
+    <t>ECFCVTEM1</t>
+  </si>
+  <si>
+    <t>Cloture commerciale mensuelle (Ventes)</t>
+  </si>
+  <si>
+    <t>EOM</t>
+  </si>
+  <si>
+    <t>Le 1er de chaque mois</t>
+  </si>
+  <si>
+    <t>Chiffre d'affaires du mois et repartition par commercial - base des commissions</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/vt/snd/cloture_commerciale_AAAAMM.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCVTEM1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCVTEM1 "raison"</t>
+  </si>
+  <si>
+    <t>Comptabilite</t>
+  </si>
+  <si>
     <t>ECFCEOD1</t>
   </si>
   <si>
@@ -279,6 +309,87 @@
     <t>./bin/rerun_job.sh ECFCEOD1 "raison"</t>
   </si>
   <si>
+    <t>ECFCCPRB1</t>
+  </si>
+  <si>
+    <t>Reconciliation bancaire (Comptabilite)</t>
+  </si>
+  <si>
+    <t>Liste les lignes de releve bancaire pas encore rapprochees depuis plus de 2 jours</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/snd/reconciliation_bancaire_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCPRB1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCPRB1 "raison"</t>
+  </si>
+  <si>
+    <t>ECFCCPFI1</t>
+  </si>
+  <si>
+    <t>Relance factures impayees (Comptabilite)</t>
+  </si>
+  <si>
+    <t>Liste les factures client en retard de paiement</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/snd/relance_factures_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCPFI1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCPFI1 "raison"</t>
+  </si>
+  <si>
+    <t>ECFCCPEM1</t>
+  </si>
+  <si>
+    <t>Cloture comptable mensuelle (Comptabilite)</t>
+  </si>
+  <si>
+    <t>Chiffre d'affaires facture - montant encaisse - impayes du mois qui vient de finir</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/snd/cloture_mensuelle_AAAAMM.txt</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCPEM1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCPEM1 "raison"</t>
+  </si>
+  <si>
+    <t>ECFCCPEQ1</t>
+  </si>
+  <si>
+    <t>Declaration TVA trimestrielle (Comptabilite)</t>
+  </si>
+  <si>
+    <t>EOQ</t>
+  </si>
+  <si>
+    <t>Le 1er jour d'un nouveau trimestre</t>
+  </si>
+  <si>
+    <t>TVA collectee - deductible - nette du trimestre qui vient de finir (calcul de pilotage - a verifier avant transmission officielle)</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/snd/declaration_tva_AAAAMM.txt</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCPEQ1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCPEQ1 "raison"</t>
+  </si>
+  <si>
+    <t>Achat</t>
+  </si>
+  <si>
     <t>ECFCCUT1</t>
   </si>
   <si>
@@ -303,106 +414,25 @@
     <t>./bin/rerun_job.sh ECFCCUT1 "raison"</t>
   </si>
   <si>
-    <t>ECFCCPRB1</t>
-  </si>
-  <si>
-    <t>Reconciliation bancaire (Comptabilite)</t>
-  </si>
-  <si>
-    <t>Liste les lignes de releve bancaire pas encore rapprochees depuis plus de 2 jours</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cp/snd/reconciliation_bancaire_AAAAMMJJ.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCCPRB1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCPRB1 "raison"</t>
-  </si>
-  <si>
-    <t>ECFCCPFI1</t>
-  </si>
-  <si>
-    <t>Relance factures impayees (Comptabilite)</t>
-  </si>
-  <si>
-    <t>Liste les factures client en retard de paiement</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cp/snd/relance_factures_AAAAMMJJ.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCCPFI1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCPFI1 "raison"</t>
-  </si>
-  <si>
-    <t>ECFCCPEM1</t>
-  </si>
-  <si>
-    <t>Cloture comptable mensuelle (Comptabilite)</t>
-  </si>
-  <si>
-    <t>EOM</t>
-  </si>
-  <si>
-    <t>Le 1er de chaque mois</t>
-  </si>
-  <si>
-    <t>Chiffre d'affaires facture - montant encaisse - impayes du mois qui vient de finir</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cp/snd/cloture_mensuelle_AAAAMM.txt</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCCPEM1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCPEM1 "raison"</t>
-  </si>
-  <si>
-    <t>ECFCCPEQ1</t>
-  </si>
-  <si>
-    <t>Declaration TVA trimestrielle (Comptabilite)</t>
-  </si>
-  <si>
-    <t>EOQ</t>
-  </si>
-  <si>
-    <t>Le 1er jour d'un nouveau trimestre</t>
-  </si>
-  <si>
-    <t>TVA collectee - deductible - nette du trimestre qui vient de finir (calcul de pilotage - a verifier avant transmission officielle)</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cp/snd/declaration_tva_AAAAMM.txt</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCCPEQ1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCPEQ1 "raison"</t>
-  </si>
-  <si>
-    <t>ECFCVTEM1</t>
-  </si>
-  <si>
-    <t>Cloture commerciale mensuelle (Ventes)</t>
-  </si>
-  <si>
-    <t>Chiffre d'affaires du mois et repartition par commercial - base des commissions</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/vt/snd/cloture_commerciale_AAAAMM.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCVTEM1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCVTEM1 "raison"</t>
+    <t>ECFCAHRA1</t>
+  </si>
+  <si>
+    <t>Propositions de reapprovisionnement (Achat)</t>
+  </si>
+  <si>
+    <t>Liste les produits sous leur seuil minimum de stock</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/ah/snd/reappro_propose_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCAHRA1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCAHRA1 "raison"</t>
+  </si>
+  <si>
+    <t>CRM</t>
   </si>
   <si>
     <t>ECFCCRRL1</t>
@@ -423,22 +453,7 @@
     <t>./bin/rerun_job.sh ECFCCRRL1 "raison"</t>
   </si>
   <si>
-    <t>ECFCAHRA1</t>
-  </si>
-  <si>
-    <t>Propositions de reapprovisionnement (Achat)</t>
-  </si>
-  <si>
-    <t>Liste les produits sous leur seuil minimum de stock</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/ah/snd/reappro_propose_AAAAMMJJ.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCAHRA1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCAHRA1 "raison"</t>
+    <t>Stock</t>
   </si>
   <si>
     <t>ECFJSTRU</t>
@@ -480,6 +495,9 @@
     <t>./bin/rerun_job.sh ECFCSTIN1 "raison"</t>
   </si>
   <si>
+    <t>Point de vente</t>
+  </si>
+  <si>
     <t>ECFCPSCX1</t>
   </si>
   <si>
@@ -498,6 +516,9 @@
     <t>./bin/rerun_job.sh ECFCPSCX1 "raison"</t>
   </si>
   <si>
+    <t>RH</t>
+  </si>
+  <si>
     <t>ECFCRHFC1</t>
   </si>
   <si>
@@ -516,6 +537,9 @@
     <t>./bin/rerun_job.sh ECFCRHFC1 "raison"</t>
   </si>
   <si>
+    <t>Presences</t>
+  </si>
+  <si>
     <t>ECFCPNHM1</t>
   </si>
   <si>
@@ -534,6 +558,9 @@
     <t>./bin/rerun_job.sh ECFCPNHM1 "raison"</t>
   </si>
   <si>
+    <t>Projets</t>
+  </si>
+  <si>
     <t>ECFCPJFA1</t>
   </si>
   <si>
@@ -552,6 +579,9 @@
     <t>./bin/rerun_job.sh ECFCPJFA1 "raison"</t>
   </si>
   <si>
+    <t>Systeme</t>
+  </si>
+  <si>
     <t>ECFCPRG1</t>
   </si>
   <si>
@@ -600,9 +630,6 @@
     <t>vt</t>
   </si>
   <si>
-    <t>Ventes</t>
-  </si>
-  <si>
     <t>$OPERATIONS_DIR/vt/rcv</t>
   </si>
   <si>
@@ -618,9 +645,6 @@
     <t>cp</t>
   </si>
   <si>
-    <t>Comptabilite</t>
-  </si>
-  <si>
     <t>$OPERATIONS_DIR/cp/rcv</t>
   </si>
   <si>
@@ -636,9 +660,6 @@
     <t>cr</t>
   </si>
   <si>
-    <t>CRM</t>
-  </si>
-  <si>
     <t>$OPERATIONS_DIR/cr/rcv</t>
   </si>
   <si>
@@ -654,9 +675,6 @@
     <t>ah</t>
   </si>
   <si>
-    <t>Achat</t>
-  </si>
-  <si>
     <t>$OPERATIONS_DIR/ah/rcv</t>
   </si>
   <si>
@@ -672,9 +690,6 @@
     <t>st</t>
   </si>
   <si>
-    <t>Stock</t>
-  </si>
-  <si>
     <t>$OPERATIONS_DIR/st/rcv</t>
   </si>
   <si>
@@ -690,9 +705,6 @@
     <t>ps</t>
   </si>
   <si>
-    <t>Point de vente</t>
-  </si>
-  <si>
     <t>$OPERATIONS_DIR/ps/rcv</t>
   </si>
   <si>
@@ -708,9 +720,6 @@
     <t>rh</t>
   </si>
   <si>
-    <t>RH</t>
-  </si>
-  <si>
     <t>$OPERATIONS_DIR/rh/rcv</t>
   </si>
   <si>
@@ -726,9 +735,6 @@
     <t>pn</t>
   </si>
   <si>
-    <t>Presences</t>
-  </si>
-  <si>
     <t>$OPERATIONS_DIR/pn/rcv</t>
   </si>
   <si>
@@ -742,9 +748,6 @@
   </si>
   <si>
     <t>pj</t>
-  </si>
-  <si>
-    <t>Projets</t>
   </si>
   <si>
     <t>$OPERATIONS_DIR/pj/rcv</t>
@@ -958,7 +961,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1043,8 +1046,15 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
-      <color rgb="FFBE82F0"/>
+      <color rgb="FF64DCFF"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1076,8 +1086,15 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFBE82F0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1114,6 +1131,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE82F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1127,7 +1150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1150,23 +1173,30 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1480,7 +1510,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27A4A5D2-FE70-4CC2-83E0-612266143BE1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF59E5C8-F50C-4DAD-A618-C3ED0F9CF201}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1707,7 +1737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC73D44-817E-4F07-A00A-40AB6EB488E9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71019500-FA56-4C8D-82AE-A66BBA5159F9}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1821,12 +1851,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED338C3A-DA4C-4D5F-A899-E433FCAE3C09}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F28086-F537-4126-8D05-E3F23A7736C9}">
   <sheetPr>
+    <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
     <col min="2" max="2" width="32.77734375" customWidth="1"/>
@@ -1890,526 +1921,656 @@
       <c r="A4" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+    </row>
+    <row r="5" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="B5" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="C5" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="D5" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="E5" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="F5" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="G5" s="20" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+      <c r="H5" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="B5" s="20" t="s">
+    </row>
+    <row r="6" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="C5" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="20" t="s">
+      <c r="B6" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="F5" s="21" t="s">
+      <c r="D6" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="24" t="s">
         <v>50</v>
       </c>
-      <c r="G5" s="21" t="s">
+      <c r="F6" s="24" t="s">
         <v>51</v>
       </c>
-      <c r="H5" s="21" t="s">
+      <c r="G6" s="24" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="H6" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="16" t="s">
+    </row>
+    <row r="7" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="16" t="s">
+      <c r="B7" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="C7" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="E7" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="G6" s="17" t="s">
+      <c r="F7" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="G7" s="20" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+      <c r="H7" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="20" t="s">
+    </row>
+    <row r="8" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="B8" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="C8" s="26" t="s">
         <v>63</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="D8" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="E8" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="G7" s="21" t="s">
+      <c r="F8" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="H7" s="21" t="s">
+      <c r="G8" s="24" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
+      <c r="H8" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B8" s="16" t="s">
+    </row>
+    <row r="9" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="B9" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="C9" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="D9" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="F8" s="17" t="s">
+      <c r="E9" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="17" t="s">
+      <c r="F9" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="G9" s="20" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
+      <c r="H9" s="20" t="s">
         <v>76</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="17"/>
+      <c r="G10" s="17"/>
+      <c r="H10" s="17"/>
+    </row>
+    <row r="11" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="H11" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="16" t="s">
+    </row>
+    <row r="12" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="E10" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="F10" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="G10" s="17" t="s">
+      <c r="D12" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E12" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="F12" s="24" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
+      <c r="G12" s="24" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="H12" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="C11" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="E11" s="21" t="s">
+    </row>
+    <row r="13" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="B13" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="G11" s="21" t="s">
+      <c r="C13" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="20" t="s">
         <v>94</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="F13" s="20" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
+      <c r="G13" s="20" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="H13" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="19" t="s">
+    </row>
+    <row r="14" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="B14" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="17" t="s">
+      <c r="C14" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="F12" s="17" t="s">
+      <c r="F14" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="G12" s="17" t="s">
+      <c r="G14" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="H14" s="24" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
+    <row r="15" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B15" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C15" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D15" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E15" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F15" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="G13" s="21" t="s">
+      <c r="G15" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H15" s="20" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="B14" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="G14" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="B15" s="20" t="s">
-        <v>119</v>
-      </c>
-      <c r="C15" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="H15" s="21" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16" s="16"/>
+      <c r="C16" s="16"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="17"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="17"/>
+    </row>
+    <row r="17" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>119</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E18" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="F18" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="G18" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="C16" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D16" s="16" t="s">
+      <c r="H18" s="24" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
+    </row>
+    <row r="20" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C20" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="G16" s="17" t="s">
-        <v>128</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="22" t="s">
+      <c r="D20" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="B17" s="20" t="s">
+      <c r="F20" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="G20" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="H20" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="E17" s="21" t="s">
+    </row>
+    <row r="21" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="17"/>
+      <c r="F21" s="17"/>
+      <c r="G21" s="17"/>
+      <c r="H21" s="17"/>
+    </row>
+    <row r="22" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="G17" s="21" t="s">
+      <c r="B22" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="H17" s="21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="18" t="s">
+      <c r="C22" s="22" t="s">
         <v>137</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="D22" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="C18" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" s="16" t="s">
+      <c r="E22" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>140</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="B23" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23" s="26" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="G18" s="17" t="s">
-        <v>141</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="B19" s="20" t="s">
+      <c r="D23" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E23" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="C19" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="D19" s="20" t="s">
+      <c r="F23" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="G23" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+    </row>
+    <row r="25" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="C25" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E19" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="H19" s="21" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="18" t="s">
-        <v>149</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="16" t="s">
+      <c r="D25" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+    </row>
+    <row r="27" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="C27" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="E20" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="B21" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="C21" s="23" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="E21" s="21" t="s">
-        <v>157</v>
-      </c>
-      <c r="F21" s="21" t="s">
+      <c r="D27" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="E27" s="20" t="s">
         <v>158</v>
       </c>
-      <c r="G21" s="21" t="s">
+      <c r="F27" s="20" t="s">
         <v>159</v>
       </c>
-      <c r="H21" s="21" t="s">
+      <c r="G27" s="20" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
+      <c r="H27" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="B22" s="16" t="s">
+    </row>
+    <row r="28" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C22" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="E22" s="17" t="s">
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+    </row>
+    <row r="29" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="F22" s="17" t="s">
+      <c r="B29" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="G22" s="17" t="s">
+      <c r="C29" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="H22" s="17" t="s">
+      <c r="F29" s="20" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="22" t="s">
+      <c r="G29" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="H29" s="20" t="s">
         <v>168</v>
       </c>
-      <c r="C23" s="23" t="s">
+    </row>
+    <row r="30" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="D23" s="20" t="s">
-        <v>99</v>
-      </c>
-      <c r="E23" s="21" t="s">
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+    </row>
+    <row r="31" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="F23" s="21" t="s">
+      <c r="B31" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="G23" s="21" t="s">
+      <c r="C31" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E31" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="H23" s="21" t="s">
+      <c r="F31" s="20" t="s">
         <v>173</v>
       </c>
+      <c r="G31" s="20" t="s">
+        <v>174</v>
+      </c>
+      <c r="H31" s="20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+    </row>
+    <row r="33" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="B33" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>179</v>
+      </c>
+      <c r="D33" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>180</v>
+      </c>
+      <c r="F33" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="H33" s="20" t="s">
+        <v>183</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H3" xr:uid="{ED338C3A-DA4C-4D5F-A899-E433FCAE3C09}"/>
-  <mergeCells count="1">
+  <autoFilter ref="A3:H3" xr:uid="{64F28086-F537-4126-8D05-E3F23A7736C9}"/>
+  <mergeCells count="11">
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A32:H32"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A21:H21"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.3888888888888889" bottom="0.3888888888888889" header="0.16666666666666666" footer="0.16666666666666666"/>
@@ -2421,7 +2582,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0B4B3E5-058D-4079-92A2-FA61E53B4DD5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F7DB36-967C-4FF3-B04E-1586A0234A59}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2436,18 +2597,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
+      <c r="A1" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="27"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="27"/>
     </row>
     <row r="2" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="26" t="s">
-        <v>175</v>
+      <c r="A2" s="29" t="s">
+        <v>185</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2465,226 +2626,226 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="18" t="s">
-        <v>182</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>183</v>
-      </c>
-      <c r="C5" s="16" t="s">
-        <v>184</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>185</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="F5" s="16" t="s">
-        <v>187</v>
+      <c r="A5" s="30" t="s">
+        <v>192</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>195</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
-        <v>188</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>189</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>190</v>
-      </c>
-      <c r="D6" s="20" t="s">
-        <v>191</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>192</v>
-      </c>
-      <c r="F6" s="20" t="s">
-        <v>193</v>
+      <c r="A6" s="31" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="F6" s="23" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
-        <v>194</v>
-      </c>
-      <c r="B7" s="16" t="s">
-        <v>195</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>196</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>198</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>199</v>
+      <c r="A7" s="30" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
-        <v>200</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>201</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>202</v>
-      </c>
-      <c r="D8" s="20" t="s">
-        <v>203</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>204</v>
-      </c>
-      <c r="F8" s="20" t="s">
-        <v>205</v>
+      <c r="A8" s="31" t="s">
+        <v>207</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="B9" s="16" t="s">
-        <v>207</v>
-      </c>
-      <c r="C9" s="16" t="s">
-        <v>208</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>209</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="F9" s="16" t="s">
-        <v>211</v>
+      <c r="A9" s="30" t="s">
+        <v>212</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>134</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="F9" s="19" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
-        <v>212</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="D10" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="F10" s="20" t="s">
+      <c r="A10" s="31" t="s">
         <v>217</v>
       </c>
+      <c r="B10" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
-        <v>218</v>
-      </c>
-      <c r="B11" s="16" t="s">
-        <v>219</v>
-      </c>
-      <c r="C11" s="16" t="s">
-        <v>220</v>
-      </c>
-      <c r="D11" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="E11" s="16" t="s">
+      <c r="A11" s="30" t="s">
         <v>222</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="B11" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>223</v>
       </c>
+      <c r="D11" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>225</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>226</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>225</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>226</v>
-      </c>
-      <c r="D12" s="20" t="s">
+      <c r="A12" s="31" t="s">
         <v>227</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="B12" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="C12" s="23" t="s">
         <v>228</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="D12" s="23" t="s">
         <v>229</v>
       </c>
+      <c r="E12" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="18" t="s">
-        <v>230</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>231</v>
-      </c>
-      <c r="C13" s="16" t="s">
+      <c r="A13" s="30" t="s">
         <v>232</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="B13" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="D13" s="19" t="s">
         <v>234</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="E13" s="19" t="s">
         <v>235</v>
       </c>
+      <c r="F13" s="19" t="s">
+        <v>236</v>
+      </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="22" t="s">
-        <v>236</v>
-      </c>
-      <c r="B14" s="20" t="s">
+      <c r="A14" s="31" t="s">
         <v>237</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="B14" s="23" t="s">
         <v>238</v>
       </c>
-      <c r="D14" s="20" t="s">
-        <v>238</v>
-      </c>
-      <c r="E14" s="20" t="s">
+      <c r="C14" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="D14" s="23" t="s">
+        <v>239</v>
+      </c>
+      <c r="E14" s="23" t="s">
         <v>240</v>
       </c>
+      <c r="F14" s="23" t="s">
+        <v>241</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F4" xr:uid="{E0B4B3E5-058D-4079-92A2-FA61E53B4DD5}"/>
+  <autoFilter ref="A4:F4" xr:uid="{33F7DB36-967C-4FF3-B04E-1586A0234A59}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -2699,7 +2860,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D8A0890-527E-4B14-84E0-376AFCECB64D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EB7B09D-E485-4BE6-A301-4B4AD1511C37}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2712,11 +2873,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="A1" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2725,133 +2886,133 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
-        <v>245</v>
-      </c>
-      <c r="B4" s="17" t="s">
+      <c r="A4" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="B4" s="20" t="s">
         <v>247</v>
       </c>
+      <c r="C4" s="20" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
-        <v>248</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="31" t="s">
         <v>249</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="B5" s="24" t="s">
         <v>250</v>
       </c>
+      <c r="C5" s="24" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
-        <v>251</v>
-      </c>
-      <c r="B6" s="17" t="s">
+      <c r="A6" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="B6" s="20" t="s">
         <v>253</v>
       </c>
+      <c r="C6" s="20" t="s">
+        <v>254</v>
+      </c>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="B7" s="21" t="s">
+      <c r="A7" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="B7" s="24" t="s">
         <v>256</v>
       </c>
+      <c r="C7" s="24" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="18" t="s">
-        <v>257</v>
-      </c>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="B8" s="20" t="s">
         <v>259</v>
       </c>
+      <c r="C8" s="20" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
-        <v>260</v>
-      </c>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="B9" s="24" t="s">
         <v>262</v>
       </c>
+      <c r="C9" s="24" t="s">
+        <v>263</v>
+      </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="B10" s="17" t="s">
+      <c r="A10" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="B10" s="20" t="s">
         <v>265</v>
       </c>
+      <c r="C10" s="20" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
-        <v>266</v>
-      </c>
-      <c r="B11" s="21" t="s">
+      <c r="A11" s="31" t="s">
         <v>267</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="B11" s="24" t="s">
         <v>268</v>
       </c>
+      <c r="C11" s="24" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="18" t="s">
-        <v>269</v>
-      </c>
-      <c r="B12" s="17" t="s">
+      <c r="A12" s="30" t="s">
         <v>270</v>
       </c>
-      <c r="C12" s="17" t="s">
+      <c r="B12" s="20" t="s">
         <v>271</v>
       </c>
+      <c r="C12" s="20" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
-        <v>272</v>
-      </c>
-      <c r="B13" s="21" t="s">
+      <c r="A13" s="31" t="s">
         <v>273</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="B13" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="C13" s="24" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="B14" s="17" t="s">
+      <c r="A14" s="30" t="s">
         <v>275</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="B14" s="20" t="s">
+        <v>276</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2869,7 +3030,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B070CCDC-2A03-4175-A6EE-99E734F702E1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E8D30FF-B0A5-43DB-BAFD-52725DE0444B}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2881,11 +3042,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
-        <v>276</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="A1" s="28" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2894,101 +3055,101 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
-        <v>280</v>
-      </c>
-      <c r="B4" s="17" t="s">
+      <c r="A4" s="20" t="s">
         <v>281</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="B4" s="20" t="s">
         <v>282</v>
       </c>
+      <c r="C4" s="20" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
-        <v>283</v>
-      </c>
-      <c r="B5" s="21" t="s">
+      <c r="A5" s="24" t="s">
         <v>284</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="B5" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" s="24" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
-        <v>285</v>
-      </c>
-      <c r="B6" s="17" t="s">
+      <c r="A6" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="B6" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
-        <v>287</v>
-      </c>
-      <c r="B7" s="21" t="s">
+      <c r="A7" s="24" t="s">
         <v>288</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="B7" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="C7" s="24" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
-        <v>289</v>
-      </c>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="C8" s="17" t="s">
-        <v>262</v>
+      <c r="B8" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>263</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="24" t="s">
         <v>292</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="B9" s="24" t="s">
         <v>293</v>
       </c>
+      <c r="C9" s="24" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="B10" s="17" t="s">
+      <c r="A10" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="B10" s="20" t="s">
         <v>296</v>
       </c>
+      <c r="C10" s="20" t="s">
+        <v>297</v>
+      </c>
     </row>
     <row r="11" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
-        <v>297</v>
-      </c>
-      <c r="B11" s="21" t="s">
+      <c r="A11" s="24" t="s">
         <v>298</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="B11" s="24" t="s">
         <v>299</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -2997,8 +3158,8 @@
       <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
-        <v>300</v>
+      <c r="A13" s="29" t="s">
+        <v>301</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>

--- a/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
+++ b/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{13D53E85-6EF1-48F8-9471-880723650060}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4B747BA-E525-41A3-AF31-9240A6BF7238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{60B9C012-0860-4352-9EE5-2F90FE5111DB}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{48A9A570-A2FC-468F-9A4B-EB5C26479F39}"/>
   </bookViews>
   <sheets>
     <sheet name="Mode d'emploi" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Espace central d''echange'!$A$4:$F$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Jobs et cycles'!$A$3:$H$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Jobs et cycles'!$A$3:$J$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Checklist quotidienne'!$A$1:$C$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Depannage niveau 1'!$A$1:$C$13</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Espace central d''echange'!$A$1:$F$14</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Glossaire Control-M'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Jobs et cycles'!$A$1:$H$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Jobs et cycles'!$A$1:$J$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Mode d''emploi'!$A$1:$D$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="317">
   <si>
     <t>Dossier d'exploitation quotidien - ERP_CRM_FACTORY</t>
   </si>
@@ -168,6 +168,12 @@
     <t>Commande relancer</t>
   </si>
   <si>
+    <t>Declenchement</t>
+  </si>
+  <si>
+    <t>Job precedent requis</t>
+  </si>
+  <si>
     <t>Ventes</t>
   </si>
   <si>
@@ -195,6 +201,12 @@
     <t>./bin/rerun_job.sh ECFCVTRL "raison"</t>
   </si>
   <si>
+    <t>Automatique - fenetre calendaire nocturne (00h05)</t>
+  </si>
+  <si>
+    <t>Aucun - demarre seul (1er job du cycle)</t>
+  </si>
+  <si>
     <t>ECFCVTNT</t>
   </si>
   <si>
@@ -213,6 +225,9 @@
     <t>./bin/rerun_job.sh ECFCVTNT "raison"</t>
   </si>
   <si>
+    <t>Automatique - des que ECFCVTRL a reussi</t>
+  </si>
+  <si>
     <t>ECFCVTRP</t>
   </si>
   <si>
@@ -234,6 +249,9 @@
     <t>./bin/rerun_job.sh ECFCVTRP "raison"</t>
   </si>
   <si>
+    <t>Automatique - des que ECFCVTNT a reussi</t>
+  </si>
+  <si>
     <t>ECFJVTSV</t>
   </si>
   <si>
@@ -258,6 +276,12 @@
     <t>Rien a faire - se relance seul toutes les 15 min</t>
   </si>
   <si>
+    <t>Automatique - repetitif toutes les 15 min (8h-18h)</t>
+  </si>
+  <si>
+    <t>Aucun - independant</t>
+  </si>
+  <si>
     <t>ECFCVTEM1</t>
   </si>
   <si>
@@ -282,6 +306,9 @@
     <t>./bin/rerun_job.sh ECFCVTEM1 "raison"</t>
   </si>
   <si>
+    <t>Automatique - fenetre calendaire mensuelle (1er du mois)</t>
+  </si>
+  <si>
     <t>Comptabilite</t>
   </si>
   <si>
@@ -309,6 +336,9 @@
     <t>./bin/rerun_job.sh ECFCEOD1 "raison"</t>
   </si>
   <si>
+    <t>Automatique - minuteur dedie 23h50</t>
+  </si>
+  <si>
     <t>ECFCCPRB1</t>
   </si>
   <si>
@@ -345,6 +375,9 @@
     <t>./bin/rerun_job.sh ECFCCPFI1 "raison"</t>
   </si>
   <si>
+    <t>Automatique - des que ECFCCPRB1 a reussi</t>
+  </si>
+  <si>
     <t>ECFCCPEM1</t>
   </si>
   <si>
@@ -387,6 +420,9 @@
     <t>./bin/rerun_job.sh ECFCCPEQ1 "raison"</t>
   </si>
   <si>
+    <t>Automatique - fenetre calendaire trimestrielle</t>
+  </si>
+  <si>
     <t>Achat</t>
   </si>
   <si>
@@ -414,6 +450,9 @@
     <t>./bin/rerun_job.sh ECFCCUT1 "raison"</t>
   </si>
   <si>
+    <t>Automatique - minuteur dedie 15h</t>
+  </si>
+  <si>
     <t>ECFCAHRA1</t>
   </si>
   <si>
@@ -432,6 +471,9 @@
     <t>./bin/rerun_job.sh ECFCAHRA1 "raison"</t>
   </si>
   <si>
+    <t>Aucun - demarre seul (seul job du cycle)</t>
+  </si>
+  <si>
     <t>CRM</t>
   </si>
   <si>
@@ -475,6 +517,9 @@
   </si>
   <si>
     <t>./bin/view_history.sh ECFJSTRU</t>
+  </si>
+  <si>
+    <t>Automatique - repetitif toutes les 15 min (continu)</t>
   </si>
   <si>
     <t>ECFCSTIN1</t>
@@ -961,7 +1006,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1066,6 +1111,19 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FFA5AABE"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFFAA3C"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color rgb="FFEBEBF5"/>
@@ -1150,7 +1208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1184,19 +1242,31 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1510,7 +1580,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF59E5C8-F50C-4DAD-A618-C3ED0F9CF201}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{006C8208-7FC9-4ECB-A676-3A9A23F55FD8}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1737,7 +1807,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71019500-FA56-4C8D-82AE-A66BBA5159F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68D858C-0C80-45EA-80ED-22A8BBB8BE0E}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1851,12 +1921,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F28086-F537-4126-8D05-E3F23A7736C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89A4DA5-D5F2-4060-9536-6AE48AA8DAB7}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
@@ -1867,9 +1937,11 @@
     <col min="6" max="6" width="45.77734375" customWidth="1"/>
     <col min="7" max="7" width="30.77734375" customWidth="1"/>
     <col min="8" max="8" width="35.77734375" customWidth="1"/>
+    <col min="9" max="9" width="42.77734375" customWidth="1"/>
+    <col min="10" max="10" width="22.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>30</v>
       </c>
@@ -1880,8 +1952,10 @@
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
       <c r="H1" s="13"/>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="12"/>
       <c r="B2" s="12"/>
       <c r="C2" s="12"/>
@@ -1890,8 +1964,10 @@
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
       <c r="H2" s="12"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>31</v>
       </c>
@@ -1916,10 +1992,16 @@
       <c r="H3" s="15" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I3" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -1928,140 +2010,172 @@
       <c r="F4" s="17"/>
       <c r="G4" s="17"/>
       <c r="H4" s="17"/>
-    </row>
-    <row r="5" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+    </row>
+    <row r="5" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C5" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5" s="23" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="J6" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="D5" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="20" t="s">
+    </row>
+    <row r="7" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="F5" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="G5" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="H5" s="20" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
-        <v>48</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="C6" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>51</v>
-      </c>
-      <c r="G6" s="24" t="s">
+      <c r="D7" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="H6" s="24" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="G7" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="H7" s="20" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="24" t="s">
+    </row>
+    <row r="8" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="26" t="s">
         <v>67</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="B8" s="24" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="27" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="J8" s="30" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A9" s="21" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F9" s="20" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="G9" s="20" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H9" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="J9" s="23" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -2070,140 +2184,172 @@
       <c r="F10" s="17"/>
       <c r="G10" s="17"/>
       <c r="H10" s="17"/>
-    </row>
-    <row r="11" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="I10" s="17"/>
+      <c r="J10" s="17"/>
+    </row>
+    <row r="11" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A11" s="21" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B11" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>98</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="I12" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12" s="30" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="J13" s="29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="26" t="s">
+        <v>109</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="27" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="D14" s="24" t="s">
         <v>80</v>
       </c>
-      <c r="D11" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="H11" s="20" t="s">
+      <c r="E14" s="25" t="s">
+        <v>111</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="H14" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="I14" s="25" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>89</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
-        <v>92</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="H13" s="20" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="25" t="s">
-        <v>98</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>99</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="J14" s="30" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+      <c r="I15" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="J15" s="23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -2212,62 +2358,76 @@
       <c r="F16" s="17"/>
       <c r="G16" s="17"/>
       <c r="H16" s="17"/>
-    </row>
-    <row r="17" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>115</v>
+        <v>127</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>117</v>
+        <v>129</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>119</v>
+        <v>131</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="25" t="s">
-        <v>121</v>
-      </c>
-      <c r="B18" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="C18" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="D18" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>123</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="G18" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="H18" s="24" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+      <c r="I17" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="J17" s="23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>135</v>
+      </c>
+      <c r="C18" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="G18" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="H18" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="I18" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="J18" s="30" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -2276,36 +2436,44 @@
       <c r="F19" s="17"/>
       <c r="G19" s="17"/>
       <c r="H19" s="17"/>
-    </row>
-    <row r="20" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="I19" s="17"/>
+      <c r="J19" s="17"/>
+    </row>
+    <row r="20" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A20" s="21" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>132</v>
+        <v>146</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+        <v>147</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J20" s="23" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -2314,62 +2482,76 @@
       <c r="F21" s="17"/>
       <c r="G21" s="17"/>
       <c r="H21" s="17"/>
-    </row>
-    <row r="22" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="I21" s="17"/>
+      <c r="J21" s="17"/>
+    </row>
+    <row r="22" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A22" s="21" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>136</v>
+        <v>150</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>138</v>
+        <v>152</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>139</v>
+        <v>153</v>
       </c>
       <c r="F22" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="I22" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="J22" s="23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="C23" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="G23" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="H23" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="I23" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="J23" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="G22" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="H22" s="20" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="B23" s="23" t="s">
-        <v>143</v>
-      </c>
-      <c r="C23" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="F23" s="24" t="s">
-        <v>145</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>146</v>
-      </c>
-      <c r="H23" s="24" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -2378,36 +2560,44 @@
       <c r="F24" s="17"/>
       <c r="G24" s="17"/>
       <c r="H24" s="17"/>
-    </row>
-    <row r="25" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+    </row>
+    <row r="25" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+      <c r="I25" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J25" s="23" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -2416,36 +2606,44 @@
       <c r="F26" s="17"/>
       <c r="G26" s="17"/>
       <c r="H26" s="17"/>
-    </row>
-    <row r="27" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+    </row>
+    <row r="27" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+        <v>176</v>
+      </c>
+      <c r="I27" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="J27" s="23" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -2454,36 +2652,44 @@
       <c r="F28" s="17"/>
       <c r="G28" s="17"/>
       <c r="H28" s="17"/>
-    </row>
-    <row r="29" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+    </row>
+    <row r="29" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A29" s="21" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+      <c r="I29" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="J29" s="23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="18" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -2492,36 +2698,44 @@
       <c r="F30" s="17"/>
       <c r="G30" s="17"/>
       <c r="H30" s="17"/>
-    </row>
-    <row r="31" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+    </row>
+    <row r="31" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="J31" s="23" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -2530,51 +2744,59 @@
       <c r="F32" s="17"/>
       <c r="G32" s="17"/>
       <c r="H32" s="17"/>
-    </row>
-    <row r="33" spans="1:8" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
+    </row>
+    <row r="33" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>183</v>
+        <v>198</v>
+      </c>
+      <c r="I33" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="J33" s="23" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H3" xr:uid="{64F28086-F537-4126-8D05-E3F23A7736C9}"/>
+  <autoFilter ref="A3:J3" xr:uid="{A89A4DA5-D5F2-4060-9536-6AE48AA8DAB7}"/>
   <mergeCells count="11">
-    <mergeCell ref="A24:H24"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A32:H32"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A21:J21"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.3888888888888889" bottom="0.3888888888888889" header="0.16666666666666666" footer="0.16666666666666666"/>
-  <pageSetup paperSize="9" scale="57" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="45" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;LERP_CRM_FACTORY - Dossier d'exploitation quotidien&amp;RPage &amp;P / &amp;N</oddFooter>
   </headerFooter>
@@ -2582,7 +2804,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F7DB36-967C-4FF3-B04E-1586A0234A59}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20B30C8B-3412-47A1-8CA2-2361094DE648}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2597,18 +2819,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
+      <c r="A1" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
     </row>
     <row r="2" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="29" t="s">
-        <v>185</v>
+      <c r="A2" s="33" t="s">
+        <v>200</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2626,226 +2848,226 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="30" t="s">
-        <v>192</v>
+      <c r="A5" s="34" t="s">
+        <v>207</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="31" t="s">
-        <v>197</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="F6" s="23" t="s">
-        <v>201</v>
+      <c r="A6" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="30" t="s">
-        <v>202</v>
+      <c r="A7" s="34" t="s">
+        <v>217</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>211</v>
+      <c r="A8" s="35" t="s">
+        <v>222</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>124</v>
+      </c>
+      <c r="C8" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="30" t="s">
-        <v>212</v>
+      <c r="A9" s="34" t="s">
+        <v>227</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="31" t="s">
-        <v>217</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>218</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>219</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="F10" s="23" t="s">
-        <v>221</v>
+      <c r="A10" s="35" t="s">
+        <v>232</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>234</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
-        <v>222</v>
+      <c r="A11" s="34" t="s">
+        <v>237</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="31" t="s">
-        <v>227</v>
-      </c>
-      <c r="B12" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="C12" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="D12" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="E12" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="F12" s="23" t="s">
-        <v>231</v>
+      <c r="A12" s="35" t="s">
+        <v>242</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="30" t="s">
-        <v>232</v>
+      <c r="A13" s="34" t="s">
+        <v>247</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="31" t="s">
-        <v>237</v>
-      </c>
-      <c r="B14" s="23" t="s">
-        <v>238</v>
-      </c>
-      <c r="C14" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="D14" s="23" t="s">
-        <v>239</v>
-      </c>
-      <c r="E14" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="F14" s="23" t="s">
-        <v>241</v>
+      <c r="A14" s="35" t="s">
+        <v>252</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="E14" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>256</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F4" xr:uid="{33F7DB36-967C-4FF3-B04E-1586A0234A59}"/>
+  <autoFilter ref="A4:F4" xr:uid="{20B30C8B-3412-47A1-8CA2-2361094DE648}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -2860,7 +3082,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0EB7B09D-E485-4BE6-A301-4B4AD1511C37}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9606EB2-1B12-44CD-BC7A-CF71F2148CA2}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2873,11 +3095,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
-        <v>242</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
+      <c r="A1" s="32" t="s">
+        <v>257</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -2886,131 +3108,131 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="30" t="s">
-        <v>246</v>
+      <c r="A4" s="34" t="s">
+        <v>261</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="31" t="s">
-        <v>249</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>251</v>
+      <c r="A5" s="35" t="s">
+        <v>264</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>265</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="30" t="s">
-        <v>252</v>
+      <c r="A6" s="34" t="s">
+        <v>267</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="31" t="s">
-        <v>255</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>257</v>
+      <c r="A7" s="35" t="s">
+        <v>270</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>271</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="30" t="s">
-        <v>258</v>
+      <c r="A8" s="34" t="s">
+        <v>273</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="31" t="s">
-        <v>261</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>263</v>
+      <c r="A9" s="35" t="s">
+        <v>276</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>277</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="30" t="s">
-        <v>264</v>
+      <c r="A10" s="34" t="s">
+        <v>279</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="31" t="s">
-        <v>267</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>268</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>269</v>
+      <c r="A11" s="35" t="s">
+        <v>282</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>283</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>284</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
-        <v>270</v>
+      <c r="A12" s="34" t="s">
+        <v>285</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="31" t="s">
-        <v>273</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>274</v>
-      </c>
-      <c r="C13" s="24" t="s">
+      <c r="A13" s="35" t="s">
+        <v>288</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="C13" s="25" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="30" t="s">
-        <v>275</v>
+      <c r="A14" s="34" t="s">
+        <v>290</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="C14" s="20" t="s">
         <v>20</v>
@@ -3030,7 +3252,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E8D30FF-B0A5-43DB-BAFD-52725DE0444B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD792D87-6FA5-4913-8CFA-083FE69E8CDB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3042,11 +3264,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
-        <v>277</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
+      <c r="A1" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -3055,101 +3277,101 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
-        <v>284</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>285</v>
-      </c>
-      <c r="C5" s="24" t="s">
+      <c r="A5" s="25" t="s">
+        <v>299</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>300</v>
+      </c>
+      <c r="C5" s="25" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="C6" s="20" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24" t="s">
-        <v>288</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>289</v>
-      </c>
-      <c r="C7" s="24" t="s">
+      <c r="A7" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>304</v>
+      </c>
+      <c r="C7" s="25" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="24" t="s">
-        <v>292</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>293</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>294</v>
+      <c r="A9" s="25" t="s">
+        <v>307</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="20" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
-        <v>298</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>299</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>300</v>
+      <c r="A11" s="25" t="s">
+        <v>313</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>315</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -3158,8 +3380,8 @@
       <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="29" t="s">
-        <v>301</v>
+      <c r="A13" s="33" t="s">
+        <v>316</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>

--- a/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
+++ b/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
@@ -8,27 +8,30 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B4B747BA-E525-41A3-AF31-9240A6BF7238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4367CC00-171E-4DAB-83AE-3546C37E3903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{48A9A570-A2FC-468F-9A4B-EB5C26479F39}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{583B5E25-D70A-4166-AA70-97E1A63ECF04}"/>
   </bookViews>
   <sheets>
     <sheet name="Mode d'emploi" sheetId="1" r:id="rId1"/>
     <sheet name="Checklist quotidienne" sheetId="2" r:id="rId2"/>
     <sheet name="Jobs et cycles" sheetId="3" r:id="rId3"/>
-    <sheet name="Espace central d'echange" sheetId="4" r:id="rId4"/>
-    <sheet name="Glossaire Control-M" sheetId="5" r:id="rId5"/>
-    <sheet name="Depannage niveau 1" sheetId="6" r:id="rId6"/>
+    <sheet name="Jobs par type de traitement" sheetId="4" r:id="rId4"/>
+    <sheet name="Espace central d'echange" sheetId="5" r:id="rId5"/>
+    <sheet name="Glossaire Control-M" sheetId="6" r:id="rId6"/>
+    <sheet name="Depannage niveau 1" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Espace central d''echange'!$A$4:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Espace central d''echange'!$A$4:$F$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Jobs et cycles'!$A$3:$J$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Jobs par type de traitement'!$A$3:$J$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Checklist quotidienne'!$A$1:$C$9</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Depannage niveau 1'!$A$1:$C$13</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Espace central d''echange'!$A$1:$F$14</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Glossaire Control-M'!$A$1:$C$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Depannage niveau 1'!$A$1:$C$13</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Espace central d''echange'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Glossaire Control-M'!$A$1:$C$14</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Jobs et cycles'!$A$1:$J$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Mode d''emploi'!$A$1:$D$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Jobs par type de traitement'!$A$1:$J$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Mode d''emploi'!$A$1:$D$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="336">
   <si>
     <t>Dossier d'exploitation quotidien - ERP_CRM_FACTORY</t>
   </si>
@@ -72,6 +75,9 @@
     <t>COMMENT LIRE LA FEUILLE 'Jobs et cycles' : les traitements sont regroupes par famille (Ventes, Comptabilite, Achat...) - un petit '-' dans la marge de gauche permet de REPLIER une famille (ne montrer que son nom) ou de la DEPLIER (voir chacun de ses traitements). Chaque ligne de detail est un traitement reel. La colonne 'Ou recuperer le resultat' donne le chemin exact (a completer avec la date du jour, format annee-mois-jour). Les colonnes 'Commande historique' et 'Commande relancer' sont deja pretes - l'identifiant du traitement est deja ecrit dedans, rien a remplacer.</t>
   </si>
   <si>
+    <t>DEUX FACONS DE LIRE LES MEMES TRAITEMENTS : la feuille 'Jobs et cycles' les groupe par famille metier (Ventes, Comptabilite...). La feuille 'Jobs par type de traitement' groupe EXACTEMENT LES MEMES 20 traitements mais par TFJ/EOM/EOD/etc. - ouverte repliee, elle repond d'un coup d'oeil a 'combien de TFJ ce soir ?' sans avoir a compter a la main dans l'autre feuille.</t>
+  </si>
+  <si>
     <t>EN CAS DE DOUTE : la feuille 'Depannage niveau 1' liste les situations les plus frequentes avec la commande exacte a taper. La feuille 'Glossaire Control-M' traduit en langage clair chaque action possible sur un traitement.</t>
   </si>
   <si>
@@ -174,625 +180,679 @@
     <t>Job precedent requis</t>
   </si>
   <si>
+    <t>Ventes - 5 traitement(s) (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>ECFCVTRL</t>
+  </si>
+  <si>
+    <t>Relance des devis en attente (Ventes)</t>
+  </si>
+  <si>
+    <t>TFJ</t>
+  </si>
+  <si>
+    <t>Chaque nuit</t>
+  </si>
+  <si>
+    <t>Repere les devis pas encore confirmes depuis plus de 5 jours</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/vt/snd/relance_devis_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCVTRL</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCVTRL "raison"</t>
+  </si>
+  <si>
+    <t>Automatique - fenetre calendaire nocturne (00h05)</t>
+  </si>
+  <si>
+    <t>Aucun - demarre seul (1er job du cycle)</t>
+  </si>
+  <si>
+    <t>ECFCVTNT</t>
+  </si>
+  <si>
+    <t>Nettoyage des vieux devis (Ventes)</t>
+  </si>
+  <si>
+    <t>Annule automatiquement les devis de plus de 30 jours jamais confirmes</t>
+  </si>
+  <si>
+    <t>Aucun fichier - voir la liste dans l'historique du job</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCVTNT</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCVTNT "raison"</t>
+  </si>
+  <si>
+    <t>Automatique - des que ECFCVTRL a reussi</t>
+  </si>
+  <si>
+    <t>ECFCVTRP</t>
+  </si>
+  <si>
+    <t>Rapport de fin de journee (Ventes)</t>
+  </si>
+  <si>
+    <t>Chaque nuit - dernier job du cycle</t>
+  </si>
+  <si>
+    <t>Ecrit le nombre de commandes confirmees et le chiffre d'affaires du jour</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/vt/snd/rapport_eod_AAAAMMJJ.txt</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCVTRP</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCVTRP "raison"</t>
+  </si>
+  <si>
+    <t>Automatique - des que ECFCVTNT a reussi</t>
+  </si>
+  <si>
+    <t>ECFJVTSV</t>
+  </si>
+  <si>
+    <t>Suivi des devis envoyes (Ventes)</t>
+  </si>
+  <si>
+    <t>JOUR/NRT</t>
+  </si>
+  <si>
+    <t>Toutes les 15 min - 8h a 18h</t>
+  </si>
+  <si>
+    <t>Alerte si un devis envoye au client reste sans reponse depuis plus de 2h</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/vt/snd/suivi_jour_devis_AAAAMMJJ_HHMM.csv (uniquement s'il y a une alerte)</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFJVTSV</t>
+  </si>
+  <si>
+    <t>Rien a faire - se relance seul toutes les 15 min</t>
+  </si>
+  <si>
+    <t>Automatique - repetitif toutes les 15 min (8h-18h)</t>
+  </si>
+  <si>
+    <t>Aucun - independant</t>
+  </si>
+  <si>
+    <t>ECFCVTEM1</t>
+  </si>
+  <si>
+    <t>Cloture commerciale mensuelle (Ventes)</t>
+  </si>
+  <si>
+    <t>EOM</t>
+  </si>
+  <si>
+    <t>Le 1er de chaque mois</t>
+  </si>
+  <si>
+    <t>Chiffre d'affaires du mois et repartition par commercial - base des commissions</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/vt/snd/cloture_commerciale_AAAAMM.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCVTEM1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCVTEM1 "raison"</t>
+  </si>
+  <si>
+    <t>Automatique - fenetre calendaire mensuelle (1er du mois)</t>
+  </si>
+  <si>
+    <t>Comptabilite - 5 traitement(s) (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>ECFCEOD1</t>
+  </si>
+  <si>
+    <t>Bascule comptable du jour (Comptabilite)</t>
+  </si>
+  <si>
+    <t>EOD</t>
+  </si>
+  <si>
+    <t>Chaque soir a 23h50 (minuteur dedie)</t>
+  </si>
+  <si>
+    <t>Fait passer la date comptable de reference au jour suivant</t>
+  </si>
+  <si>
+    <t>$STATE_DIR/valeur_comptable_courante.txt (juste la date - pas un rapport)</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCEOD1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCEOD1 "raison"</t>
+  </si>
+  <si>
+    <t>Automatique - minuteur dedie 23h50</t>
+  </si>
+  <si>
+    <t>ECFCCPRB1</t>
+  </si>
+  <si>
+    <t>Reconciliation bancaire (Comptabilite)</t>
+  </si>
+  <si>
+    <t>Liste les lignes de releve bancaire pas encore rapprochees depuis plus de 2 jours</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/snd/reconciliation_bancaire_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCPRB1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCPRB1 "raison"</t>
+  </si>
+  <si>
+    <t>ECFCCPFI1</t>
+  </si>
+  <si>
+    <t>Relance factures impayees (Comptabilite)</t>
+  </si>
+  <si>
+    <t>Liste les factures client en retard de paiement</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/snd/relance_factures_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCPFI1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCPFI1 "raison"</t>
+  </si>
+  <si>
+    <t>Automatique - des que ECFCCPRB1 a reussi</t>
+  </si>
+  <si>
+    <t>ECFCCPEM1</t>
+  </si>
+  <si>
+    <t>Cloture comptable mensuelle (Comptabilite)</t>
+  </si>
+  <si>
+    <t>Chiffre d'affaires facture - montant encaisse - impayes du mois qui vient de finir</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/snd/cloture_mensuelle_AAAAMM.txt</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCPEM1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCPEM1 "raison"</t>
+  </si>
+  <si>
+    <t>ECFCCPEQ1</t>
+  </si>
+  <si>
+    <t>Declaration TVA trimestrielle (Comptabilite)</t>
+  </si>
+  <si>
+    <t>EOQ</t>
+  </si>
+  <si>
+    <t>Le 1er jour d'un nouveau trimestre</t>
+  </si>
+  <si>
+    <t>TVA collectee - deductible - nette du trimestre qui vient de finir (calcul de pilotage - a verifier avant transmission officielle)</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/snd/declaration_tva_AAAAMM.txt</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCPEQ1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCPEQ1 "raison"</t>
+  </si>
+  <si>
+    <t>Automatique - fenetre calendaire trimestrielle</t>
+  </si>
+  <si>
+    <t>Achat - 2 traitement(s) (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>ECFCCUT1</t>
+  </si>
+  <si>
+    <t>Heure limite commandes fournisseurs (Achat)</t>
+  </si>
+  <si>
+    <t>CUTOFF</t>
+  </si>
+  <si>
+    <t>Chaque jour a 15h (minuteur dedie)</t>
+  </si>
+  <si>
+    <t>Apres 15h toute nouvelle commande fournisseur passe automatiquement a la date du lendemain</t>
+  </si>
+  <si>
+    <t>$STATE_DIR/cutoff_achat_date_valeur.txt (juste la date - pas un rapport)</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCUT1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCUT1 "raison"</t>
+  </si>
+  <si>
+    <t>Automatique - minuteur dedie 15h</t>
+  </si>
+  <si>
+    <t>ECFCAHRA1</t>
+  </si>
+  <si>
+    <t>Propositions de reapprovisionnement (Achat)</t>
+  </si>
+  <si>
+    <t>Liste les produits sous leur seuil minimum de stock</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/ah/snd/reappro_propose_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCAHRA1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCAHRA1 "raison"</t>
+  </si>
+  <si>
+    <t>Aucun - demarre seul (seul job du cycle)</t>
+  </si>
+  <si>
+    <t>CRM - 1 traitement(s) (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>ECFCCRRL1</t>
+  </si>
+  <si>
+    <t>Relance des pistes commerciales (CRM)</t>
+  </si>
+  <si>
+    <t>Liste les pistes commerciales sans nouvelle depuis plus de 7 jours</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cr/snd/relance_pistes_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCRRL1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCRRL1 "raison"</t>
+  </si>
+  <si>
+    <t>Stock - 2 traitement(s) (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>ECFJSTRU</t>
+  </si>
+  <si>
+    <t>Alerte rupture de stock</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>Toutes les 15 min - en continu</t>
+  </si>
+  <si>
+    <t>Alerte des qu'un produit tombe a zero de stock</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/st/snd/alerte_rupture_AAAAMMJJ_HHMM.csv (uniquement s'il y a une rupture)</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFJSTRU</t>
+  </si>
+  <si>
+    <t>Automatique - repetitif toutes les 15 min (continu)</t>
+  </si>
+  <si>
+    <t>ECFCSTIN1</t>
+  </si>
+  <si>
+    <t>Valorisation du stock (Stock)</t>
+  </si>
+  <si>
+    <t>Calcule la valeur totale du stock disponible</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/st/snd/valorisation_stock_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCSTIN1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCSTIN1 "raison"</t>
+  </si>
+  <si>
+    <t>Point de vente - 1 traitement(s) (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>ECFCPSCX1</t>
+  </si>
+  <si>
+    <t>Cloture de caisse (Point de vente)</t>
+  </si>
+  <si>
+    <t>Rapport des sessions de caisse fermees dans la journee</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/ps/snd/cloture_caisse_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCPSCX1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCPSCX1 "raison"</t>
+  </si>
+  <si>
+    <t>RH - 1 traitement(s) (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>ECFCRHFC1</t>
+  </si>
+  <si>
+    <t>Alerte fin de contrat (RH)</t>
+  </si>
+  <si>
+    <t>Liste les contrats (CDD/periode d'essai) qui arrivent a echeance sous 30 jours</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/rh/snd/alerte_fin_contrat_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCRHFC1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCRHFC1 "raison"</t>
+  </si>
+  <si>
+    <t>Presences - 1 traitement(s) (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>ECFCPNHM1</t>
+  </si>
+  <si>
+    <t>Heures travaillees du mois (Presences)</t>
+  </si>
+  <si>
+    <t>Total des heures pointees par employe pour le mois qui vient de finir - base de la paie</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/pn/snd/heures_travaillees_AAAAMM.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCPNHM1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCPNHM1 "raison"</t>
+  </si>
+  <si>
+    <t>Projets - 1 traitement(s) (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>ECFCPJFA1</t>
+  </si>
+  <si>
+    <t>Base de facturation projets (Projets)</t>
+  </si>
+  <si>
+    <t>Heures de travail passees par projet pour le mois qui vient de finir - base de la facture client</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/pj/snd/facturation_temps_passe_AAAAMM.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCPJFA1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCPJFA1 "raison"</t>
+  </si>
+  <si>
+    <t>Systeme - 1 traitement(s) (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>ECFCPRG1</t>
+  </si>
+  <si>
+    <t>Archivage a froid (Systeme)</t>
+  </si>
+  <si>
+    <t>PURGE</t>
+  </si>
+  <si>
+    <t>Deplace les fichiers traites de plus de 90 jours vers l'archive a froid - ne supprime jamais rien</t>
+  </si>
+  <si>
+    <t>$ODOO_HOME/operations_archive_froide/&lt;module&gt;/</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCPRG1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCPRG1 "raison"</t>
+  </si>
+  <si>
+    <t>Memes 20 traitements, groupes par type de traitement (TFJ/EOM/EOD/...) - pour repondre a 'combien de TFJ ce soir ?'</t>
+  </si>
+  <si>
+    <t>TFJ - 10 traitements (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>JOUR/NRT - 1 traitement (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>EOM - 4 traitements (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>EOD - 1 traitement (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>EOQ - 1 traitement (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>CUTOFF - 1 traitement (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>NRT - 1 traitement (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>PURGE - 1 traitement (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>Espace central d'echange ($OPERATIONS_DIR) - meme logique qu'un espace SM2/ADI bancaire (RCV/SND/ARC)</t>
+  </si>
+  <si>
+    <t>Chaque module a EXACTEMENT 4 sous-dossiers, toujours les memes noms : rcv (fichiers RECUS, a traiter), snd (fichiers PRODUITS par les traitements - c'est ici qu'on va chercher les rapports), tmp (transit technique - ne jamais y toucher), arc (archive - fichiers deja traites, ranges automatiquement).</t>
+  </si>
+  <si>
+    <t>Code module</t>
+  </si>
+  <si>
+    <t>Module</t>
+  </si>
+  <si>
+    <t>Dossier RECU (rcv)</t>
+  </si>
+  <si>
+    <t>Dossier PRODUIT (snd)</t>
+  </si>
+  <si>
+    <t>Dossier ARCHIVE (arc)</t>
+  </si>
+  <si>
+    <t>A quoi ca sert</t>
+  </si>
+  <si>
+    <t>vt</t>
+  </si>
+  <si>
     <t>Ventes</t>
   </si>
   <si>
-    <t>ECFCVTRL</t>
-  </si>
-  <si>
-    <t>Relance des devis en attente (Ventes)</t>
-  </si>
-  <si>
-    <t>TFJ</t>
-  </si>
-  <si>
-    <t>Chaque nuit</t>
-  </si>
-  <si>
-    <t>Repere les devis pas encore confirmes depuis plus de 5 jours</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/vt/snd/relance_devis_AAAAMMJJ.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCVTRL</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCVTRL "raison"</t>
-  </si>
-  <si>
-    <t>Automatique - fenetre calendaire nocturne (00h05)</t>
-  </si>
-  <si>
-    <t>Aucun - demarre seul (1er job du cycle)</t>
-  </si>
-  <si>
-    <t>ECFCVTNT</t>
-  </si>
-  <si>
-    <t>Nettoyage des vieux devis (Ventes)</t>
-  </si>
-  <si>
-    <t>Annule automatiquement les devis de plus de 30 jours jamais confirmes</t>
-  </si>
-  <si>
-    <t>Aucun fichier - voir la liste dans l'historique du job</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCVTNT</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCVTNT "raison"</t>
-  </si>
-  <si>
-    <t>Automatique - des que ECFCVTRL a reussi</t>
-  </si>
-  <si>
-    <t>ECFCVTRP</t>
-  </si>
-  <si>
-    <t>Rapport de fin de journee (Ventes)</t>
-  </si>
-  <si>
-    <t>Chaque nuit - dernier job du cycle</t>
-  </si>
-  <si>
-    <t>Ecrit le nombre de commandes confirmees et le chiffre d'affaires du jour</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/vt/snd/rapport_eod_AAAAMMJJ.txt</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCVTRP</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCVTRP "raison"</t>
-  </si>
-  <si>
-    <t>Automatique - des que ECFCVTNT a reussi</t>
-  </si>
-  <si>
-    <t>ECFJVTSV</t>
-  </si>
-  <si>
-    <t>Suivi des devis envoyes (Ventes)</t>
-  </si>
-  <si>
-    <t>JOUR/NRT</t>
-  </si>
-  <si>
-    <t>Toutes les 15 min - 8h a 18h</t>
-  </si>
-  <si>
-    <t>Alerte si un devis envoye au client reste sans reponse depuis plus de 2h</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/vt/snd/suivi_jour_devis_AAAAMMJJ_HHMM.csv (uniquement s'il y a une alerte)</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFJVTSV</t>
-  </si>
-  <si>
-    <t>Rien a faire - se relance seul toutes les 15 min</t>
-  </si>
-  <si>
-    <t>Automatique - repetitif toutes les 15 min (8h-18h)</t>
-  </si>
-  <si>
-    <t>Aucun - independant</t>
-  </si>
-  <si>
-    <t>ECFCVTEM1</t>
-  </si>
-  <si>
-    <t>Cloture commerciale mensuelle (Ventes)</t>
-  </si>
-  <si>
-    <t>EOM</t>
-  </si>
-  <si>
-    <t>Le 1er de chaque mois</t>
-  </si>
-  <si>
-    <t>Chiffre d'affaires du mois et repartition par commercial - base des commissions</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/vt/snd/cloture_commerciale_AAAAMM.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCVTEM1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCVTEM1 "raison"</t>
-  </si>
-  <si>
-    <t>Automatique - fenetre calendaire mensuelle (1er du mois)</t>
+    <t>$OPERATIONS_DIR/vt/rcv</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/vt/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/vt/arc</t>
+  </si>
+  <si>
+    <t>Devis - commandes - factures client</t>
+  </si>
+  <si>
+    <t>cp</t>
   </si>
   <si>
     <t>Comptabilite</t>
   </si>
   <si>
-    <t>ECFCEOD1</t>
-  </si>
-  <si>
-    <t>Bascule comptable du jour (Comptabilite)</t>
-  </si>
-  <si>
-    <t>EOD</t>
-  </si>
-  <si>
-    <t>Chaque soir a 23h50 (minuteur dedie)</t>
-  </si>
-  <si>
-    <t>Fait passer la date comptable de reference au jour suivant</t>
-  </si>
-  <si>
-    <t>$STATE_DIR/valeur_comptable_courante.txt (juste la date - pas un rapport)</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCEOD1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCEOD1 "raison"</t>
-  </si>
-  <si>
-    <t>Automatique - minuteur dedie 23h50</t>
-  </si>
-  <si>
-    <t>ECFCCPRB1</t>
-  </si>
-  <si>
-    <t>Reconciliation bancaire (Comptabilite)</t>
-  </si>
-  <si>
-    <t>Liste les lignes de releve bancaire pas encore rapprochees depuis plus de 2 jours</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cp/snd/reconciliation_bancaire_AAAAMMJJ.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCCPRB1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCPRB1 "raison"</t>
-  </si>
-  <si>
-    <t>ECFCCPFI1</t>
-  </si>
-  <si>
-    <t>Relance factures impayees (Comptabilite)</t>
-  </si>
-  <si>
-    <t>Liste les factures client en retard de paiement</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cp/snd/relance_factures_AAAAMMJJ.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCCPFI1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCPFI1 "raison"</t>
-  </si>
-  <si>
-    <t>Automatique - des que ECFCCPRB1 a reussi</t>
-  </si>
-  <si>
-    <t>ECFCCPEM1</t>
-  </si>
-  <si>
-    <t>Cloture comptable mensuelle (Comptabilite)</t>
-  </si>
-  <si>
-    <t>Chiffre d'affaires facture - montant encaisse - impayes du mois qui vient de finir</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cp/snd/cloture_mensuelle_AAAAMM.txt</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCCPEM1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCPEM1 "raison"</t>
-  </si>
-  <si>
-    <t>ECFCCPEQ1</t>
-  </si>
-  <si>
-    <t>Declaration TVA trimestrielle (Comptabilite)</t>
-  </si>
-  <si>
-    <t>EOQ</t>
-  </si>
-  <si>
-    <t>Le 1er jour d'un nouveau trimestre</t>
-  </si>
-  <si>
-    <t>TVA collectee - deductible - nette du trimestre qui vient de finir (calcul de pilotage - a verifier avant transmission officielle)</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cp/snd/declaration_tva_AAAAMM.txt</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCCPEQ1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCPEQ1 "raison"</t>
-  </si>
-  <si>
-    <t>Automatique - fenetre calendaire trimestrielle</t>
+    <t>$OPERATIONS_DIR/cp/rcv</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/arc</t>
+  </si>
+  <si>
+    <t>Reconciliation - factures - clotures - TVA</t>
+  </si>
+  <si>
+    <t>cr</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cr/rcv</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cr/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cr/arc</t>
+  </si>
+  <si>
+    <t>Pistes et opportunites commerciales</t>
+  </si>
+  <si>
+    <t>ah</t>
   </si>
   <si>
     <t>Achat</t>
   </si>
   <si>
-    <t>ECFCCUT1</t>
-  </si>
-  <si>
-    <t>Heure limite commandes fournisseurs (Achat)</t>
-  </si>
-  <si>
-    <t>CUTOFF</t>
-  </si>
-  <si>
-    <t>Chaque jour a 15h (minuteur dedie)</t>
-  </si>
-  <si>
-    <t>Apres 15h toute nouvelle commande fournisseur passe automatiquement a la date du lendemain</t>
-  </si>
-  <si>
-    <t>$STATE_DIR/cutoff_achat_date_valeur.txt (juste la date - pas un rapport)</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCCUT1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCUT1 "raison"</t>
-  </si>
-  <si>
-    <t>Automatique - minuteur dedie 15h</t>
-  </si>
-  <si>
-    <t>ECFCAHRA1</t>
-  </si>
-  <si>
-    <t>Propositions de reapprovisionnement (Achat)</t>
-  </si>
-  <si>
-    <t>Liste les produits sous leur seuil minimum de stock</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/ah/snd/reappro_propose_AAAAMMJJ.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCAHRA1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCAHRA1 "raison"</t>
-  </si>
-  <si>
-    <t>Aucun - demarre seul (seul job du cycle)</t>
-  </si>
-  <si>
-    <t>CRM</t>
-  </si>
-  <si>
-    <t>ECFCCRRL1</t>
-  </si>
-  <si>
-    <t>Relance des pistes commerciales (CRM)</t>
-  </si>
-  <si>
-    <t>Liste les pistes commerciales sans nouvelle depuis plus de 7 jours</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cr/snd/relance_pistes_AAAAMMJJ.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCCRRL1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCRRL1 "raison"</t>
+    <t>$OPERATIONS_DIR/ah/rcv</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/ah/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/ah/arc</t>
+  </si>
+  <si>
+    <t>Commandes fournisseurs - reapprovisionnement</t>
+  </si>
+  <si>
+    <t>st</t>
   </si>
   <si>
     <t>Stock</t>
   </si>
   <si>
-    <t>ECFJSTRU</t>
-  </si>
-  <si>
-    <t>Alerte rupture de stock</t>
-  </si>
-  <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>Toutes les 15 min - en continu</t>
-  </si>
-  <si>
-    <t>Alerte des qu'un produit tombe a zero de stock</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/st/snd/alerte_rupture_AAAAMMJJ_HHMM.csv (uniquement s'il y a une rupture)</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFJSTRU</t>
-  </si>
-  <si>
-    <t>Automatique - repetitif toutes les 15 min (continu)</t>
-  </si>
-  <si>
-    <t>ECFCSTIN1</t>
-  </si>
-  <si>
-    <t>Valorisation du stock (Stock)</t>
-  </si>
-  <si>
-    <t>Calcule la valeur totale du stock disponible</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/st/snd/valorisation_stock_AAAAMMJJ.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCSTIN1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCSTIN1 "raison"</t>
+    <t>$OPERATIONS_DIR/st/rcv</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/st/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/st/arc</t>
+  </si>
+  <si>
+    <t>Ruptures - valorisation</t>
+  </si>
+  <si>
+    <t>ps</t>
   </si>
   <si>
     <t>Point de vente</t>
   </si>
   <si>
-    <t>ECFCPSCX1</t>
-  </si>
-  <si>
-    <t>Cloture de caisse (Point de vente)</t>
-  </si>
-  <si>
-    <t>Rapport des sessions de caisse fermees dans la journee</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/ps/snd/cloture_caisse_AAAAMMJJ.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCPSCX1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCPSCX1 "raison"</t>
+    <t>$OPERATIONS_DIR/ps/rcv</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/ps/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/ps/arc</t>
+  </si>
+  <si>
+    <t>Sessions de caisse</t>
+  </si>
+  <si>
+    <t>rh</t>
   </si>
   <si>
     <t>RH</t>
   </si>
   <si>
-    <t>ECFCRHFC1</t>
-  </si>
-  <si>
-    <t>Alerte fin de contrat (RH)</t>
-  </si>
-  <si>
-    <t>Liste les contrats (CDD/periode d'essai) qui arrivent a echeance sous 30 jours</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/rh/snd/alerte_fin_contrat_AAAAMMJJ.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCRHFC1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCRHFC1 "raison"</t>
+    <t>$OPERATIONS_DIR/rh/rcv</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/rh/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/rh/arc</t>
+  </si>
+  <si>
+    <t>Contrats employes</t>
+  </si>
+  <si>
+    <t>pn</t>
   </si>
   <si>
     <t>Presences</t>
   </si>
   <si>
-    <t>ECFCPNHM1</t>
-  </si>
-  <si>
-    <t>Heures travaillees du mois (Presences)</t>
-  </si>
-  <si>
-    <t>Total des heures pointees par employe pour le mois qui vient de finir - base de la paie</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/pn/snd/heures_travaillees_AAAAMM.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCPNHM1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCPNHM1 "raison"</t>
+    <t>$OPERATIONS_DIR/pn/rcv</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/pn/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/pn/arc</t>
+  </si>
+  <si>
+    <t>Pointages et heures travaillees</t>
+  </si>
+  <si>
+    <t>pj</t>
   </si>
   <si>
     <t>Projets</t>
-  </si>
-  <si>
-    <t>ECFCPJFA1</t>
-  </si>
-  <si>
-    <t>Base de facturation projets (Projets)</t>
-  </si>
-  <si>
-    <t>Heures de travail passees par projet pour le mois qui vient de finir - base de la facture client</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/pj/snd/facturation_temps_passe_AAAAMM.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCPJFA1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCPJFA1 "raison"</t>
-  </si>
-  <si>
-    <t>Systeme</t>
-  </si>
-  <si>
-    <t>ECFCPRG1</t>
-  </si>
-  <si>
-    <t>Archivage a froid (Systeme)</t>
-  </si>
-  <si>
-    <t>PURGE</t>
-  </si>
-  <si>
-    <t>Deplace les fichiers traites de plus de 90 jours vers l'archive a froid - ne supprime jamais rien</t>
-  </si>
-  <si>
-    <t>$ODOO_HOME/operations_archive_froide/&lt;module&gt;/</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCPRG1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCPRG1 "raison"</t>
-  </si>
-  <si>
-    <t>Espace central d'echange ($OPERATIONS_DIR) - meme logique qu'un espace SM2/ADI bancaire (RCV/SND/ARC)</t>
-  </si>
-  <si>
-    <t>Chaque module a EXACTEMENT 4 sous-dossiers, toujours les memes noms : rcv (fichiers RECUS, a traiter), snd (fichiers PRODUITS par les traitements - c'est ici qu'on va chercher les rapports), tmp (transit technique - ne jamais y toucher), arc (archive - fichiers deja traites, ranges automatiquement).</t>
-  </si>
-  <si>
-    <t>Code module</t>
-  </si>
-  <si>
-    <t>Module</t>
-  </si>
-  <si>
-    <t>Dossier RECU (rcv)</t>
-  </si>
-  <si>
-    <t>Dossier PRODUIT (snd)</t>
-  </si>
-  <si>
-    <t>Dossier ARCHIVE (arc)</t>
-  </si>
-  <si>
-    <t>A quoi ca sert</t>
-  </si>
-  <si>
-    <t>vt</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/vt/rcv</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/vt/snd</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/vt/arc</t>
-  </si>
-  <si>
-    <t>Devis - commandes - factures client</t>
-  </si>
-  <si>
-    <t>cp</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cp/rcv</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cp/snd</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cp/arc</t>
-  </si>
-  <si>
-    <t>Reconciliation - factures - clotures - TVA</t>
-  </si>
-  <si>
-    <t>cr</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cr/rcv</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cr/snd</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cr/arc</t>
-  </si>
-  <si>
-    <t>Pistes et opportunites commerciales</t>
-  </si>
-  <si>
-    <t>ah</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/ah/rcv</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/ah/snd</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/ah/arc</t>
-  </si>
-  <si>
-    <t>Commandes fournisseurs - reapprovisionnement</t>
-  </si>
-  <si>
-    <t>st</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/st/rcv</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/st/snd</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/st/arc</t>
-  </si>
-  <si>
-    <t>Ruptures - valorisation</t>
-  </si>
-  <si>
-    <t>ps</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/ps/rcv</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/ps/snd</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/ps/arc</t>
-  </si>
-  <si>
-    <t>Sessions de caisse</t>
-  </si>
-  <si>
-    <t>rh</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/rh/rcv</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/rh/snd</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/rh/arc</t>
-  </si>
-  <si>
-    <t>Contrats employes</t>
-  </si>
-  <si>
-    <t>pn</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/pn/rcv</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/pn/snd</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/pn/arc</t>
-  </si>
-  <si>
-    <t>Pointages et heures travaillees</t>
-  </si>
-  <si>
-    <t>pj</t>
   </si>
   <si>
     <t>$OPERATIONS_DIR/pj/rcv</t>
@@ -1580,11 +1640,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{006C8208-7FC9-4ECB-A676-3A9A23F55FD8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{116BECBB-5AC9-4192-9EBA-B7EDC740F385}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="100.77734375" customWidth="1"/>
@@ -1774,16 +1834,44 @@
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
+    <row r="29" spans="1:4" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A30" s="1"/>
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="1:4" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A32" s="1"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1"/>
+      <c r="C33" s="1"/>
+      <c r="D33" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="16">
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A13:D13"/>
     <mergeCell ref="A15:D15"/>
     <mergeCell ref="A17:D17"/>
@@ -1807,7 +1895,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C68D858C-0C80-45EA-80ED-22A8BBB8BE0E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{750D668D-162C-4CB1-BA0F-4D8DE03A72AA}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1820,7 +1908,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -1832,79 +1920,79 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1921,7 +2009,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A89A4DA5-D5F2-4060-9536-6AE48AA8DAB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D595B-3492-4D5D-997D-3472F5568334}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -1943,7 +2031,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -1969,39 +2057,39 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I3" s="15" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J3" s="15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -2015,167 +2103,167 @@
     </row>
     <row r="5" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E5" s="20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" s="20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H5" s="20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I5" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J5" s="23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A6" s="26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F6" s="25" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G6" s="25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H6" s="25" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J6" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A7" s="21" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G7" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H7" s="20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I7" s="20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J7" s="29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A8" s="26" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F8" s="25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H8" s="25" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J8" s="30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A9" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J9" s="23" t="s">
         <v>77</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="I9" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="J9" s="23" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="18" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B10" s="16"/>
       <c r="C10" s="16"/>
@@ -2189,167 +2277,167 @@
     </row>
     <row r="11" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A11" s="21" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F11" s="20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H11" s="20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I11" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J11" s="23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A12" s="26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F12" s="25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H12" s="25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J12" s="30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A13" s="21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F13" s="20" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G13" s="20" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H13" s="20" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I13" s="20" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J13" s="29" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A14" s="26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F14" s="25" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H14" s="25" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J14" s="30" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A15" s="21" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C15" s="22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D15" s="19" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F15" s="20" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G15" s="20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H15" s="20" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="I15" s="20" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J15" s="23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B16" s="16"/>
       <c r="C16" s="16"/>
@@ -2363,71 +2451,71 @@
     </row>
     <row r="17" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A17" s="21" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B17" s="19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C17" s="22" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D17" s="19" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F17" s="20" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G17" s="20" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H17" s="20" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I17" s="20" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J17" s="23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A18" s="26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C18" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D18" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E18" s="25" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F18" s="25" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H18" s="25" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I18" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J18" s="30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B19" s="16"/>
       <c r="C19" s="16"/>
@@ -2441,39 +2529,39 @@
     </row>
     <row r="20" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A20" s="21" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B20" s="19" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C20" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D20" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F20" s="20" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G20" s="20" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H20" s="20" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="I20" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J20" s="23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="18" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="16"/>
@@ -2487,71 +2575,71 @@
     </row>
     <row r="22" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A22" s="21" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D22" s="19" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F22" s="20" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G22" s="20" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H22" s="20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I22" s="20" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J22" s="23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A23" s="26" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B23" s="24" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C23" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D23" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G23" s="25" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="I23" s="25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J23" s="30" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="18" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B24" s="16"/>
       <c r="C24" s="16"/>
@@ -2565,39 +2653,39 @@
     </row>
     <row r="25" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A25" s="21" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B25" s="19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C25" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D25" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F25" s="20" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G25" s="20" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H25" s="20" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I25" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J25" s="23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -2611,39 +2699,39 @@
     </row>
     <row r="27" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B27" s="19" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C27" s="22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D27" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G27" s="20" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H27" s="20" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I27" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J27" s="23" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -2657,39 +2745,39 @@
     </row>
     <row r="29" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A29" s="21" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B29" s="19" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C29" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E29" s="20" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F29" s="20" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G29" s="20" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H29" s="20" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I29" s="20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J29" s="23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="18" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B30" s="16"/>
       <c r="C30" s="16"/>
@@ -2703,39 +2791,39 @@
     </row>
     <row r="31" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B31" s="19" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C31" s="22" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D31" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E31" s="20" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G31" s="20" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H31" s="20" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="I31" s="20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J31" s="23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="18" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B32" s="16"/>
       <c r="C32" s="16"/>
@@ -2749,38 +2837,38 @@
     </row>
     <row r="33" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B33" s="19" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C33" s="22" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D33" s="19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E33" s="20" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G33" s="20" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H33" s="20" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="I33" s="20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J33" s="23" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J3" xr:uid="{A89A4DA5-D5F2-4060-9536-6AE48AA8DAB7}"/>
+  <autoFilter ref="A3:J3" xr:uid="{C75D595B-3492-4D5D-997D-3472F5568334}"/>
   <mergeCells count="11">
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A26:J26"/>
@@ -2804,7 +2892,860 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20B30C8B-3412-47A1-8CA2-2361094DE648}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1126BCA-F755-4076-BC25-1026A5CA93EB}">
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.77734375" customWidth="1"/>
+    <col min="2" max="2" width="32.77734375" customWidth="1"/>
+    <col min="3" max="3" width="12.77734375" customWidth="1"/>
+    <col min="4" max="4" width="22.77734375" customWidth="1"/>
+    <col min="5" max="5" width="50.77734375" customWidth="1"/>
+    <col min="6" max="6" width="45.77734375" customWidth="1"/>
+    <col min="7" max="7" width="30.77734375" customWidth="1"/>
+    <col min="8" max="8" width="35.77734375" customWidth="1"/>
+    <col min="9" max="9" width="42.77734375" customWidth="1"/>
+    <col min="10" max="10" width="22.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="40.049999999999997" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+    </row>
+    <row r="5" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B5" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="J5" s="23" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D6" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G6" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="I7" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="J7" s="29" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="B8" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D8" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>101</v>
+      </c>
+      <c r="H8" s="25" t="s">
+        <v>102</v>
+      </c>
+      <c r="I8" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="30" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>105</v>
+      </c>
+      <c r="F9" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>107</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>108</v>
+      </c>
+      <c r="I9" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="J9" s="29" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>137</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="G10" s="25" t="s">
+        <v>139</v>
+      </c>
+      <c r="H10" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="I10" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="J10" s="30" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="F11" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="I11" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="J11" s="23" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="26" t="s">
+        <v>158</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>160</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="H12" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="I12" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="J12" s="30" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="B13" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="F13" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>170</v>
+      </c>
+      <c r="I13" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" s="23" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>173</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E14" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="F14" s="25" t="s">
+        <v>175</v>
+      </c>
+      <c r="G14" s="25" t="s">
+        <v>176</v>
+      </c>
+      <c r="H14" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="I14" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="J14" s="30" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="40.049999999999997" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="B15" s="16"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
+      <c r="I15" s="17"/>
+      <c r="J15" s="17"/>
+    </row>
+    <row r="16" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="J16" s="23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="40.049999999999997" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
+      <c r="I17" s="17"/>
+      <c r="J17" s="17"/>
+    </row>
+    <row r="18" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="21" t="s">
+        <v>78</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C18" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="I18" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J18" s="23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="26" t="s">
+        <v>110</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>111</v>
+      </c>
+      <c r="C19" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="G19" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="H19" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="I19" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="J19" s="30" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>80</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>181</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>182</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>183</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>184</v>
+      </c>
+      <c r="I20" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J20" s="23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="26" t="s">
+        <v>186</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>187</v>
+      </c>
+      <c r="C21" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>188</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>189</v>
+      </c>
+      <c r="G21" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="H21" s="25" t="s">
+        <v>191</v>
+      </c>
+      <c r="I21" s="25" t="s">
+        <v>86</v>
+      </c>
+      <c r="J21" s="30" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="40.049999999999997" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="17"/>
+      <c r="J22" s="17"/>
+    </row>
+    <row r="23" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="F23" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="I23" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="J23" s="23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="40.049999999999997" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="18" t="s">
+        <v>205</v>
+      </c>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
+    </row>
+    <row r="25" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="21" t="s">
+        <v>116</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D25" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>120</v>
+      </c>
+      <c r="F25" s="20" t="s">
+        <v>121</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>122</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>123</v>
+      </c>
+      <c r="I25" s="20" t="s">
+        <v>124</v>
+      </c>
+      <c r="J25" s="23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="40.049999999999997" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+    </row>
+    <row r="27" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>128</v>
+      </c>
+      <c r="D27" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="F27" s="20" t="s">
+        <v>131</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>132</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="I27" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="J27" s="23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="40.049999999999997" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="18" t="s">
+        <v>207</v>
+      </c>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="17"/>
+      <c r="F28" s="17"/>
+      <c r="G28" s="17"/>
+      <c r="H28" s="17"/>
+      <c r="I28" s="17"/>
+      <c r="J28" s="17"/>
+    </row>
+    <row r="29" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="F29" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="H29" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="I29" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="J29" s="23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="40.049999999999997" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
+    </row>
+    <row r="31" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="B31" s="19" t="s">
+        <v>194</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>195</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="F31" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="G31" s="20" t="s">
+        <v>198</v>
+      </c>
+      <c r="H31" s="20" t="s">
+        <v>199</v>
+      </c>
+      <c r="I31" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="J31" s="23" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A3:J3" xr:uid="{B1126BCA-F755-4076-BC25-1026A5CA93EB}"/>
+  <mergeCells count="9">
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A28:J28"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A15:J15"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A24:J24"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.3888888888888889" bottom="0.3888888888888889" header="0.16666666666666666" footer="0.16666666666666666"/>
+  <pageSetup paperSize="9" scale="45" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter>&amp;LERP_CRM_FACTORY - Dossier d'exploitation quotidien&amp;RPage &amp;P / &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9406B1E9-7694-4A1F-BF09-2C433D8838C7}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2820,7 +3761,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
@@ -2830,7 +3771,7 @@
     </row>
     <row r="2" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="33" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2848,226 +3789,226 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="34" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>41</v>
+        <v>218</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="35" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>86</v>
+        <v>224</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="34" t="s">
-        <v>217</v>
+        <v>229</v>
       </c>
       <c r="B7" s="19" t="s">
-        <v>141</v>
+        <v>230</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="35" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>124</v>
+        <v>236</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>224</v>
+        <v>238</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>225</v>
+        <v>239</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>226</v>
+        <v>240</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="34" t="s">
-        <v>227</v>
+        <v>241</v>
       </c>
       <c r="B9" s="19" t="s">
-        <v>148</v>
+        <v>242</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="D9" s="19" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="35" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="B10" s="24" t="s">
-        <v>163</v>
+        <v>248</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="D10" s="24" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="F10" s="24" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="34" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="B11" s="19" t="s">
-        <v>170</v>
+        <v>254</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="D11" s="19" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="35" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>177</v>
+        <v>260</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="34" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="B13" s="19" t="s">
-        <v>184</v>
+        <v>266</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>248</v>
+        <v>267</v>
       </c>
       <c r="D13" s="19" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>251</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="35" t="s">
-        <v>252</v>
+        <v>271</v>
       </c>
       <c r="B14" s="24" t="s">
-        <v>253</v>
+        <v>272</v>
       </c>
       <c r="C14" s="24" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="D14" s="24" t="s">
-        <v>254</v>
+        <v>273</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>256</v>
+        <v>275</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F4" xr:uid="{20B30C8B-3412-47A1-8CA2-2361094DE648}"/>
+  <autoFilter ref="A4:F4" xr:uid="{9406B1E9-7694-4A1F-BF09-2C433D8838C7}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -3081,8 +4022,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9606EB2-1B12-44CD-BC7A-CF71F2148CA2}">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3265C6B0-D840-43C5-BEE9-87D30B41E72F}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3096,7 +4037,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
-        <v>257</v>
+        <v>276</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
@@ -3108,134 +4049,134 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>258</v>
+        <v>277</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>259</v>
+        <v>278</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>260</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="34" t="s">
-        <v>261</v>
+        <v>280</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>263</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="35" t="s">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>266</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="34" t="s">
-        <v>267</v>
+        <v>286</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>268</v>
+        <v>287</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>269</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="35" t="s">
-        <v>270</v>
+        <v>289</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>271</v>
+        <v>290</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>272</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="34" t="s">
-        <v>273</v>
+        <v>292</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>274</v>
+        <v>293</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="35" t="s">
-        <v>276</v>
+        <v>295</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>277</v>
+        <v>296</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="34" t="s">
-        <v>279</v>
+        <v>298</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>280</v>
+        <v>299</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>281</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="35" t="s">
-        <v>282</v>
+        <v>301</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>283</v>
+        <v>302</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>284</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="34" t="s">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>286</v>
+        <v>305</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>287</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="35" t="s">
-        <v>288</v>
+        <v>307</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>289</v>
+        <v>308</v>
       </c>
       <c r="C13" s="25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="34" t="s">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>291</v>
+        <v>310</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -3251,8 +4192,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD792D87-6FA5-4913-8CFA-083FE69E8CDB}">
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3178942C-40BF-4D5A-B67E-AAEE7C3B7138}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3265,7 +4206,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="32" t="s">
-        <v>292</v>
+        <v>311</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
@@ -3277,101 +4218,101 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>293</v>
+        <v>312</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>294</v>
+        <v>313</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>295</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="20" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>297</v>
+        <v>316</v>
       </c>
       <c r="C4" s="20" t="s">
-        <v>298</v>
+        <v>317</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="25" t="s">
-        <v>299</v>
+        <v>318</v>
       </c>
       <c r="B5" s="25" t="s">
-        <v>300</v>
+        <v>319</v>
       </c>
       <c r="C5" s="25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
-        <v>301</v>
+        <v>320</v>
       </c>
       <c r="B6" s="20" t="s">
-        <v>302</v>
+        <v>321</v>
       </c>
       <c r="C6" s="20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="25" t="s">
-        <v>303</v>
+        <v>322</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>304</v>
+        <v>323</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="20" t="s">
-        <v>305</v>
+        <v>324</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>306</v>
+        <v>325</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>278</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="25" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>308</v>
+        <v>327</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>309</v>
+        <v>328</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="20" t="s">
-        <v>310</v>
+        <v>329</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>311</v>
+        <v>330</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>312</v>
+        <v>331</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="25" t="s">
-        <v>313</v>
+        <v>332</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>314</v>
+        <v>333</v>
       </c>
       <c r="C11" s="25" t="s">
-        <v>315</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -3381,7 +4322,7 @@
     </row>
     <row r="13" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="33" t="s">
-        <v>316</v>
+        <v>335</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>

--- a/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
+++ b/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4367CC00-171E-4DAB-83AE-3546C37E3903}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5E5DE68-2B86-4588-A403-FFF5CA9D2966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{583B5E25-D70A-4166-AA70-97E1A63ECF04}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{5CA9DAA0-172B-440A-81F0-240CDBE4BA20}"/>
   </bookViews>
   <sheets>
     <sheet name="Mode d'emploi" sheetId="1" r:id="rId1"/>
@@ -183,7 +183,7 @@
     <t>Ventes - 5 traitement(s) (deplier pour voir le detail)</t>
   </si>
   <si>
-    <t>ECFCVTRL</t>
+    <t>ECFCRELVT1</t>
   </si>
   <si>
     <t>Relance des devis en attente (Ventes)</t>
@@ -201,10 +201,10 @@
     <t>$OPERATIONS_DIR/vt/snd/relance_devis_AAAAMMJJ.csv</t>
   </si>
   <si>
-    <t>./bin/view_history.sh ECFCVTRL</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCVTRL "raison"</t>
+    <t>./bin/view_history.sh ECFCRELVT1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCRELVT1 "raison"</t>
   </si>
   <si>
     <t>Automatique - fenetre calendaire nocturne (00h05)</t>
@@ -231,10 +231,10 @@
     <t>./bin/rerun_job.sh ECFCVTNT "raison"</t>
   </si>
   <si>
-    <t>Automatique - des que ECFCVTRL a reussi</t>
-  </si>
-  <si>
-    <t>ECFCVTRP</t>
+    <t>Automatique - des que ECFCRELVT1 a reussi</t>
+  </si>
+  <si>
+    <t>ECFCCLOVT1</t>
   </si>
   <si>
     <t>Rapport de fin de journee (Ventes)</t>
@@ -249,16 +249,16 @@
     <t>$OPERATIONS_DIR/vt/snd/rapport_eod_AAAAMMJJ.txt</t>
   </si>
   <si>
-    <t>./bin/view_history.sh ECFCVTRP</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCVTRP "raison"</t>
+    <t>./bin/view_history.sh ECFCCLOVT1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCLOVT1 "raison"</t>
   </si>
   <si>
     <t>Automatique - des que ECFCVTNT a reussi</t>
   </si>
   <si>
-    <t>ECFJVTSV</t>
+    <t>ECFJALRVT1</t>
   </si>
   <si>
     <t>Suivi des devis envoyes (Ventes)</t>
@@ -276,7 +276,7 @@
     <t>$OPERATIONS_DIR/vt/snd/suivi_jour_devis_AAAAMMJJ_HHMM.csv (uniquement s'il y a une alerte)</t>
   </si>
   <si>
-    <t>./bin/view_history.sh ECFJVTSV</t>
+    <t>./bin/view_history.sh ECFJALRVT1</t>
   </si>
   <si>
     <t>Rien a faire - se relance seul toutes les 15 min</t>
@@ -288,7 +288,7 @@
     <t>Aucun - independant</t>
   </si>
   <si>
-    <t>ECFCVTEM1</t>
+    <t>ECFCCLOVT2</t>
   </si>
   <si>
     <t>Cloture commerciale mensuelle (Ventes)</t>
@@ -306,10 +306,10 @@
     <t>$OPERATIONS_DIR/vt/snd/cloture_commerciale_AAAAMM.csv</t>
   </si>
   <si>
-    <t>./bin/view_history.sh ECFCVTEM1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCVTEM1 "raison"</t>
+    <t>./bin/view_history.sh ECFCCLOVT2</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCLOVT2 "raison"</t>
   </si>
   <si>
     <t>Automatique - fenetre calendaire mensuelle (1er du mois)</t>
@@ -318,7 +318,7 @@
     <t>Comptabilite - 5 traitement(s) (deplier pour voir le detail)</t>
   </si>
   <si>
-    <t>ECFCEOD1</t>
+    <t>ECFCCLOCP1</t>
   </si>
   <si>
     <t>Bascule comptable du jour (Comptabilite)</t>
@@ -336,10 +336,10 @@
     <t>$STATE_DIR/valeur_comptable_courante.txt (juste la date - pas un rapport)</t>
   </si>
   <si>
-    <t>./bin/view_history.sh ECFCEOD1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCEOD1 "raison"</t>
+    <t>./bin/view_history.sh ECFCCLOCP1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCLOCP1 "raison"</t>
   </si>
   <si>
     <t>Automatique - minuteur dedie 23h50</t>
@@ -363,7 +363,7 @@
     <t>./bin/rerun_job.sh ECFCCPRB1 "raison"</t>
   </si>
   <si>
-    <t>ECFCCPFI1</t>
+    <t>ECFCRELCP1</t>
   </si>
   <si>
     <t>Relance factures impayees (Comptabilite)</t>
@@ -375,16 +375,16 @@
     <t>$OPERATIONS_DIR/cp/snd/relance_factures_AAAAMMJJ.csv</t>
   </si>
   <si>
-    <t>./bin/view_history.sh ECFCCPFI1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCPFI1 "raison"</t>
+    <t>./bin/view_history.sh ECFCRELCP1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCRELCP1 "raison"</t>
   </si>
   <si>
     <t>Automatique - des que ECFCCPRB1 a reussi</t>
   </si>
   <si>
-    <t>ECFCCPEM1</t>
+    <t>ECFCCLOCP2</t>
   </si>
   <si>
     <t>Cloture comptable mensuelle (Comptabilite)</t>
@@ -396,10 +396,10 @@
     <t>$OPERATIONS_DIR/cp/snd/cloture_mensuelle_AAAAMM.txt</t>
   </si>
   <si>
-    <t>./bin/view_history.sh ECFCCPEM1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCPEM1 "raison"</t>
+    <t>./bin/view_history.sh ECFCCLOCP2</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCLOCP2 "raison"</t>
   </si>
   <si>
     <t>ECFCCPEQ1</t>
@@ -483,7 +483,7 @@
     <t>CRM - 1 traitement(s) (deplier pour voir le detail)</t>
   </si>
   <si>
-    <t>ECFCCRRL1</t>
+    <t>ECFCRELCR1</t>
   </si>
   <si>
     <t>Relance des pistes commerciales (CRM)</t>
@@ -495,16 +495,16 @@
     <t>$OPERATIONS_DIR/cr/snd/relance_pistes_AAAAMMJJ.csv</t>
   </si>
   <si>
-    <t>./bin/view_history.sh ECFCCRRL1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCRRL1 "raison"</t>
+    <t>./bin/view_history.sh ECFCRELCR1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCRELCR1 "raison"</t>
   </si>
   <si>
     <t>Stock - 2 traitement(s) (deplier pour voir le detail)</t>
   </si>
   <si>
-    <t>ECFJSTRU</t>
+    <t>ECFJALRST1</t>
   </si>
   <si>
     <t>Alerte rupture de stock</t>
@@ -522,7 +522,7 @@
     <t>$OPERATIONS_DIR/st/snd/alerte_rupture_AAAAMMJJ_HHMM.csv (uniquement s'il y a une rupture)</t>
   </si>
   <si>
-    <t>./bin/view_history.sh ECFJSTRU</t>
+    <t>./bin/view_history.sh ECFJALRST1</t>
   </si>
   <si>
     <t>Automatique - repetitif toutes les 15 min (continu)</t>
@@ -549,7 +549,7 @@
     <t>Point de vente - 1 traitement(s) (deplier pour voir le detail)</t>
   </si>
   <si>
-    <t>ECFCPSCX1</t>
+    <t>ECFCCLOPS1</t>
   </si>
   <si>
     <t>Cloture de caisse (Point de vente)</t>
@@ -561,16 +561,16 @@
     <t>$OPERATIONS_DIR/ps/snd/cloture_caisse_AAAAMMJJ.csv</t>
   </si>
   <si>
-    <t>./bin/view_history.sh ECFCPSCX1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCPSCX1 "raison"</t>
+    <t>./bin/view_history.sh ECFCCLOPS1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCLOPS1 "raison"</t>
   </si>
   <si>
     <t>RH - 1 traitement(s) (deplier pour voir le detail)</t>
   </si>
   <si>
-    <t>ECFCRHFC1</t>
+    <t>ECFCALRRH1</t>
   </si>
   <si>
     <t>Alerte fin de contrat (RH)</t>
@@ -582,10 +582,10 @@
     <t>$OPERATIONS_DIR/rh/snd/alerte_fin_contrat_AAAAMMJJ.csv</t>
   </si>
   <si>
-    <t>./bin/view_history.sh ECFCRHFC1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCRHFC1 "raison"</t>
+    <t>./bin/view_history.sh ECFCALRRH1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCALRRH1 "raison"</t>
   </si>
   <si>
     <t>Presences - 1 traitement(s) (deplier pour voir le detail)</t>
@@ -1640,7 +1640,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{116BECBB-5AC9-4192-9EBA-B7EDC740F385}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EDBC628-842D-4FD5-A669-07FE066BECEE}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1895,7 +1895,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{750D668D-162C-4CB1-BA0F-4D8DE03A72AA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D42A438D-2511-41E7-A65E-EF6CD2B615AB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2009,7 +2009,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C75D595B-3492-4D5D-997D-3472F5568334}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{445E424D-07DA-4037-8EE1-9C20DC2AD792}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -2868,7 +2868,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J3" xr:uid="{C75D595B-3492-4D5D-997D-3472F5568334}"/>
+  <autoFilter ref="A3:J3" xr:uid="{445E424D-07DA-4037-8EE1-9C20DC2AD792}"/>
   <mergeCells count="11">
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A26:J26"/>
@@ -2892,7 +2892,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1126BCA-F755-4076-BC25-1026A5CA93EB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{250EDC6E-E94E-4F86-8F32-37B842AD2DF0}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -3723,7 +3723,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J3" xr:uid="{B1126BCA-F755-4076-BC25-1026A5CA93EB}"/>
+  <autoFilter ref="A3:J3" xr:uid="{250EDC6E-E94E-4F86-8F32-37B842AD2DF0}"/>
   <mergeCells count="9">
     <mergeCell ref="A26:J26"/>
     <mergeCell ref="A28:J28"/>
@@ -3745,7 +3745,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9406B1E9-7694-4A1F-BF09-2C433D8838C7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FFF9A64-935F-4A21-8AD2-3F360791801C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4008,7 +4008,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F4" xr:uid="{9406B1E9-7694-4A1F-BF09-2C433D8838C7}"/>
+  <autoFilter ref="A4:F4" xr:uid="{1FFF9A64-935F-4A21-8AD2-3F360791801C}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -4023,7 +4023,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3265C6B0-D840-43C5-BEE9-87D30B41E72F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{200C1E46-2E30-4595-ACDC-25B7C7121560}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4193,7 +4193,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3178942C-40BF-4D5A-B67E-AAEE7C3B7138}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06524582-77F1-4ADA-99B8-0D5211B3FFCC}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>

--- a/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
+++ b/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D5E5DE68-2B86-4588-A403-FFF5CA9D2966}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB7C38C8-D647-4991-8E7B-DAEF6D84EF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{5CA9DAA0-172B-440A-81F0-240CDBE4BA20}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{4CD67DC2-9D93-409A-ABE6-75A034E1D9DE}"/>
   </bookViews>
   <sheets>
     <sheet name="Mode d'emploi" sheetId="1" r:id="rId1"/>
@@ -29,8 +29,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Depannage niveau 1'!$A$1:$C$13</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Espace central d''echange'!$A$1:$F$14</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Glossaire Control-M'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Jobs et cycles'!$A$1:$J$33</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Jobs par type de traitement'!$A$1:$J$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Jobs et cycles'!$A$1:$J$50</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Jobs par type de traitement'!$A$1:$J$48</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Mode d''emploi'!$A$1:$D$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="358">
   <si>
     <t>Dossier d'exploitation quotidien - ERP_CRM_FACTORY</t>
   </si>
@@ -183,6 +183,9 @@
     <t>Ventes - 5 traitement(s) (deplier pour voir le detail)</t>
   </si>
   <si>
+    <t xml:space="preserve">   TFJ - 3 traitements</t>
+  </si>
+  <si>
     <t>ECFCRELVT1</t>
   </si>
   <si>
@@ -258,6 +261,42 @@
     <t>Automatique - des que ECFCVTNT a reussi</t>
   </si>
   <si>
+    <t xml:space="preserve">   EOM - 1 traitement</t>
+  </si>
+  <si>
+    <t>ECFCCLOVT2</t>
+  </si>
+  <si>
+    <t>Cloture commerciale mensuelle (Ventes)</t>
+  </si>
+  <si>
+    <t>EOM</t>
+  </si>
+  <si>
+    <t>Le 1er de chaque mois</t>
+  </si>
+  <si>
+    <t>Chiffre d'affaires du mois et repartition par commercial - base des commissions</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/vt/snd/cloture_commerciale_AAAAMM.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCLOVT2</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCLOVT2 "raison"</t>
+  </si>
+  <si>
+    <t>Automatique - fenetre calendaire mensuelle (1er du mois)</t>
+  </si>
+  <si>
+    <t>Aucun - independant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   JOUR/NRT - 1 traitement</t>
+  </si>
+  <si>
     <t>ECFJALRVT1</t>
   </si>
   <si>
@@ -285,39 +324,102 @@
     <t>Automatique - repetitif toutes les 15 min (8h-18h)</t>
   </si>
   <si>
-    <t>Aucun - independant</t>
-  </si>
-  <si>
-    <t>ECFCCLOVT2</t>
-  </si>
-  <si>
-    <t>Cloture commerciale mensuelle (Ventes)</t>
-  </si>
-  <si>
-    <t>EOM</t>
-  </si>
-  <si>
-    <t>Le 1er de chaque mois</t>
-  </si>
-  <si>
-    <t>Chiffre d'affaires du mois et repartition par commercial - base des commissions</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/vt/snd/cloture_commerciale_AAAAMM.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCCLOVT2</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCLOVT2 "raison"</t>
-  </si>
-  <si>
-    <t>Automatique - fenetre calendaire mensuelle (1er du mois)</t>
-  </si>
-  <si>
     <t>Comptabilite - 5 traitement(s) (deplier pour voir le detail)</t>
   </si>
   <si>
+    <t xml:space="preserve">   TFJ - 2 traitements</t>
+  </si>
+  <si>
+    <t>ECFCCPRB1</t>
+  </si>
+  <si>
+    <t>Reconciliation bancaire (Comptabilite)</t>
+  </si>
+  <si>
+    <t>Liste les lignes de releve bancaire pas encore rapprochees depuis plus de 2 jours</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/snd/reconciliation_bancaire_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCPRB1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCPRB1 "raison"</t>
+  </si>
+  <si>
+    <t>ECFCRELCP1</t>
+  </si>
+  <si>
+    <t>Relance factures impayees (Comptabilite)</t>
+  </si>
+  <si>
+    <t>Liste les factures client en retard de paiement</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/snd/relance_factures_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCRELCP1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCRELCP1 "raison"</t>
+  </si>
+  <si>
+    <t>Automatique - des que ECFCCPRB1 a reussi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   EOQ - 1 traitement</t>
+  </si>
+  <si>
+    <t>ECFCCPEQ1</t>
+  </si>
+  <si>
+    <t>Declaration TVA trimestrielle (Comptabilite)</t>
+  </si>
+  <si>
+    <t>EOQ</t>
+  </si>
+  <si>
+    <t>Le 1er jour d'un nouveau trimestre</t>
+  </si>
+  <si>
+    <t>TVA collectee - deductible - nette du trimestre qui vient de finir (calcul de pilotage - a verifier avant transmission officielle)</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/snd/declaration_tva_AAAAMM.txt</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCPEQ1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCPEQ1 "raison"</t>
+  </si>
+  <si>
+    <t>Automatique - fenetre calendaire trimestrielle</t>
+  </si>
+  <si>
+    <t>ECFCCLOCP2</t>
+  </si>
+  <si>
+    <t>Cloture comptable mensuelle (Comptabilite)</t>
+  </si>
+  <si>
+    <t>Chiffre d'affaires facture - montant encaisse - impayes du mois qui vient de finir</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/snd/cloture_mensuelle_AAAAMM.txt</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCLOCP2</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCLOCP2 "raison"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   EOD - 1 traitement</t>
+  </si>
+  <si>
     <t>ECFCCLOCP1</t>
   </si>
   <si>
@@ -345,93 +447,36 @@
     <t>Automatique - minuteur dedie 23h50</t>
   </si>
   <si>
-    <t>ECFCCPRB1</t>
-  </si>
-  <si>
-    <t>Reconciliation bancaire (Comptabilite)</t>
-  </si>
-  <si>
-    <t>Liste les lignes de releve bancaire pas encore rapprochees depuis plus de 2 jours</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cp/snd/reconciliation_bancaire_AAAAMMJJ.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCCPRB1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCPRB1 "raison"</t>
-  </si>
-  <si>
-    <t>ECFCRELCP1</t>
-  </si>
-  <si>
-    <t>Relance factures impayees (Comptabilite)</t>
-  </si>
-  <si>
-    <t>Liste les factures client en retard de paiement</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cp/snd/relance_factures_AAAAMMJJ.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCRELCP1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCRELCP1 "raison"</t>
-  </si>
-  <si>
-    <t>Automatique - des que ECFCCPRB1 a reussi</t>
-  </si>
-  <si>
-    <t>ECFCCLOCP2</t>
-  </si>
-  <si>
-    <t>Cloture comptable mensuelle (Comptabilite)</t>
-  </si>
-  <si>
-    <t>Chiffre d'affaires facture - montant encaisse - impayes du mois qui vient de finir</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cp/snd/cloture_mensuelle_AAAAMM.txt</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCCLOCP2</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCLOCP2 "raison"</t>
-  </si>
-  <si>
-    <t>ECFCCPEQ1</t>
-  </si>
-  <si>
-    <t>Declaration TVA trimestrielle (Comptabilite)</t>
-  </si>
-  <si>
-    <t>EOQ</t>
-  </si>
-  <si>
-    <t>Le 1er jour d'un nouveau trimestre</t>
-  </si>
-  <si>
-    <t>TVA collectee - deductible - nette du trimestre qui vient de finir (calcul de pilotage - a verifier avant transmission officielle)</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/cp/snd/declaration_tva_AAAAMM.txt</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCCPEQ1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCPEQ1 "raison"</t>
-  </si>
-  <si>
-    <t>Automatique - fenetre calendaire trimestrielle</t>
-  </si>
-  <si>
     <t>Achat - 2 traitement(s) (deplier pour voir le detail)</t>
   </si>
   <si>
+    <t xml:space="preserve">   TFJ - 1 traitement</t>
+  </si>
+  <si>
+    <t>ECFCAHRA1</t>
+  </si>
+  <si>
+    <t>Propositions de reapprovisionnement (Achat)</t>
+  </si>
+  <si>
+    <t>Liste les produits sous leur seuil minimum de stock</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/ah/snd/reappro_propose_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCAHRA1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCAHRA1 "raison"</t>
+  </si>
+  <si>
+    <t>Aucun - demarre seul (seul job du cycle)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   CUTOFF - 1 traitement</t>
+  </si>
+  <si>
     <t>ECFCCUT1</t>
   </si>
   <si>
@@ -459,27 +504,6 @@
     <t>Automatique - minuteur dedie 15h</t>
   </si>
   <si>
-    <t>ECFCAHRA1</t>
-  </si>
-  <si>
-    <t>Propositions de reapprovisionnement (Achat)</t>
-  </si>
-  <si>
-    <t>Liste les produits sous leur seuil minimum de stock</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/ah/snd/reappro_propose_AAAAMMJJ.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCAHRA1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCAHRA1 "raison"</t>
-  </si>
-  <si>
-    <t>Aucun - demarre seul (seul job du cycle)</t>
-  </si>
-  <si>
     <t>CRM - 1 traitement(s) (deplier pour voir le detail)</t>
   </si>
   <si>
@@ -504,6 +528,27 @@
     <t>Stock - 2 traitement(s) (deplier pour voir le detail)</t>
   </si>
   <si>
+    <t>ECFCSTIN1</t>
+  </si>
+  <si>
+    <t>Valorisation du stock (Stock)</t>
+  </si>
+  <si>
+    <t>Calcule la valeur totale du stock disponible</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/st/snd/valorisation_stock_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCSTIN1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCSTIN1 "raison"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   NRT - 1 traitement</t>
+  </si>
+  <si>
     <t>ECFJALRST1</t>
   </si>
   <si>
@@ -528,24 +573,6 @@
     <t>Automatique - repetitif toutes les 15 min (continu)</t>
   </si>
   <si>
-    <t>ECFCSTIN1</t>
-  </si>
-  <si>
-    <t>Valorisation du stock (Stock)</t>
-  </si>
-  <si>
-    <t>Calcule la valeur totale du stock disponible</t>
-  </si>
-  <si>
-    <t>$OPERATIONS_DIR/st/snd/valorisation_stock_AAAAMMJJ.csv</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCSTIN1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCSTIN1 "raison"</t>
-  </si>
-  <si>
     <t>Point de vente - 1 traitement(s) (deplier pour voir le detail)</t>
   </si>
   <si>
@@ -633,6 +660,9 @@
     <t>Systeme - 1 traitement(s) (deplier pour voir le detail)</t>
   </si>
   <si>
+    <t xml:space="preserve">   PURGE - 1 traitement</t>
+  </si>
+  <si>
     <t>ECFCPRG1</t>
   </si>
   <si>
@@ -660,12 +690,45 @@
     <t>TFJ - 10 traitements (deplier pour voir le detail)</t>
   </si>
   <si>
+    <t xml:space="preserve">   Ventes - 3 traitements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Comptabilite - 2 traitements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Point de vente - 1 traitement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   RH - 1 traitement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Stock - 1 traitement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Achat - 1 traitement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   CRM - 1 traitement</t>
+  </si>
+  <si>
     <t>JOUR/NRT - 1 traitement (deplier pour voir le detail)</t>
   </si>
   <si>
+    <t xml:space="preserve">   Ventes - 1 traitement</t>
+  </si>
+  <si>
     <t>EOM - 4 traitements (deplier pour voir le detail)</t>
   </si>
   <si>
+    <t xml:space="preserve">   Presences - 1 traitement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Projets - 1 traitement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Comptabilite - 1 traitement</t>
+  </si>
+  <si>
     <t>EOD - 1 traitement (deplier pour voir le detail)</t>
   </si>
   <si>
@@ -679,6 +742,9 @@
   </si>
   <si>
     <t>PURGE - 1 traitement (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Systeme - 1 traitement</t>
   </si>
   <si>
     <t>Espace central d'echange ($OPERATIONS_DIR) - meme logique qu'un espace SM2/ADI bancaire (RCV/SND/ARC)</t>
@@ -1066,7 +1132,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1158,6 +1224,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FFE6DCFA"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FF64DCFF"/>
       <name val="Arial"/>
@@ -1212,7 +1285,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1255,6 +1328,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5A3C82"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1268,7 +1347,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1296,37 +1375,39 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1640,7 +1721,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8EDBC628-842D-4FD5-A669-07FE066BECEE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8D7A0E5-C8B0-4260-92CA-775086BDB445}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1895,7 +1976,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D42A438D-2511-41E7-A65E-EF6CD2B615AB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB60D2D4-AE02-4080-9135-15EDA9DF677B}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2009,13 +2090,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{445E424D-07DA-4037-8EE1-9C20DC2AD792}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0323787E-4EA4-4E4D-B29D-D748291388E3}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
     <col min="2" max="2" width="32.77734375" customWidth="1"/>
@@ -2101,637 +2182,547 @@
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
     </row>
-    <row r="5" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+    </row>
+    <row r="6" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A6" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="B6" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="C6" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="D6" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="E6" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="F6" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="G6" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="H6" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="I6" s="23" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26" t="s">
+      <c r="J6" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="24" t="s">
+    </row>
+    <row r="7" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A7" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="24" t="s">
+      <c r="B7" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="25" t="s">
+      <c r="D7" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="F7" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="G7" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="I6" s="25" t="s">
+      <c r="H7" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="J6" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+      <c r="I7" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="J7" s="31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A8" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="19" t="s">
+      <c r="B8" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="C8" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="E8" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="F8" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="G8" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="H8" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="I8" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="32" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A10" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J10" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+    </row>
+    <row r="12" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A12" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="J12" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
+      <c r="I13" s="17"/>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A15" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="26" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="B8" s="24" t="s">
+    <row r="16" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A16" s="29" t="s">
+        <v>98</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="30" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="28" t="s">
+        <v>100</v>
+      </c>
+      <c r="F16" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>102</v>
+      </c>
+      <c r="H16" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="I16" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="J16" s="31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="20"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+    </row>
+    <row r="18" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A18" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B18" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="D18" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="F18" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="G18" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="H18" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="I18" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="J18" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="27" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="25" t="s">
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="20"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="20"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+    </row>
+    <row r="20" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A20" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="F8" s="25" t="s">
+      <c r="D20" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="G8" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="H8" s="25" t="s">
-        <v>75</v>
-      </c>
-      <c r="I8" s="25" t="s">
-        <v>76</v>
-      </c>
-      <c r="J8" s="30" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
+      <c r="E20" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="H20" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="I20" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="J20" s="26" t="s">
         <v>79</v>
       </c>
-      <c r="C9" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="I9" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="J9" s="23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="16"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-    </row>
-    <row r="11" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="I11" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="J11" s="23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="24" t="s">
+    </row>
+    <row r="21" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+    </row>
+    <row r="22" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A22" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B22" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="D22" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="H22" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="I22" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="J22" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="17"/>
+      <c r="F23" s="17"/>
+      <c r="G23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+    </row>
+    <row r="24" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+    </row>
+    <row r="25" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A25" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C25" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="E12" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="G12" s="25" t="s">
-        <v>101</v>
-      </c>
-      <c r="H12" s="25" t="s">
-        <v>102</v>
-      </c>
-      <c r="I12" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="J12" s="30" t="s">
+      <c r="D25" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>136</v>
+      </c>
+      <c r="G25" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="I25" s="23" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="H13" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="I13" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="J13" s="29" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="G14" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="H14" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="I14" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" s="30" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="B15" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="D15" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="F15" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G15" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="H15" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="I15" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="J15" s="23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-    </row>
-    <row r="17" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="F17" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="G17" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="H17" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="I17" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="J17" s="23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>136</v>
-      </c>
-      <c r="C18" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="E18" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="F18" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="G18" s="25" t="s">
+      <c r="J25" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="H18" s="25" t="s">
+    </row>
+    <row r="26" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="I18" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="J18" s="30" t="s">
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+    </row>
+    <row r="27" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A27" s="24" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="18" t="s">
+      <c r="B27" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-    </row>
-    <row r="20" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="21" t="s">
+      <c r="C27" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="D27" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="C20" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="E20" s="20" t="s">
+      <c r="E27" s="23" t="s">
         <v>145</v>
       </c>
-      <c r="F20" s="20" t="s">
+      <c r="F27" s="23" t="s">
         <v>146</v>
       </c>
-      <c r="G20" s="20" t="s">
+      <c r="G27" s="23" t="s">
         <v>147</v>
       </c>
-      <c r="H20" s="20" t="s">
+      <c r="H27" s="23" t="s">
         <v>148</v>
       </c>
-      <c r="I20" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="J20" s="23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="18" t="s">
+      <c r="I27" s="23" t="s">
         <v>149</v>
       </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
-    </row>
-    <row r="22" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="C22" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="F22" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="G22" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="H22" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="I22" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="J22" s="23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="B23" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="C23" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="E23" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="F23" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="G23" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="H23" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="I23" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="J23" s="30" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="18" t="s">
-        <v>164</v>
-      </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-    </row>
-    <row r="25" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C25" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="H25" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="I25" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="J25" s="23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="18" t="s">
-        <v>171</v>
-      </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-    </row>
-    <row r="27" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>173</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>174</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>175</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>176</v>
-      </c>
-      <c r="H27" s="20" t="s">
-        <v>177</v>
-      </c>
-      <c r="I27" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="J27" s="23" t="s">
-        <v>141</v>
+      <c r="J27" s="26" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18" t="s">
-        <v>178</v>
+        <v>150</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="16"/>
@@ -2743,144 +2734,489 @@
       <c r="I28" s="17"/>
       <c r="J28" s="17"/>
     </row>
-    <row r="29" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A29" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+    </row>
+    <row r="30" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A30" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="F30" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="G30" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="H30" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="I30" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J30" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="B31" s="16"/>
+      <c r="C31" s="16"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="17"/>
+      <c r="F31" s="17"/>
+      <c r="G31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
+      <c r="J31" s="17"/>
+    </row>
+    <row r="32" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+    </row>
+    <row r="33" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A33" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="G33" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="H33" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="I33" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J33" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+    </row>
+    <row r="35" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A35" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="F35" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="G35" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="H35" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="I35" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="J35" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="B36" s="16"/>
+      <c r="C36" s="16"/>
+      <c r="D36" s="16"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
+    </row>
+    <row r="37" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+    </row>
+    <row r="38" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A38" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D38" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="G38" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="H38" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="B29" s="19" t="s">
+      <c r="I38" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J38" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="C29" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="E29" s="20" t="s">
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+    </row>
+    <row r="40" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+    </row>
+    <row r="41" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A41" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="F29" s="20" t="s">
+      <c r="B41" s="22" t="s">
         <v>182</v>
       </c>
-      <c r="G29" s="20" t="s">
+      <c r="C41" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D41" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E41" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="H29" s="20" t="s">
+      <c r="F41" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="I29" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="J29" s="23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="18" t="s">
+      <c r="G41" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-    </row>
-    <row r="31" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="21" t="s">
+      <c r="H41" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="B31" s="19" t="s">
+      <c r="I41" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J41" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="C31" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="E31" s="20" t="s">
+      <c r="B42" s="16"/>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+      <c r="H42" s="17"/>
+      <c r="I42" s="17"/>
+      <c r="J42" s="17"/>
+    </row>
+    <row r="43" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B43" s="19"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+    </row>
+    <row r="44" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A44" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="F31" s="20" t="s">
+      <c r="B44" s="22" t="s">
         <v>189</v>
       </c>
-      <c r="G31" s="20" t="s">
+      <c r="C44" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D44" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E44" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="H31" s="20" t="s">
+      <c r="F44" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="I31" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="J31" s="23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="18" t="s">
+      <c r="G44" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="B32" s="16"/>
-      <c r="C32" s="16"/>
-      <c r="D32" s="16"/>
-      <c r="E32" s="17"/>
-      <c r="F32" s="17"/>
-      <c r="G32" s="17"/>
-      <c r="H32" s="17"/>
-      <c r="I32" s="17"/>
-      <c r="J32" s="17"/>
-    </row>
-    <row r="33" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="21" t="s">
+      <c r="H44" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="I44" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J44" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="B45" s="16"/>
+      <c r="C45" s="16"/>
+      <c r="D45" s="16"/>
+      <c r="E45" s="17"/>
+      <c r="F45" s="17"/>
+      <c r="G45" s="17"/>
+      <c r="H45" s="17"/>
+      <c r="I45" s="17"/>
+      <c r="J45" s="17"/>
+    </row>
+    <row r="46" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+    </row>
+    <row r="47" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A47" s="24" t="s">
         <v>195</v>
       </c>
-      <c r="D33" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="E33" s="20" t="s">
+      <c r="B47" s="22" t="s">
         <v>196</v>
       </c>
-      <c r="F33" s="20" t="s">
+      <c r="C47" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D47" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E47" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="G33" s="20" t="s">
+      <c r="F47" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="H33" s="20" t="s">
+      <c r="G47" s="23" t="s">
         <v>199</v>
       </c>
-      <c r="I33" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="J33" s="23" t="s">
-        <v>77</v>
+      <c r="H47" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="I47" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J47" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+    </row>
+    <row r="49" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
+    </row>
+    <row r="50" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A50" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="B50" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E50" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="F50" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="G50" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="H50" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="I50" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J50" s="26" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J3" xr:uid="{445E424D-07DA-4037-8EE1-9C20DC2AD792}"/>
-  <mergeCells count="11">
-    <mergeCell ref="A24:J24"/>
+  <autoFilter ref="A3:J3" xr:uid="{0323787E-4EA4-4E4D-B29D-D748291388E3}"/>
+  <mergeCells count="28">
+    <mergeCell ref="A45:J45"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="A49:J49"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A43:J43"/>
     <mergeCell ref="A26:J26"/>
     <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A31:J31"/>
     <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="A17:J17"/>
+    <mergeCell ref="A19:J19"/>
+    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A24:J24"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A10:J10"/>
-    <mergeCell ref="A16:J16"/>
-    <mergeCell ref="A19:J19"/>
-    <mergeCell ref="A21:J21"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A11:J11"/>
+    <mergeCell ref="A13:J13"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.3888888888888889" bottom="0.3888888888888889" header="0.16666666666666666" footer="0.16666666666666666"/>
@@ -2892,13 +3228,13 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{250EDC6E-E94E-4F86-8F32-37B842AD2DF0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FFE2CA6-D3DA-485A-94DF-C742C9CBCAEF}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J48"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
     <col min="2" max="2" width="32.77734375" customWidth="1"/>
@@ -2914,7 +3250,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -2970,9 +3306,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="40.049999999999997" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -2984,517 +3320,427 @@
       <c r="I4" s="17"/>
       <c r="J4" s="17"/>
     </row>
-    <row r="5" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B5" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+    </row>
+    <row r="6" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A6" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="B6" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="C6" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="D6" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="E6" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="F6" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="H5" s="20" t="s">
+      <c r="G6" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="I5" s="20" t="s">
+      <c r="H6" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="J5" s="23" t="s">
+      <c r="I6" s="23" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="26" t="s">
+      <c r="J6" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="24" t="s">
+    </row>
+    <row r="7" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A7" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="C6" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="D6" s="24" t="s">
+      <c r="B7" s="27" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="E6" s="25" t="s">
-        <v>55</v>
-      </c>
-      <c r="F6" s="25" t="s">
+      <c r="D7" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="E7" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="F7" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="H6" s="25" t="s">
+      <c r="G7" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="I6" s="25" t="s">
+      <c r="H7" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="J6" s="28" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+      <c r="I7" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="J7" s="31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A8" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="C7" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D7" s="19" t="s">
+      <c r="B8" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="C8" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="E8" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="F8" s="23" t="s">
         <v>65</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="G8" s="23" t="s">
         <v>66</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="H8" s="23" t="s">
         <v>67</v>
       </c>
-      <c r="J7" s="29" t="s">
+      <c r="I8" s="23" t="s">
+        <v>68</v>
+      </c>
+      <c r="J8" s="32" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A10" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>97</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J10" s="26" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26" t="s">
-        <v>97</v>
-      </c>
-      <c r="B8" s="24" t="s">
+    <row r="11" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A11" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="D8" s="24" t="s">
+      <c r="B11" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="C11" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="25" t="s">
-        <v>99</v>
-      </c>
-      <c r="F8" s="25" t="s">
+      <c r="D11" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="E11" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="G8" s="25" t="s">
+      <c r="F11" s="28" t="s">
         <v>101</v>
       </c>
-      <c r="H8" s="25" t="s">
+      <c r="G11" s="28" t="s">
         <v>102</v>
       </c>
-      <c r="I8" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="J8" s="30" t="s">
+      <c r="H11" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="I11" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="20"/>
+      <c r="F12" s="20"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+    </row>
+    <row r="13" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A13" s="24" t="s">
+        <v>174</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="I13" s="23" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>105</v>
-      </c>
-      <c r="F9" s="20" t="s">
-        <v>106</v>
-      </c>
-      <c r="G9" s="20" t="s">
-        <v>107</v>
-      </c>
-      <c r="H9" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="I9" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="J9" s="29" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26" t="s">
+      <c r="J13" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20"/>
+      <c r="J14" s="20"/>
+    </row>
+    <row r="15" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A15" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="I15" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+    </row>
+    <row r="17" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A17" s="24" t="s">
+        <v>158</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>159</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E17" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="F17" s="23" t="s">
+        <v>161</v>
+      </c>
+      <c r="G17" s="23" t="s">
+        <v>162</v>
+      </c>
+      <c r="H17" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="I17" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J17" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A19" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E19" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="F19" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="C10" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="24" t="s">
+      <c r="G19" s="23" t="s">
+        <v>137</v>
+      </c>
+      <c r="H19" s="23" t="s">
+        <v>138</v>
+      </c>
+      <c r="I19" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J19" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="21" t="s">
+        <v>218</v>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A21" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>152</v>
+      </c>
+      <c r="C21" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="E10" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="F10" s="25" t="s">
-        <v>138</v>
-      </c>
-      <c r="G10" s="25" t="s">
+      <c r="D21" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="H21" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="I21" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J21" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="H10" s="25" t="s">
-        <v>140</v>
-      </c>
-      <c r="I10" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="J10" s="30" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>144</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="F11" s="20" t="s">
-        <v>146</v>
-      </c>
-      <c r="G11" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="H11" s="20" t="s">
-        <v>148</v>
-      </c>
-      <c r="I11" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="J11" s="23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26" t="s">
-        <v>158</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="F12" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="G12" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="H12" s="25" t="s">
-        <v>163</v>
-      </c>
-      <c r="I12" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="J12" s="30" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>167</v>
-      </c>
-      <c r="F13" s="20" t="s">
-        <v>168</v>
-      </c>
-      <c r="G13" s="20" t="s">
-        <v>169</v>
-      </c>
-      <c r="H13" s="20" t="s">
-        <v>170</v>
-      </c>
-      <c r="I13" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="J13" s="23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="26" t="s">
-        <v>172</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="F14" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="G14" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="H14" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="I14" s="25" t="s">
-        <v>51</v>
-      </c>
-      <c r="J14" s="30" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="40.049999999999997" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="16"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-      <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
-    </row>
-    <row r="16" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="G16" s="20" t="s">
-        <v>74</v>
-      </c>
-      <c r="H16" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="I16" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="J16" s="23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" ht="40.049999999999997" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="18" t="s">
-        <v>203</v>
-      </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-      <c r="I17" s="17"/>
-      <c r="J17" s="17"/>
-    </row>
-    <row r="18" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C18" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="F18" s="20" t="s">
-        <v>83</v>
-      </c>
-      <c r="G18" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="H18" s="20" t="s">
-        <v>85</v>
-      </c>
-      <c r="I18" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="J18" s="23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="26" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="24" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="F19" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="G19" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="H19" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="I19" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="J19" s="30" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="21" t="s">
-        <v>179</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>180</v>
-      </c>
-      <c r="C20" s="22" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="F20" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="G20" s="20" t="s">
-        <v>183</v>
-      </c>
-      <c r="H20" s="20" t="s">
-        <v>184</v>
-      </c>
-      <c r="I20" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="J20" s="23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26" t="s">
-        <v>186</v>
-      </c>
-      <c r="B21" s="24" t="s">
-        <v>187</v>
-      </c>
-      <c r="C21" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" s="25" t="s">
-        <v>188</v>
-      </c>
-      <c r="F21" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="G21" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="H21" s="25" t="s">
-        <v>191</v>
-      </c>
-      <c r="I21" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="J21" s="30" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" ht="40.049999999999997" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="16"/>
@@ -3506,234 +3752,579 @@
       <c r="I22" s="17"/>
       <c r="J22" s="17"/>
     </row>
-    <row r="23" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A23" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+    </row>
+    <row r="24" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A24" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="B23" s="19" t="s">
+      <c r="I24" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="C23" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>92</v>
-      </c>
-      <c r="F23" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="G23" s="20" t="s">
-        <v>94</v>
-      </c>
-      <c r="H23" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="I23" s="20" t="s">
-        <v>96</v>
-      </c>
-      <c r="J23" s="23" t="s">
+      <c r="J24" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="H25" s="17"/>
+      <c r="I25" s="17"/>
+      <c r="J25" s="17"/>
+    </row>
+    <row r="26" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="21" t="s">
+        <v>222</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+    </row>
+    <row r="27" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A27" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>189</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" s="23" t="s">
+        <v>190</v>
+      </c>
+      <c r="F27" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="G27" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="H27" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="I27" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J27" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+    </row>
+    <row r="29" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A29" s="24" t="s">
+        <v>195</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>196</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D29" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E29" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="F29" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="G29" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="H29" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="I29" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J29" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+    </row>
+    <row r="31" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A31" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="G31" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="H31" s="23" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="40.049999999999997" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="18" t="s">
+      <c r="I31" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J31" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
+      <c r="G32" s="20"/>
+      <c r="H32" s="20"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+    </row>
+    <row r="33" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A33" s="24" t="s">
+        <v>115</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="G33" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="H33" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="I33" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J33" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="18" t="s">
+        <v>225</v>
+      </c>
+      <c r="B34" s="16"/>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="17"/>
+      <c r="F34" s="17"/>
+      <c r="G34" s="17"/>
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+    </row>
+    <row r="35" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+    </row>
+    <row r="36" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A36" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="F36" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="G36" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="H36" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="I36" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="J36" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="18" t="s">
+        <v>226</v>
+      </c>
+      <c r="B37" s="16"/>
+      <c r="C37" s="16"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="17"/>
+      <c r="F37" s="17"/>
+      <c r="G37" s="17"/>
+      <c r="H37" s="17"/>
+      <c r="I37" s="17"/>
+      <c r="J37" s="17"/>
+    </row>
+    <row r="38" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+    </row>
+    <row r="39" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A39" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="E39" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="F39" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="G39" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="H39" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="I39" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="J39" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+    </row>
+    <row r="41" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+    </row>
+    <row r="42" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A42" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="D42" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="E42" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="F42" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="G42" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="H42" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="I42" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="J42" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="18" t="s">
+        <v>228</v>
+      </c>
+      <c r="B43" s="16"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
+      <c r="H43" s="17"/>
+      <c r="I43" s="17"/>
+      <c r="J43" s="17"/>
+    </row>
+    <row r="44" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="B44" s="19"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="20"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="20"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+    </row>
+    <row r="45" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A45" s="24" t="s">
+        <v>165</v>
+      </c>
+      <c r="B45" s="22" t="s">
+        <v>166</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="D45" s="22" t="s">
+        <v>168</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="F45" s="23" t="s">
+        <v>170</v>
+      </c>
+      <c r="G45" s="23" t="s">
+        <v>171</v>
+      </c>
+      <c r="H45" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="I45" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="J45" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="B46" s="16"/>
+      <c r="C46" s="16"/>
+      <c r="D46" s="16"/>
+      <c r="E46" s="17"/>
+      <c r="F46" s="17"/>
+      <c r="G46" s="17"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+    </row>
+    <row r="47" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+    </row>
+    <row r="48" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A48" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="B48" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="C48" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-    </row>
-    <row r="25" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>117</v>
-      </c>
-      <c r="C25" s="22" t="s">
-        <v>118</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>120</v>
-      </c>
-      <c r="F25" s="20" t="s">
-        <v>121</v>
-      </c>
-      <c r="G25" s="20" t="s">
-        <v>122</v>
-      </c>
-      <c r="H25" s="20" t="s">
-        <v>123</v>
-      </c>
-      <c r="I25" s="20" t="s">
-        <v>124</v>
-      </c>
-      <c r="J25" s="23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="40.049999999999997" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="18" t="s">
+      <c r="D48" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E48" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-    </row>
-    <row r="27" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>127</v>
-      </c>
-      <c r="C27" s="22" t="s">
-        <v>128</v>
-      </c>
-      <c r="D27" s="19" t="s">
-        <v>129</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="F27" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="G27" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="H27" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="I27" s="20" t="s">
-        <v>134</v>
-      </c>
-      <c r="J27" s="23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" ht="40.049999999999997" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="18" t="s">
+      <c r="F48" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-    </row>
-    <row r="29" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>151</v>
-      </c>
-      <c r="C29" s="22" t="s">
-        <v>152</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>153</v>
-      </c>
-      <c r="E29" s="20" t="s">
-        <v>154</v>
-      </c>
-      <c r="F29" s="20" t="s">
-        <v>155</v>
-      </c>
-      <c r="G29" s="20" t="s">
-        <v>156</v>
-      </c>
-      <c r="H29" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="I29" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="J29" s="23" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="40.049999999999997" customHeight="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="18" t="s">
+      <c r="G48" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="B30" s="16"/>
-      <c r="C30" s="16"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
-    </row>
-    <row r="31" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>195</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="E31" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="F31" s="20" t="s">
-        <v>197</v>
-      </c>
-      <c r="G31" s="20" t="s">
-        <v>198</v>
-      </c>
-      <c r="H31" s="20" t="s">
-        <v>199</v>
-      </c>
-      <c r="I31" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="J31" s="23" t="s">
-        <v>77</v>
+      <c r="H48" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="I48" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J48" s="26" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J3" xr:uid="{250EDC6E-E94E-4F86-8F32-37B842AD2DF0}"/>
-  <mergeCells count="9">
+  <autoFilter ref="A3:J3" xr:uid="{9FFE2CA6-D3DA-485A-94DF-C742C9CBCAEF}"/>
+  <mergeCells count="26">
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A40:J40"/>
+    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A44:J44"/>
     <mergeCell ref="A26:J26"/>
     <mergeCell ref="A28:J28"/>
     <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A16:J16"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="A23:J23"/>
+    <mergeCell ref="A25:J25"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A15:J15"/>
-    <mergeCell ref="A17:J17"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="A12:J12"/>
+    <mergeCell ref="A14:J14"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.3888888888888889" bottom="0.3888888888888889" header="0.16666666666666666" footer="0.16666666666666666"/>
@@ -3745,7 +4336,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FFF9A64-935F-4A21-8AD2-3F360791801C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EEB9EF5-56FF-44A6-8565-A2144B13FAEF}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -3760,18 +4351,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
+      <c r="A1" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
     </row>
     <row r="2" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="33" t="s">
-        <v>210</v>
+      <c r="A2" s="35" t="s">
+        <v>232</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3789,226 +4380,226 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>211</v>
+        <v>233</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>212</v>
+        <v>234</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>213</v>
+        <v>235</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>214</v>
+        <v>236</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>215</v>
+        <v>237</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>216</v>
+        <v>238</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
-        <v>217</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>218</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>219</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>220</v>
-      </c>
-      <c r="E5" s="19" t="s">
-        <v>221</v>
-      </c>
-      <c r="F5" s="19" t="s">
-        <v>222</v>
+      <c r="A5" s="36" t="s">
+        <v>239</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>240</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>242</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="35" t="s">
-        <v>223</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>224</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>228</v>
+      <c r="A6" s="37" t="s">
+        <v>245</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>247</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>248</v>
+      </c>
+      <c r="E6" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="34" t="s">
-        <v>229</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>230</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>231</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>232</v>
-      </c>
-      <c r="E7" s="19" t="s">
-        <v>233</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>234</v>
+      <c r="A7" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="35" t="s">
-        <v>235</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>237</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>239</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>240</v>
+      <c r="A8" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>258</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>259</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>260</v>
+      </c>
+      <c r="E8" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="B9" s="19" t="s">
-        <v>242</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>243</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>244</v>
-      </c>
-      <c r="E9" s="19" t="s">
-        <v>245</v>
-      </c>
-      <c r="F9" s="19" t="s">
-        <v>246</v>
+      <c r="A9" s="36" t="s">
+        <v>263</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>266</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>252</v>
+      <c r="A10" s="37" t="s">
+        <v>269</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>271</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>274</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="34" t="s">
-        <v>253</v>
-      </c>
-      <c r="B11" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>255</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>256</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>257</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>258</v>
+      <c r="A11" s="36" t="s">
+        <v>275</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>278</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>279</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="35" t="s">
-        <v>259</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>262</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>263</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>264</v>
+      <c r="A12" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>282</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>283</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>284</v>
+      </c>
+      <c r="E12" s="27" t="s">
+        <v>285</v>
+      </c>
+      <c r="F12" s="27" t="s">
+        <v>286</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="34" t="s">
-        <v>265</v>
-      </c>
-      <c r="B13" s="19" t="s">
-        <v>266</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>267</v>
-      </c>
-      <c r="D13" s="19" t="s">
-        <v>268</v>
-      </c>
-      <c r="E13" s="19" t="s">
-        <v>269</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>270</v>
+      <c r="A13" s="36" t="s">
+        <v>287</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="E13" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>292</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="35" t="s">
-        <v>271</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>272</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>273</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>274</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>275</v>
+      <c r="A14" s="37" t="s">
+        <v>293</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>294</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>295</v>
+      </c>
+      <c r="E14" s="27" t="s">
+        <v>296</v>
+      </c>
+      <c r="F14" s="27" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F4" xr:uid="{1FFF9A64-935F-4A21-8AD2-3F360791801C}"/>
+  <autoFilter ref="A4:F4" xr:uid="{2EEB9EF5-56FF-44A6-8565-A2144B13FAEF}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
@@ -4023,7 +4614,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{200C1E46-2E30-4595-ACDC-25B7C7121560}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFFD21DB-3329-4B9A-B657-AF9188DBEA70}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4036,11 +4627,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
+      <c r="A1" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -4049,133 +4640,133 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="34" t="s">
-        <v>280</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>281</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>282</v>
+      <c r="A4" s="36" t="s">
+        <v>302</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="35" t="s">
-        <v>283</v>
-      </c>
-      <c r="B5" s="25" t="s">
-        <v>284</v>
-      </c>
-      <c r="C5" s="25" t="s">
-        <v>285</v>
+      <c r="A5" s="37" t="s">
+        <v>305</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>306</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>307</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="34" t="s">
-        <v>286</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>288</v>
+      <c r="A6" s="36" t="s">
+        <v>308</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>309</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="35" t="s">
-        <v>289</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>290</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>291</v>
+      <c r="A7" s="37" t="s">
+        <v>311</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="34" t="s">
-        <v>292</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>294</v>
+      <c r="A8" s="36" t="s">
+        <v>314</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="35" t="s">
-        <v>295</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>296</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>297</v>
+      <c r="A9" s="37" t="s">
+        <v>317</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>318</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="34" t="s">
-        <v>298</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>300</v>
+      <c r="A10" s="36" t="s">
+        <v>320</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>321</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>322</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="35" t="s">
-        <v>301</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>303</v>
+      <c r="A11" s="37" t="s">
+        <v>323</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>324</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="34" t="s">
-        <v>304</v>
-      </c>
-      <c r="B12" s="20" t="s">
-        <v>305</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>306</v>
+      <c r="A12" s="36" t="s">
+        <v>326</v>
+      </c>
+      <c r="B12" s="23" t="s">
+        <v>327</v>
+      </c>
+      <c r="C12" s="23" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="35" t="s">
-        <v>307</v>
-      </c>
-      <c r="B13" s="25" t="s">
-        <v>308</v>
-      </c>
-      <c r="C13" s="25" t="s">
+      <c r="A13" s="37" t="s">
+        <v>329</v>
+      </c>
+      <c r="B13" s="28" t="s">
+        <v>330</v>
+      </c>
+      <c r="C13" s="28" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="34" t="s">
-        <v>309</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>310</v>
-      </c>
-      <c r="C14" s="20" t="s">
+      <c r="A14" s="36" t="s">
+        <v>331</v>
+      </c>
+      <c r="B14" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="C14" s="23" t="s">
         <v>21</v>
       </c>
     </row>
@@ -4193,7 +4784,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06524582-77F1-4ADA-99B8-0D5211B3FFCC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DD02C2-8071-45FB-B5A3-8D3D6A17898B}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4205,11 +4796,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="32" t="s">
-        <v>311</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
+      <c r="A1" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
@@ -4218,101 +4809,101 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>312</v>
+        <v>334</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="20" t="s">
-        <v>315</v>
-      </c>
-      <c r="B4" s="20" t="s">
-        <v>316</v>
-      </c>
-      <c r="C4" s="20" t="s">
-        <v>317</v>
+      <c r="A4" s="23" t="s">
+        <v>337</v>
+      </c>
+      <c r="B4" s="23" t="s">
+        <v>338</v>
+      </c>
+      <c r="C4" s="23" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
-        <v>318</v>
-      </c>
-      <c r="B5" s="25" t="s">
+      <c r="A5" s="28" t="s">
+        <v>340</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>341</v>
+      </c>
+      <c r="C5" s="28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="23" t="s">
+        <v>342</v>
+      </c>
+      <c r="B6" s="23" t="s">
+        <v>343</v>
+      </c>
+      <c r="C6" s="23" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="B7" s="28" t="s">
+        <v>345</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="23" t="s">
+        <v>346</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>347</v>
+      </c>
+      <c r="C8" s="23" t="s">
         <v>319</v>
       </c>
-      <c r="C5" s="25" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="20" t="s">
-        <v>320</v>
-      </c>
-      <c r="B6" s="20" t="s">
-        <v>321</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25" t="s">
-        <v>322</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>323</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="20" t="s">
-        <v>324</v>
-      </c>
-      <c r="B8" s="20" t="s">
-        <v>325</v>
-      </c>
-      <c r="C8" s="20" t="s">
-        <v>297</v>
-      </c>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25" t="s">
-        <v>326</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>327</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>328</v>
+      <c r="A9" s="28" t="s">
+        <v>348</v>
+      </c>
+      <c r="B9" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="20" t="s">
-        <v>329</v>
-      </c>
-      <c r="B10" s="20" t="s">
-        <v>330</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>331</v>
+      <c r="A10" s="23" t="s">
+        <v>351</v>
+      </c>
+      <c r="B10" s="23" t="s">
+        <v>352</v>
+      </c>
+      <c r="C10" s="23" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="25" t="s">
-        <v>332</v>
-      </c>
-      <c r="B11" s="25" t="s">
-        <v>333</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>334</v>
+      <c r="A11" s="28" t="s">
+        <v>354</v>
+      </c>
+      <c r="B11" s="28" t="s">
+        <v>355</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -4321,8 +4912,8 @@
       <c r="C12" s="1"/>
     </row>
     <row r="13" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="33" t="s">
-        <v>335</v>
+      <c r="A13" s="35" t="s">
+        <v>357</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>

--- a/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
+++ b/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BB7C38C8-D647-4991-8E7B-DAEF6D84EF24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C830A778-63DA-4FF1-8D49-0D1CF2DAC398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{4CD67DC2-9D93-409A-ABE6-75A034E1D9DE}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{5F095F53-5FD8-4B1D-85CA-5DA550ACD957}"/>
   </bookViews>
   <sheets>
     <sheet name="Mode d'emploi" sheetId="1" r:id="rId1"/>
@@ -22,12 +22,12 @@
     <sheet name="Depannage niveau 1" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Espace central d''echange'!$A$4:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Espace central d''echange'!$A$4:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Jobs et cycles'!$A$3:$J$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Jobs par type de traitement'!$A$3:$J$3</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Checklist quotidienne'!$A$1:$C$9</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Depannage niveau 1'!$A$1:$C$13</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Espace central d''echange'!$A$1:$F$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Espace central d''echange'!$A$1:$G$14</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Glossaire Control-M'!$A$1:$C$14</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Jobs et cycles'!$A$1:$J$50</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Jobs par type de traitement'!$A$1:$J$48</definedName>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="639" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="368">
   <si>
     <t>Dossier d'exploitation quotidien - ERP_CRM_FACTORY</t>
   </si>
@@ -747,10 +747,10 @@
     <t xml:space="preserve">   Systeme - 1 traitement</t>
   </si>
   <si>
-    <t>Espace central d'echange ($OPERATIONS_DIR) - meme logique qu'un espace SM2/ADI bancaire (RCV/SND/ARC)</t>
-  </si>
-  <si>
-    <t>Chaque module a EXACTEMENT 4 sous-dossiers, toujours les memes noms : rcv (fichiers RECUS, a traiter), snd (fichiers PRODUITS par les traitements - c'est ici qu'on va chercher les rapports), tmp (transit technique - ne jamais y toucher), arc (archive - fichiers deja traites, ranges automatiquement).</t>
+    <t>Espace central d'echange ($OPERATIONS_DIR) - meme logique qu'un espace SM2/ADI bancaire (RCV/SND/TMP/ARC)</t>
+  </si>
+  <si>
+    <t>Chaque module a EXACTEMENT 4 sous-dossiers, toujours les memes noms : rcv (fichiers RECUS, a traiter), snd (fichiers PRODUITS par les traitements - c'est ici qu'on va chercher les rapports), tmp (transit technique - ne jamais y toucher), arc (archive - fichiers deja traites, ranges automatiquement). Ces 4 roles sont des variables reelles dans vars.conf (DOSSIER_RECU/DOSSIER_PRODUIT/DOSSIER_TRANSIT/DOSSIER_ARCHIVE) - jamais un litteral recopie a la main dans un job.</t>
   </si>
   <si>
     <t>Code module</t>
@@ -765,6 +765,9 @@
     <t>Dossier PRODUIT (snd)</t>
   </si>
   <si>
+    <t>Dossier TRANSIT (tmp)</t>
+  </si>
+  <si>
     <t>Dossier ARCHIVE (arc)</t>
   </si>
   <si>
@@ -783,6 +786,9 @@
     <t>$OPERATIONS_DIR/vt/snd</t>
   </si>
   <si>
+    <t>$OPERATIONS_DIR/vt/tmp</t>
+  </si>
+  <si>
     <t>$OPERATIONS_DIR/vt/arc</t>
   </si>
   <si>
@@ -801,6 +807,9 @@
     <t>$OPERATIONS_DIR/cp/snd</t>
   </si>
   <si>
+    <t>$OPERATIONS_DIR/cp/tmp</t>
+  </si>
+  <si>
     <t>$OPERATIONS_DIR/cp/arc</t>
   </si>
   <si>
@@ -819,6 +828,9 @@
     <t>$OPERATIONS_DIR/cr/snd</t>
   </si>
   <si>
+    <t>$OPERATIONS_DIR/cr/tmp</t>
+  </si>
+  <si>
     <t>$OPERATIONS_DIR/cr/arc</t>
   </si>
   <si>
@@ -837,6 +849,9 @@
     <t>$OPERATIONS_DIR/ah/snd</t>
   </si>
   <si>
+    <t>$OPERATIONS_DIR/ah/tmp</t>
+  </si>
+  <si>
     <t>$OPERATIONS_DIR/ah/arc</t>
   </si>
   <si>
@@ -855,6 +870,9 @@
     <t>$OPERATIONS_DIR/st/snd</t>
   </si>
   <si>
+    <t>$OPERATIONS_DIR/st/tmp</t>
+  </si>
+  <si>
     <t>$OPERATIONS_DIR/st/arc</t>
   </si>
   <si>
@@ -873,6 +891,9 @@
     <t>$OPERATIONS_DIR/ps/snd</t>
   </si>
   <si>
+    <t>$OPERATIONS_DIR/ps/tmp</t>
+  </si>
+  <si>
     <t>$OPERATIONS_DIR/ps/arc</t>
   </si>
   <si>
@@ -891,6 +912,9 @@
     <t>$OPERATIONS_DIR/rh/snd</t>
   </si>
   <si>
+    <t>$OPERATIONS_DIR/rh/tmp</t>
+  </si>
+  <si>
     <t>$OPERATIONS_DIR/rh/arc</t>
   </si>
   <si>
@@ -909,6 +933,9 @@
     <t>$OPERATIONS_DIR/pn/snd</t>
   </si>
   <si>
+    <t>$OPERATIONS_DIR/pn/tmp</t>
+  </si>
+  <si>
     <t>$OPERATIONS_DIR/pn/arc</t>
   </si>
   <si>
@@ -925,6 +952,9 @@
   </si>
   <si>
     <t>$OPERATIONS_DIR/pj/snd</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/pj/tmp</t>
   </si>
   <si>
     <t>$OPERATIONS_DIR/pj/arc</t>
@@ -1721,7 +1751,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8D7A0E5-C8B0-4260-92CA-775086BDB445}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F997462E-C81E-4604-93DB-3C47C770A609}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -1976,7 +2006,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB60D2D4-AE02-4080-9135-15EDA9DF677B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DE335C6-C1E2-4B9E-A853-E328C392A8E3}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2090,7 +2120,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0323787E-4EA4-4E4D-B29D-D748291388E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA89D5E1-262B-4155-80FC-CE4FFF85BC4A}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -3187,7 +3217,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J3" xr:uid="{0323787E-4EA4-4E4D-B29D-D748291388E3}"/>
+  <autoFilter ref="A3:J3" xr:uid="{FA89D5E1-262B-4155-80FC-CE4FFF85BC4A}"/>
   <mergeCells count="28">
     <mergeCell ref="A45:J45"/>
     <mergeCell ref="A46:J46"/>
@@ -3228,7 +3258,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FFE2CA6-D3DA-485A-94DF-C742C9CBCAEF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D1D78E-A5D8-4506-B76F-259AE304FAD6}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -4297,7 +4327,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J3" xr:uid="{9FFE2CA6-D3DA-485A-94DF-C742C9CBCAEF}"/>
+  <autoFilter ref="A3:J3" xr:uid="{E2D1D78E-A5D8-4506-B76F-259AE304FAD6}"/>
   <mergeCells count="26">
     <mergeCell ref="A46:J46"/>
     <mergeCell ref="A47:J47"/>
@@ -4336,21 +4366,21 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EEB9EF5-56FF-44A6-8565-A2144B13FAEF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AE26777-ED2E-4BF7-8B7C-C8D146414D52}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
     <col min="2" max="2" width="20.77734375" customWidth="1"/>
-    <col min="3" max="4" width="28.77734375" customWidth="1"/>
-    <col min="5" max="5" width="32.77734375" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" customWidth="1"/>
+    <col min="3" max="5" width="28.77734375" customWidth="1"/>
+    <col min="6" max="6" width="32.77734375" customWidth="1"/>
+    <col min="7" max="7" width="40.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
         <v>231</v>
       </c>
@@ -4359,8 +4389,9 @@
       <c r="D1" s="33"/>
       <c r="E1" s="33"/>
       <c r="F1" s="33"/>
-    </row>
-    <row r="2" spans="1:6" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G1" s="33"/>
+    </row>
+    <row r="2" spans="1:7" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="35" t="s">
         <v>232</v>
       </c>
@@ -4369,16 +4400,18 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G2" s="2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="1"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
         <v>233</v>
       </c>
@@ -4397,216 +4430,249 @@
       <c r="F4" s="15" t="s">
         <v>238</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="15" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="36" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="37" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="36" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+        <v>259</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="37" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="36" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>273</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="37" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>280</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="36" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>287</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="37" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>294</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="36" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>301</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="37" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>297</v>
+        <v>306</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:F4" xr:uid="{2EEB9EF5-56FF-44A6-8565-A2144B13FAEF}"/>
+  <autoFilter ref="A4:G4" xr:uid="{3AE26777-ED2E-4BF7-8B7C-C8D146414D52}"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.30555555555555558" right="0.30555555555555558" top="0.3888888888888889" bottom="0.3888888888888889" header="0.16666666666666666" footer="0.16666666666666666"/>
-  <pageSetup paperSize="9" scale="84" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="72" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;LERP_CRM_FACTORY - Dossier d'exploitation quotidien&amp;RPage &amp;P / &amp;N</oddFooter>
   </headerFooter>
@@ -4614,7 +4680,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFFD21DB-3329-4B9A-B657-AF9188DBEA70}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C6719FA-186E-473F-AA2D-A47A5225302C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4628,7 +4694,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -4640,120 +4706,120 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="36" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="37" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="36" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="37" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="36" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="37" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="36" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="37" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="36" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="37" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C13" s="28" t="s">
         <v>24</v>
@@ -4761,10 +4827,10 @@
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="36" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="C14" s="23" t="s">
         <v>21</v>
@@ -4784,7 +4850,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DD02C2-8071-45FB-B5A3-8D3D6A17898B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5345DFC6-3946-46A0-9538-73D9EFE38E84}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4797,7 +4863,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -4809,32 +4875,32 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="28" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="C5" s="28" t="s">
         <v>24</v>
@@ -4842,10 +4908,10 @@
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="C6" s="23" t="s">
         <v>18</v>
@@ -4853,10 +4919,10 @@
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="28" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>21</v>
@@ -4864,46 +4930,46 @@
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="28" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -4913,7 +4979,7 @@
     </row>
     <row r="13" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="35" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>

--- a/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
+++ b/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C830A778-63DA-4FF1-8D49-0D1CF2DAC398}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E790EFA-9655-410E-9196-A74AAB69829A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{5F095F53-5FD8-4B1D-85CA-5DA550ACD957}"/>
+    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{E041A09E-B47F-4181-9BFC-06F97AE019C5}"/>
   </bookViews>
   <sheets>
     <sheet name="Mode d'emploi" sheetId="1" r:id="rId1"/>
@@ -29,8 +29,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Depannage niveau 1'!$A$1:$C$13</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Espace central d''echange'!$A$1:$G$14</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Glossaire Control-M'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Jobs et cycles'!$A$1:$J$50</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Jobs par type de traitement'!$A$1:$J$48</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Jobs et cycles'!$A$1:$J$75</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Jobs par type de traitement'!$A$1:$J$73</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Mode d''emploi'!$A$1:$D$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="450">
   <si>
     <t>Dossier d'exploitation quotidien - ERP_CRM_FACTORY</t>
   </si>
@@ -504,7 +504,64 @@
     <t>Automatique - minuteur dedie 15h</t>
   </si>
   <si>
-    <t>CRM - 1 traitement(s) (deplier pour voir le detail)</t>
+    <t>CRM - 3 traitement(s) (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   EOW - 1 traitement</t>
+  </si>
+  <si>
+    <t>ECFCCLOCR1</t>
+  </si>
+  <si>
+    <t>Bilan hebdomadaire du pipeline (CRM)</t>
+  </si>
+  <si>
+    <t>EOW</t>
+  </si>
+  <si>
+    <t>Le samedi</t>
+  </si>
+  <si>
+    <t>Bilan hebdo pipeline : nouvelles pistes - gagnees/perdues - valeur du pipeline</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cr/snd/pipeline_hebdomadaire_AAAAMMJJ.txt</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCLOCR1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCLOCR1 "raison"</t>
+  </si>
+  <si>
+    <t>Automatique - fenetre calendaire hebdomadaire (samedi)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   NRT - 1 traitement</t>
+  </si>
+  <si>
+    <t>ECFJSCORCR1</t>
+  </si>
+  <si>
+    <t>Score de qualification (CRM)</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>Toutes les 15 min - en continu</t>
+  </si>
+  <si>
+    <t>Calcule un score 0-3 sur les pistes actives et met a jour leur priorite</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cr/snd/score_qualification_AAAAMMJJ_HHMM.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFJSCORCR1</t>
+  </si>
+  <si>
+    <t>Automatique - repetitif toutes les 15 min (continu)</t>
   </si>
   <si>
     <t>ECFCRELCR1</t>
@@ -546,21 +603,12 @@
     <t>./bin/rerun_job.sh ECFCSTIN1 "raison"</t>
   </si>
   <si>
-    <t xml:space="preserve">   NRT - 1 traitement</t>
-  </si>
-  <si>
     <t>ECFJALRST1</t>
   </si>
   <si>
     <t>Alerte rupture de stock</t>
   </si>
   <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>Toutes les 15 min - en continu</t>
-  </si>
-  <si>
     <t>Alerte des qu'un produit tombe a zero de stock</t>
   </si>
   <si>
@@ -570,10 +618,25 @@
     <t>./bin/view_history.sh ECFJALRST1</t>
   </si>
   <si>
-    <t>Automatique - repetitif toutes les 15 min (continu)</t>
-  </si>
-  <si>
-    <t>Point de vente - 1 traitement(s) (deplier pour voir le detail)</t>
+    <t>Point de vente - 2 traitement(s) (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>ECFCCLOPS2</t>
+  </si>
+  <si>
+    <t>Bilan mensuel des ventes par PDV</t>
+  </si>
+  <si>
+    <t>Bilan mensuel ventes regroupees par point de vente</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/ps/snd/rapport_ventes_mensuel_AAAAMM.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCLOPS2</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCLOPS2 "raison"</t>
   </si>
   <si>
     <t>ECFCCLOPS1</t>
@@ -594,7 +657,55 @@
     <t>./bin/rerun_job.sh ECFCCLOPS1 "raison"</t>
   </si>
   <si>
-    <t>RH - 1 traitement(s) (deplier pour voir le detail)</t>
+    <t>RH - 3 traitement(s) (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   EOY - 1 traitement</t>
+  </si>
+  <si>
+    <t>ECFCCLORH2</t>
+  </si>
+  <si>
+    <t>Bilan social annuel (RH)</t>
+  </si>
+  <si>
+    <t>EOY</t>
+  </si>
+  <si>
+    <t>Le 1er janvier</t>
+  </si>
+  <si>
+    <t>Bilan RH complet de l'annee ecoulee</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/rh/snd/bilan_social_AAAA.txt</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCLORH2</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCLORH2 "raison"</t>
+  </si>
+  <si>
+    <t>Automatique - fenetre calendaire annuelle (1er janvier)</t>
+  </si>
+  <si>
+    <t>ECFCCLORH1</t>
+  </si>
+  <si>
+    <t>Effectifs et anciennete (RH)</t>
+  </si>
+  <si>
+    <t>Photographie mensuelle des effectifs actifs</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/rh/snd/effectifs_anciennete_AAAAMM.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCLORH1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCLORH1 "raison"</t>
   </si>
   <si>
     <t>ECFCALRRH1</t>
@@ -684,10 +795,127 @@
     <t>./bin/rerun_job.sh ECFCPRG1 "raison"</t>
   </si>
   <si>
+    <t>Reparation - 2 traitement(s) (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>ECFCCLORP1</t>
+  </si>
+  <si>
+    <t>Rapport quotidien SAV (Reparation)</t>
+  </si>
+  <si>
+    <t>Point quotidien reparations en cours et terminees</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/rp/snd/rapport_sav_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCLORP1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCLORP1 "raison"</t>
+  </si>
+  <si>
+    <t>ECFJALRRP1</t>
+  </si>
+  <si>
+    <t>Notification avancement reparation</t>
+  </si>
+  <si>
+    <t>Previent le client des changements d'etape de sa reparation</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/rp/snd/notification_avancement_AAAAMMJJ_HHMM.csv (uniquement s'il y a du nouveau)</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFJALRRP1</t>
+  </si>
+  <si>
+    <t>Flotte vehicules - 2 traitement(s) (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>ECFCCLOFL1</t>
+  </si>
+  <si>
+    <t>Controle entretien mensuel (Flotte)</t>
+  </si>
+  <si>
+    <t>Verifie quels vehicules ont besoin d'entretien</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/fl/snd/controle_entretien_AAAAMM.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCLOFL1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCLOFL1 "raison"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   JOUR - 1 traitement</t>
+  </si>
+  <si>
+    <t>ECFCALRFL1</t>
+  </si>
+  <si>
+    <t>Alerte echeance assurance/CT (Flotte)</t>
+  </si>
+  <si>
+    <t>JOUR</t>
+  </si>
+  <si>
+    <t>Alerte avant expiration assurance/controle technique sous 30j</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/fl/snd/alerte_echeance_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCALRFL1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCALRFL1 "raison"</t>
+  </si>
+  <si>
+    <t>eCommerce - 2 traitement(s) (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>ECFJRELEC1</t>
+  </si>
+  <si>
+    <t>Relance paniers abandonnes (eCommerce)</t>
+  </si>
+  <si>
+    <t>Relance les clients avec panier inactif depuis plus de 4h</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/ec/snd/relance_paniers_AAAAMMJJ_HHMM.csv (uniquement si nouveau panier a relancer)</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFJRELEC1</t>
+  </si>
+  <si>
+    <t>ECFCCLOEC1</t>
+  </si>
+  <si>
+    <t>Bilan quotidien ventes en ligne (eCommerce)</t>
+  </si>
+  <si>
+    <t>Bilan quotidien ventes en ligne + paniers abandonnes</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/ec/snd/rapport_ventes_paniers_AAAAMMJJ.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCLOEC1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCLOEC1 "raison"</t>
+  </si>
+  <si>
     <t>Memes 20 traitements, groupes par type de traitement (TFJ/EOM/EOD/...) - pour repondre a 'combien de TFJ ce soir ?'</t>
   </si>
   <si>
-    <t>TFJ - 10 traitements (deplier pour voir le detail)</t>
+    <t>TFJ - 12 traitements (deplier pour voir le detail)</t>
   </si>
   <si>
     <t xml:space="preserve">   Ventes - 3 traitements</t>
@@ -696,39 +924,48 @@
     <t xml:space="preserve">   Comptabilite - 2 traitements</t>
   </si>
   <si>
+    <t xml:space="preserve">   RH - 1 traitement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Reparation - 1 traitement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   eCommerce - 1 traitement</t>
+  </si>
+  <si>
     <t xml:space="preserve">   Point de vente - 1 traitement</t>
   </si>
   <si>
-    <t xml:space="preserve">   RH - 1 traitement</t>
+    <t xml:space="preserve">   Achat - 1 traitement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   CRM - 1 traitement</t>
   </si>
   <si>
     <t xml:space="preserve">   Stock - 1 traitement</t>
   </si>
   <si>
-    <t xml:space="preserve">   Achat - 1 traitement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   CRM - 1 traitement</t>
-  </si>
-  <si>
-    <t>JOUR/NRT - 1 traitement (deplier pour voir le detail)</t>
+    <t>JOUR/NRT - 3 traitements (deplier pour voir le detail)</t>
   </si>
   <si>
     <t xml:space="preserve">   Ventes - 1 traitement</t>
   </si>
   <si>
-    <t>EOM - 4 traitements (deplier pour voir le detail)</t>
+    <t>EOM - 7 traitements (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Flotte vehicules - 1 traitement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Projets - 1 traitement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Comptabilite - 1 traitement</t>
   </si>
   <si>
     <t xml:space="preserve">   Presences - 1 traitement</t>
   </si>
   <si>
-    <t xml:space="preserve">   Projets - 1 traitement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">   Comptabilite - 1 traitement</t>
-  </si>
-  <si>
     <t>EOD - 1 traitement (deplier pour voir le detail)</t>
   </si>
   <si>
@@ -738,13 +975,22 @@
     <t>CUTOFF - 1 traitement (deplier pour voir le detail)</t>
   </si>
   <si>
-    <t>NRT - 1 traitement (deplier pour voir le detail)</t>
+    <t>NRT - 2 traitements (deplier pour voir le detail)</t>
   </si>
   <si>
     <t>PURGE - 1 traitement (deplier pour voir le detail)</t>
   </si>
   <si>
     <t xml:space="preserve">   Systeme - 1 traitement</t>
+  </si>
+  <si>
+    <t>EOW - 1 traitement (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>JOUR - 1 traitement (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>EOY - 1 traitement (deplier pour voir le detail)</t>
   </si>
   <si>
     <t>Espace central d'echange ($OPERATIONS_DIR) - meme logique qu'un espace SM2/ADI bancaire (RCV/SND/TMP/ARC)</t>
@@ -1751,7 +1997,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F997462E-C81E-4604-93DB-3C47C770A609}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5221FC86-28DB-407E-9D30-F735C2D16DE8}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2006,7 +2252,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DE335C6-C1E2-4B9E-A853-E328C392A8E3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B347097-CDBD-40D7-8709-33823CD79C10}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2120,12 +2366,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA89D5E1-262B-4155-80FC-CE4FFF85BC4A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19B72177-293A-429E-8666-97D11F8E143D}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J50"/>
+  <dimension ref="A1:J75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
@@ -2766,7 +3012,7 @@
     </row>
     <row r="29" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A29" s="21" t="s">
-        <v>132</v>
+        <v>151</v>
       </c>
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
@@ -2780,279 +3026,297 @@
     </row>
     <row r="30" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A30" s="24" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C30" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="F30" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="G30" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="H30" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="I30" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="J30" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+    </row>
+    <row r="32" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A32" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="B32" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="D32" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="G32" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="H32" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="I32" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="J32" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B33" s="19"/>
+      <c r="C33" s="19"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+    </row>
+    <row r="34" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A34" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="B34" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="D34" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="23" t="s">
-        <v>153</v>
-      </c>
-      <c r="F30" s="23" t="s">
-        <v>154</v>
-      </c>
-      <c r="G30" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="H30" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="I30" s="23" t="s">
+      <c r="E34" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="F34" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="G34" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="H34" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="I34" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J30" s="26" t="s">
+      <c r="J34" s="26" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="18" t="s">
-        <v>157</v>
-      </c>
-      <c r="B31" s="16"/>
-      <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="17"/>
-      <c r="G31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
-      <c r="J31" s="17"/>
-    </row>
-    <row r="32" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="21" t="s">
+    <row r="35" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="B35" s="16"/>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="17"/>
+      <c r="F35" s="17"/>
+      <c r="G35" s="17"/>
+      <c r="H35" s="17"/>
+      <c r="I35" s="17"/>
+      <c r="J35" s="17"/>
+    </row>
+    <row r="36" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-    </row>
-    <row r="33" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A33" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>159</v>
-      </c>
-      <c r="C33" s="25" t="s">
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+    </row>
+    <row r="37" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A37" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B37" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="C37" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="D37" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="E33" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="F33" s="23" t="s">
+      <c r="E37" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="F37" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="G37" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="H37" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="I37" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J37" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="G33" s="23" t="s">
-        <v>162</v>
-      </c>
-      <c r="H33" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="I33" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J33" s="26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="21" t="s">
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+    </row>
+    <row r="39" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A39" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="B39" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="C39" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="20"/>
-      <c r="F34" s="20"/>
-      <c r="G34" s="20"/>
-      <c r="H34" s="20"/>
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-    </row>
-    <row r="35" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A35" s="24" t="s">
+      <c r="D39" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="B35" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="C35" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="D35" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="E35" s="23" t="s">
+      <c r="E39" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="F39" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="G39" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="H39" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="I39" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="F35" s="23" t="s">
-        <v>170</v>
-      </c>
-      <c r="G35" s="23" t="s">
-        <v>171</v>
-      </c>
-      <c r="H35" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="I35" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="J35" s="26" t="s">
+      <c r="J39" s="26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="18" t="s">
-        <v>173</v>
-      </c>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
-    </row>
-    <row r="37" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B37" s="19"/>
-      <c r="C37" s="19"/>
-      <c r="D37" s="19"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-    </row>
-    <row r="38" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A38" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="B38" s="22" t="s">
-        <v>175</v>
-      </c>
-      <c r="C38" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D38" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="E38" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="F38" s="23" t="s">
-        <v>177</v>
-      </c>
-      <c r="G38" s="23" t="s">
-        <v>178</v>
-      </c>
-      <c r="H38" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="I38" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J38" s="26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="18" t="s">
-        <v>180</v>
-      </c>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="17"/>
-      <c r="F39" s="17"/>
-      <c r="G39" s="17"/>
-      <c r="H39" s="17"/>
-      <c r="I39" s="17"/>
-      <c r="J39" s="17"/>
-    </row>
-    <row r="40" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="20"/>
-      <c r="F40" s="20"/>
-      <c r="G40" s="20"/>
-      <c r="H40" s="20"/>
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-    </row>
-    <row r="41" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A41" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="B41" s="22" t="s">
-        <v>182</v>
-      </c>
-      <c r="C41" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="E41" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="F41" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="G41" s="23" t="s">
-        <v>185</v>
-      </c>
-      <c r="H41" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="I41" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J41" s="26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="D42" s="16"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="17"/>
-      <c r="G42" s="17"/>
-      <c r="H42" s="17"/>
-      <c r="I42" s="17"/>
-      <c r="J42" s="17"/>
+    <row r="40" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="18" t="s">
+        <v>188</v>
+      </c>
+      <c r="B40" s="16"/>
+      <c r="C40" s="16"/>
+      <c r="D40" s="16"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
+      <c r="H40" s="17"/>
+      <c r="I40" s="17"/>
+      <c r="J40" s="17"/>
+    </row>
+    <row r="41" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+    </row>
+    <row r="42" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A42" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="B42" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D42" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E42" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="F42" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="G42" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="H42" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="I42" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J42" s="26" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="43" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A43" s="21" t="s">
-        <v>69</v>
+        <v>132</v>
       </c>
       <c r="B43" s="19"/>
       <c r="C43" s="19"/>
@@ -3066,39 +3330,39 @@
     </row>
     <row r="44" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A44" s="24" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B44" s="22" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="C44" s="25" t="s">
-        <v>72</v>
+        <v>46</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="G44" s="23" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="I44" s="23" t="s">
-        <v>78</v>
+        <v>52</v>
       </c>
       <c r="J44" s="26" t="s">
-        <v>79</v>
+        <v>139</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="18" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B45" s="16"/>
       <c r="C45" s="16"/>
@@ -3112,7 +3376,7 @@
     </row>
     <row r="46" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A46" s="21" t="s">
-        <v>69</v>
+        <v>202</v>
       </c>
       <c r="B46" s="19"/>
       <c r="C46" s="19"/>
@@ -3126,115 +3390,659 @@
     </row>
     <row r="47" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A47" s="24" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>72</v>
+        <v>205</v>
       </c>
       <c r="D47" s="22" t="s">
-        <v>73</v>
+        <v>206</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="I47" s="23" t="s">
-        <v>78</v>
+        <v>211</v>
       </c>
       <c r="J47" s="26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="17"/>
-      <c r="J48" s="17"/>
-    </row>
-    <row r="49" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="20"/>
-      <c r="J49" s="20"/>
-    </row>
-    <row r="50" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A50" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="B50" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="D50" s="22" t="s">
+    <row r="48" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B48" s="19"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+    </row>
+    <row r="49" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A49" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="B49" s="22" t="s">
+        <v>213</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D49" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="E50" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="F50" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="G50" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="H50" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="I50" s="23" t="s">
+      <c r="E49" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="F49" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="G49" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="H49" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="I49" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="J50" s="26" t="s">
+      <c r="J49" s="26" t="s">
         <v>79</v>
       </c>
     </row>
+    <row r="50" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="20"/>
+      <c r="F50" s="20"/>
+      <c r="G50" s="20"/>
+      <c r="H50" s="20"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
+    </row>
+    <row r="51" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A51" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="B51" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D51" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="F51" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="G51" s="23" t="s">
+        <v>222</v>
+      </c>
+      <c r="H51" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="I51" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J51" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="18" t="s">
+        <v>224</v>
+      </c>
+      <c r="B52" s="16"/>
+      <c r="C52" s="16"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+      <c r="J52" s="17"/>
+    </row>
+    <row r="53" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B53" s="19"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="20"/>
+      <c r="F53" s="20"/>
+      <c r="G53" s="20"/>
+      <c r="H53" s="20"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="20"/>
+    </row>
+    <row r="54" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A54" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="B54" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="C54" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D54" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="F54" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="G54" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="H54" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="I54" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J54" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="B55" s="16"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="17"/>
+      <c r="F55" s="17"/>
+      <c r="G55" s="17"/>
+      <c r="H55" s="17"/>
+      <c r="I55" s="17"/>
+      <c r="J55" s="17"/>
+    </row>
+    <row r="56" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B56" s="19"/>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="20"/>
+      <c r="F56" s="20"/>
+      <c r="G56" s="20"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="20"/>
+      <c r="J56" s="20"/>
+    </row>
+    <row r="57" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A57" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="B57" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="C57" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D57" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="F57" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="G57" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="H57" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="I57" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J57" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="18" t="s">
+        <v>238</v>
+      </c>
+      <c r="B58" s="16"/>
+      <c r="C58" s="16"/>
+      <c r="D58" s="16"/>
+      <c r="E58" s="17"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="17"/>
+    </row>
+    <row r="59" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="B59" s="19"/>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="20"/>
+      <c r="F59" s="20"/>
+      <c r="G59" s="20"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="20"/>
+      <c r="J59" s="20"/>
+    </row>
+    <row r="60" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A60" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="B60" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="C60" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="D60" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E60" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="F60" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="G60" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="H60" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="I60" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J60" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="18" t="s">
+        <v>247</v>
+      </c>
+      <c r="B61" s="16"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="17"/>
+      <c r="F61" s="17"/>
+      <c r="G61" s="17"/>
+      <c r="H61" s="17"/>
+      <c r="I61" s="17"/>
+      <c r="J61" s="17"/>
+    </row>
+    <row r="62" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B62" s="19"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+    </row>
+    <row r="63" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A63" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="B63" s="22" t="s">
+        <v>249</v>
+      </c>
+      <c r="C63" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D63" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E63" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="F63" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="G63" s="23" t="s">
+        <v>252</v>
+      </c>
+      <c r="H63" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="I63" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J63" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B64" s="19"/>
+      <c r="C64" s="19"/>
+      <c r="D64" s="19"/>
+      <c r="E64" s="20"/>
+      <c r="F64" s="20"/>
+      <c r="G64" s="20"/>
+      <c r="H64" s="20"/>
+      <c r="I64" s="20"/>
+      <c r="J64" s="20"/>
+    </row>
+    <row r="65" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A65" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="B65" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="C65" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D65" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="E65" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="F65" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="G65" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="H65" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="I65" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="J65" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="B66" s="16"/>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="17"/>
+      <c r="F66" s="17"/>
+      <c r="G66" s="17"/>
+      <c r="H66" s="17"/>
+      <c r="I66" s="17"/>
+      <c r="J66" s="17"/>
+    </row>
+    <row r="67" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B67" s="19"/>
+      <c r="C67" s="19"/>
+      <c r="D67" s="19"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="20"/>
+      <c r="G67" s="20"/>
+      <c r="H67" s="20"/>
+      <c r="I67" s="20"/>
+      <c r="J67" s="20"/>
+    </row>
+    <row r="68" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A68" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="B68" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="C68" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D68" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E68" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="F68" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="G68" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="H68" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="I68" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J68" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="B69" s="19"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="20"/>
+      <c r="F69" s="20"/>
+      <c r="G69" s="20"/>
+      <c r="H69" s="20"/>
+      <c r="I69" s="20"/>
+      <c r="J69" s="20"/>
+    </row>
+    <row r="70" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A70" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="B70" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="D70" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E70" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="F70" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="G70" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="H70" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="I70" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J70" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="18" t="s">
+        <v>274</v>
+      </c>
+      <c r="B71" s="16"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="17"/>
+      <c r="F71" s="17"/>
+      <c r="G71" s="17"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="17"/>
+    </row>
+    <row r="72" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="21" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="19"/>
+      <c r="C72" s="19"/>
+      <c r="D72" s="19"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
+      <c r="H72" s="20"/>
+      <c r="I72" s="20"/>
+      <c r="J72" s="20"/>
+    </row>
+    <row r="73" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A73" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="B73" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="C73" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D73" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="E73" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="F73" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="G73" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="H73" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="I73" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="J73" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="B74" s="19"/>
+      <c r="C74" s="19"/>
+      <c r="D74" s="19"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="20"/>
+      <c r="G74" s="20"/>
+      <c r="H74" s="20"/>
+      <c r="I74" s="20"/>
+      <c r="J74" s="20"/>
+    </row>
+    <row r="75" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A75" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="B75" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D75" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E75" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="F75" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="G75" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="H75" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="I75" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J75" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:J3" xr:uid="{FA89D5E1-262B-4155-80FC-CE4FFF85BC4A}"/>
-  <mergeCells count="28">
-    <mergeCell ref="A45:J45"/>
+  <autoFilter ref="A3:J3" xr:uid="{19B72177-293A-429E-8666-97D11F8E143D}"/>
+  <mergeCells count="42">
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A67:J67"/>
+    <mergeCell ref="A69:J69"/>
+    <mergeCell ref="A71:J71"/>
+    <mergeCell ref="A72:J72"/>
+    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A56:J56"/>
+    <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A59:J59"/>
+    <mergeCell ref="A61:J61"/>
+    <mergeCell ref="A62:J62"/>
+    <mergeCell ref="A64:J64"/>
     <mergeCell ref="A46:J46"/>
     <mergeCell ref="A48:J48"/>
-    <mergeCell ref="A49:J49"/>
+    <mergeCell ref="A50:J50"/>
+    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A53:J53"/>
+    <mergeCell ref="A55:J55"/>
     <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A37:J37"/>
-    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A38:J38"/>
     <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A41:J41"/>
     <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A45:J45"/>
     <mergeCell ref="A26:J26"/>
     <mergeCell ref="A28:J28"/>
     <mergeCell ref="A29:J29"/>
     <mergeCell ref="A31:J31"/>
-    <mergeCell ref="A32:J32"/>
-    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A33:J33"/>
+    <mergeCell ref="A35:J35"/>
     <mergeCell ref="A14:J14"/>
     <mergeCell ref="A17:J17"/>
     <mergeCell ref="A19:J19"/>
@@ -3258,12 +4066,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2D1D78E-A5D8-4506-B76F-259AE304FAD6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BC65ED9-AB40-4CEB-B626-6A6F40CB9629}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J73"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
@@ -3280,7 +4088,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>210</v>
+        <v>286</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -3338,7 +4146,7 @@
     </row>
     <row r="4" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>211</v>
+        <v>287</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -3352,7 +4160,7 @@
     </row>
     <row r="5" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
-        <v>212</v>
+        <v>288</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
@@ -3462,7 +4270,7 @@
     </row>
     <row r="9" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A9" s="21" t="s">
-        <v>213</v>
+        <v>289</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
@@ -3540,7 +4348,7 @@
     </row>
     <row r="12" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A12" s="21" t="s">
-        <v>214</v>
+        <v>290</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -3554,10 +4362,10 @@
     </row>
     <row r="13" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A13" s="24" t="s">
-        <v>174</v>
+        <v>218</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>175</v>
+        <v>219</v>
       </c>
       <c r="C13" s="25" t="s">
         <v>46</v>
@@ -3566,16 +4374,16 @@
         <v>47</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>176</v>
+        <v>220</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>177</v>
+        <v>221</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>178</v>
+        <v>222</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>179</v>
+        <v>223</v>
       </c>
       <c r="I13" s="23" t="s">
         <v>52</v>
@@ -3586,7 +4394,7 @@
     </row>
     <row r="14" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
-        <v>215</v>
+        <v>291</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -3600,10 +4408,10 @@
     </row>
     <row r="15" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A15" s="24" t="s">
-        <v>181</v>
+        <v>248</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>182</v>
+        <v>249</v>
       </c>
       <c r="C15" s="25" t="s">
         <v>46</v>
@@ -3612,16 +4420,16 @@
         <v>47</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>183</v>
+        <v>250</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>184</v>
+        <v>251</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>185</v>
+        <v>252</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>186</v>
+        <v>253</v>
       </c>
       <c r="I15" s="23" t="s">
         <v>52</v>
@@ -3632,7 +4440,7 @@
     </row>
     <row r="16" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A16" s="21" t="s">
-        <v>216</v>
+        <v>292</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -3646,10 +4454,10 @@
     </row>
     <row r="17" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A17" s="24" t="s">
-        <v>158</v>
+        <v>280</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>159</v>
+        <v>281</v>
       </c>
       <c r="C17" s="25" t="s">
         <v>46</v>
@@ -3658,16 +4466,16 @@
         <v>47</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>160</v>
+        <v>282</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>161</v>
+        <v>283</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>162</v>
+        <v>284</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>163</v>
+        <v>285</v>
       </c>
       <c r="I17" s="23" t="s">
         <v>52</v>
@@ -3678,7 +4486,7 @@
     </row>
     <row r="18" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A18" s="21" t="s">
-        <v>217</v>
+        <v>293</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -3692,10 +4500,10 @@
     </row>
     <row r="19" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A19" s="24" t="s">
-        <v>133</v>
+        <v>195</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>134</v>
+        <v>196</v>
       </c>
       <c r="C19" s="25" t="s">
         <v>46</v>
@@ -3704,16 +4512,16 @@
         <v>47</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>135</v>
+        <v>197</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>136</v>
+        <v>198</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>137</v>
+        <v>199</v>
       </c>
       <c r="H19" s="23" t="s">
-        <v>138</v>
+        <v>200</v>
       </c>
       <c r="I19" s="23" t="s">
         <v>52</v>
@@ -3724,7 +4532,7 @@
     </row>
     <row r="20" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A20" s="21" t="s">
-        <v>218</v>
+        <v>294</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="19"/>
@@ -3738,10 +4546,10 @@
     </row>
     <row r="21" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="s">
-        <v>151</v>
+        <v>133</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="C21" s="25" t="s">
         <v>46</v>
@@ -3750,16 +4558,16 @@
         <v>47</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>153</v>
+        <v>135</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>156</v>
+        <v>138</v>
       </c>
       <c r="I21" s="23" t="s">
         <v>52</v>
@@ -3768,341 +4576,359 @@
         <v>139</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17"/>
-      <c r="G22" s="17"/>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
-    </row>
-    <row r="23" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="20"/>
-      <c r="F23" s="20"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-    </row>
-    <row r="24" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A24" s="24" t="s">
+    <row r="22" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="20"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="20"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+    </row>
+    <row r="23" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A23" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>171</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>172</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="I23" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J23" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+    </row>
+    <row r="25" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A25" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="G25" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>182</v>
+      </c>
+      <c r="I25" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J25" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="17"/>
+      <c r="F26" s="17"/>
+      <c r="G26" s="17"/>
+      <c r="H26" s="17"/>
+      <c r="I26" s="17"/>
+      <c r="J26" s="17"/>
+    </row>
+    <row r="27" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="20"/>
+      <c r="H27" s="20"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+    </row>
+    <row r="28" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A28" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="B28" s="22" t="s">
+        <v>276</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D28" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="E28" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="F28" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="G28" s="23" t="s">
+        <v>279</v>
+      </c>
+      <c r="H28" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="I28" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="J28" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+    </row>
+    <row r="30" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A30" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="B30" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="E30" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="F30" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="G30" s="23" t="s">
+        <v>258</v>
+      </c>
+      <c r="H30" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="I30" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="J30" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="19"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
+      <c r="G31" s="20"/>
+      <c r="H31" s="20"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+    </row>
+    <row r="32" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A32" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B32" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C32" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D32" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E32" s="23" t="s">
         <v>85</v>
       </c>
-      <c r="F24" s="23" t="s">
+      <c r="F32" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="G24" s="23" t="s">
+      <c r="G32" s="23" t="s">
         <v>87</v>
       </c>
-      <c r="H24" s="23" t="s">
+      <c r="H32" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="I24" s="23" t="s">
+      <c r="I32" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="J24" s="26" t="s">
+      <c r="J32" s="26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="18" t="s">
-        <v>221</v>
-      </c>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="17"/>
-      <c r="F25" s="17"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="17"/>
-      <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
-    </row>
-    <row r="26" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="21" t="s">
-        <v>222</v>
-      </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-    </row>
-    <row r="27" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A27" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="B27" s="22" t="s">
+    <row r="33" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="B33" s="16"/>
+      <c r="C33" s="16"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
+    </row>
+    <row r="34" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="B34" s="19"/>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+    </row>
+    <row r="35" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A35" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="B35" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>262</v>
+      </c>
+      <c r="F35" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="G35" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="H35" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="I35" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J35" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="21" t="s">
+        <v>293</v>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="19"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+    </row>
+    <row r="37" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A37" s="24" t="s">
         <v>189</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="B37" s="22" t="s">
+        <v>190</v>
+      </c>
+      <c r="C37" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="D27" s="22" t="s">
+      <c r="D37" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="E27" s="23" t="s">
-        <v>190</v>
-      </c>
-      <c r="F27" s="23" t="s">
+      <c r="E37" s="23" t="s">
         <v>191</v>
       </c>
-      <c r="G27" s="23" t="s">
+      <c r="F37" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="H27" s="23" t="s">
+      <c r="G37" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="I27" s="23" t="s">
+      <c r="H37" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="I37" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="J27" s="26" t="s">
+      <c r="J37" s="26" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="28" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="21" t="s">
-        <v>223</v>
-      </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
-      <c r="D28" s="19"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-    </row>
-    <row r="29" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A29" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="B29" s="22" t="s">
-        <v>196</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="D29" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="F29" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="G29" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="H29" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="I29" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="J29" s="26" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="20"/>
-      <c r="F30" s="20"/>
-      <c r="G30" s="20"/>
-      <c r="H30" s="20"/>
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-    </row>
-    <row r="31" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A31" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="E31" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="F31" s="23" t="s">
-        <v>75</v>
-      </c>
-      <c r="G31" s="23" t="s">
-        <v>76</v>
-      </c>
-      <c r="H31" s="23" t="s">
-        <v>77</v>
-      </c>
-      <c r="I31" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="J31" s="26" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
-      <c r="D32" s="19"/>
-      <c r="E32" s="20"/>
-      <c r="F32" s="20"/>
-      <c r="G32" s="20"/>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-    </row>
-    <row r="33" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A33" s="24" t="s">
-        <v>115</v>
-      </c>
-      <c r="B33" s="22" t="s">
-        <v>116</v>
-      </c>
-      <c r="C33" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="E33" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="F33" s="23" t="s">
-        <v>118</v>
-      </c>
-      <c r="G33" s="23" t="s">
-        <v>119</v>
-      </c>
-      <c r="H33" s="23" t="s">
-        <v>120</v>
-      </c>
-      <c r="I33" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="J33" s="26" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="17"/>
-      <c r="F34" s="17"/>
-      <c r="G34" s="17"/>
-      <c r="H34" s="17"/>
-      <c r="I34" s="17"/>
-      <c r="J34" s="17"/>
-    </row>
-    <row r="35" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="20"/>
-      <c r="F35" s="20"/>
-      <c r="G35" s="20"/>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-    </row>
-    <row r="36" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A36" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="B36" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>124</v>
-      </c>
-      <c r="D36" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="E36" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="F36" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="G36" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="H36" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="I36" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="J36" s="26" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="17"/>
-      <c r="F37" s="17"/>
-      <c r="G37" s="17"/>
-      <c r="H37" s="17"/>
-      <c r="I37" s="17"/>
-      <c r="J37" s="17"/>
     </row>
     <row r="38" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A38" s="21" t="s">
-        <v>224</v>
+        <v>290</v>
       </c>
       <c r="B38" s="19"/>
       <c r="C38" s="19"/>
@@ -4116,113 +4942,131 @@
     </row>
     <row r="39" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A39" s="24" t="s">
-        <v>106</v>
+        <v>212</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>107</v>
+        <v>213</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="D39" s="22" t="s">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>110</v>
+        <v>214</v>
       </c>
       <c r="F39" s="23" t="s">
-        <v>111</v>
+        <v>215</v>
       </c>
       <c r="G39" s="23" t="s">
-        <v>112</v>
+        <v>216</v>
       </c>
       <c r="H39" s="23" t="s">
-        <v>113</v>
+        <v>217</v>
       </c>
       <c r="I39" s="23" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="J39" s="26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="18" t="s">
-        <v>227</v>
-      </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-    </row>
-    <row r="41" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="21" t="s">
-        <v>217</v>
-      </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-    </row>
-    <row r="42" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A42" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="B42" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="D42" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E42" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="F42" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="G42" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="H42" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="I42" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="J42" s="26" t="s">
+    <row r="40" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+    </row>
+    <row r="41" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A41" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E41" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="F41" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="G41" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="H41" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="I41" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J41" s="26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="18" t="s">
-        <v>228</v>
-      </c>
-      <c r="B43" s="16"/>
-      <c r="C43" s="16"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="17"/>
-      <c r="G43" s="17"/>
-      <c r="H43" s="17"/>
-      <c r="I43" s="17"/>
-      <c r="J43" s="17"/>
+    <row r="42" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+    </row>
+    <row r="43" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A43" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D43" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E43" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="F43" s="23" t="s">
+        <v>75</v>
+      </c>
+      <c r="G43" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="H43" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="I43" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J43" s="26" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="44" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A44" s="21" t="s">
-        <v>216</v>
+        <v>302</v>
       </c>
       <c r="B44" s="19"/>
       <c r="C44" s="19"/>
@@ -4236,119 +5080,645 @@
     </row>
     <row r="45" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A45" s="24" t="s">
-        <v>165</v>
+        <v>115</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>166</v>
+        <v>116</v>
       </c>
       <c r="C45" s="25" t="s">
-        <v>167</v>
+        <v>72</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>168</v>
+        <v>73</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>169</v>
+        <v>117</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>170</v>
+        <v>118</v>
       </c>
       <c r="G45" s="23" t="s">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>88</v>
+        <v>120</v>
       </c>
       <c r="I45" s="23" t="s">
-        <v>172</v>
+        <v>78</v>
       </c>
       <c r="J45" s="26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="18" t="s">
+    <row r="46" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="B46" s="19"/>
+      <c r="C46" s="19"/>
+      <c r="D46" s="19"/>
+      <c r="E46" s="20"/>
+      <c r="F46" s="20"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="20"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+    </row>
+    <row r="47" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A47" s="24" t="s">
+        <v>225</v>
+      </c>
+      <c r="B47" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D47" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E47" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="F47" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="G47" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="B46" s="16"/>
-      <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="17"/>
-      <c r="F46" s="17"/>
-      <c r="G46" s="17"/>
-      <c r="H46" s="17"/>
-      <c r="I46" s="17"/>
-      <c r="J46" s="17"/>
-    </row>
-    <row r="47" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="21" t="s">
+      <c r="H47" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="B47" s="19"/>
-      <c r="C47" s="19"/>
-      <c r="D47" s="19"/>
-      <c r="E47" s="20"/>
-      <c r="F47" s="20"/>
-      <c r="G47" s="20"/>
-      <c r="H47" s="20"/>
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-    </row>
-    <row r="48" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A48" s="24" t="s">
+      <c r="I47" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J47" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="B48" s="16"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="17"/>
+      <c r="J48" s="17"/>
+    </row>
+    <row r="49" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="20"/>
+      <c r="F49" s="20"/>
+      <c r="G49" s="20"/>
+      <c r="H49" s="20"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
+    </row>
+    <row r="50" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A50" s="24" t="s">
+        <v>122</v>
+      </c>
+      <c r="B50" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>125</v>
+      </c>
+      <c r="E50" s="23" t="s">
+        <v>126</v>
+      </c>
+      <c r="F50" s="23" t="s">
+        <v>127</v>
+      </c>
+      <c r="G50" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="H50" s="23" t="s">
+        <v>129</v>
+      </c>
+      <c r="I50" s="23" t="s">
+        <v>130</v>
+      </c>
+      <c r="J50" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="18" t="s">
+        <v>305</v>
+      </c>
+      <c r="B51" s="16"/>
+      <c r="C51" s="16"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="17"/>
+      <c r="H51" s="17"/>
+      <c r="I51" s="17"/>
+      <c r="J51" s="17"/>
+    </row>
+    <row r="52" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+    </row>
+    <row r="53" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A53" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B53" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C53" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="F53" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="G53" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="H53" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="I53" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="J53" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="18" t="s">
+        <v>306</v>
+      </c>
+      <c r="B54" s="16"/>
+      <c r="C54" s="16"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+      <c r="J54" s="17"/>
+    </row>
+    <row r="55" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="B55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="20"/>
+      <c r="F55" s="20"/>
+      <c r="G55" s="20"/>
+      <c r="H55" s="20"/>
+      <c r="I55" s="20"/>
+      <c r="J55" s="20"/>
+    </row>
+    <row r="56" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A56" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="B56" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="C56" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="D56" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="E56" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="F56" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="G56" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="H56" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="I56" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="J56" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="18" t="s">
+        <v>307</v>
+      </c>
+      <c r="B57" s="16"/>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="17"/>
+      <c r="F57" s="17"/>
+      <c r="G57" s="17"/>
+      <c r="H57" s="17"/>
+      <c r="I57" s="17"/>
+      <c r="J57" s="17"/>
+    </row>
+    <row r="58" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="B58" s="19"/>
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="20"/>
+      <c r="F58" s="20"/>
+      <c r="G58" s="20"/>
+      <c r="H58" s="20"/>
+      <c r="I58" s="20"/>
+      <c r="J58" s="20"/>
+    </row>
+    <row r="59" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A59" s="24" t="s">
+        <v>162</v>
+      </c>
+      <c r="B59" s="22" t="s">
+        <v>163</v>
+      </c>
+      <c r="C59" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="D59" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="E59" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="F59" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="G59" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="H59" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="I59" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="J59" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="B60" s="19"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
+      <c r="H60" s="20"/>
+      <c r="I60" s="20"/>
+      <c r="J60" s="20"/>
+    </row>
+    <row r="61" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A61" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="B61" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="C61" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="D61" s="22" t="s">
+        <v>165</v>
+      </c>
+      <c r="E61" s="23" t="s">
+        <v>185</v>
+      </c>
+      <c r="F61" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="G61" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="H61" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="I61" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="J61" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="18" t="s">
+        <v>308</v>
+      </c>
+      <c r="B62" s="16"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="17"/>
+    </row>
+    <row r="63" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="B63" s="19"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+    </row>
+    <row r="64" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A64" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="B64" s="22" t="s">
+        <v>241</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="D64" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E64" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="F64" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="G64" s="23" t="s">
+        <v>245</v>
+      </c>
+      <c r="H64" s="23" t="s">
+        <v>246</v>
+      </c>
+      <c r="I64" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J64" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="B65" s="16"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="17"/>
+      <c r="G65" s="17"/>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
+      <c r="J65" s="17"/>
+    </row>
+    <row r="66" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="21" t="s">
+        <v>295</v>
+      </c>
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
+      <c r="H66" s="20"/>
+      <c r="I66" s="20"/>
+      <c r="J66" s="20"/>
+    </row>
+    <row r="67" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A67" s="24" t="s">
+        <v>152</v>
+      </c>
+      <c r="B67" s="22" t="s">
+        <v>153</v>
+      </c>
+      <c r="C67" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="D67" s="22" t="s">
+        <v>155</v>
+      </c>
+      <c r="E67" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="F67" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="G67" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="H67" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="I67" s="23" t="s">
+        <v>160</v>
+      </c>
+      <c r="J67" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="18" t="s">
+        <v>311</v>
+      </c>
+      <c r="B68" s="16"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="17"/>
+      <c r="F68" s="17"/>
+      <c r="G68" s="17"/>
+      <c r="H68" s="17"/>
+      <c r="I68" s="17"/>
+      <c r="J68" s="17"/>
+    </row>
+    <row r="69" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="B69" s="19"/>
+      <c r="C69" s="19"/>
+      <c r="D69" s="19"/>
+      <c r="E69" s="20"/>
+      <c r="F69" s="20"/>
+      <c r="G69" s="20"/>
+      <c r="H69" s="20"/>
+      <c r="I69" s="20"/>
+      <c r="J69" s="20"/>
+    </row>
+    <row r="70" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A70" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="B70" s="22" t="s">
+        <v>268</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>269</v>
+      </c>
+      <c r="D70" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E70" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="F70" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="G70" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="H70" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="I70" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J70" s="26" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="18" t="s">
+        <v>312</v>
+      </c>
+      <c r="B71" s="16"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="16"/>
+      <c r="E71" s="17"/>
+      <c r="F71" s="17"/>
+      <c r="G71" s="17"/>
+      <c r="H71" s="17"/>
+      <c r="I71" s="17"/>
+      <c r="J71" s="17"/>
+    </row>
+    <row r="72" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="B72" s="19"/>
+      <c r="C72" s="19"/>
+      <c r="D72" s="19"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="20"/>
+      <c r="G72" s="20"/>
+      <c r="H72" s="20"/>
+      <c r="I72" s="20"/>
+      <c r="J72" s="20"/>
+    </row>
+    <row r="73" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A73" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="B48" s="22" t="s">
+      <c r="B73" s="22" t="s">
         <v>204</v>
       </c>
-      <c r="C48" s="25" t="s">
+      <c r="C73" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="D48" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="E48" s="23" t="s">
+      <c r="D73" s="22" t="s">
         <v>206</v>
       </c>
-      <c r="F48" s="23" t="s">
+      <c r="E73" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="G48" s="23" t="s">
+      <c r="F73" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="H48" s="23" t="s">
+      <c r="G73" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="I48" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="J48" s="26" t="s">
+      <c r="H73" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="I73" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="J73" s="26" t="s">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J3" xr:uid="{E2D1D78E-A5D8-4506-B76F-259AE304FAD6}"/>
-  <mergeCells count="26">
-    <mergeCell ref="A46:J46"/>
-    <mergeCell ref="A47:J47"/>
-    <mergeCell ref="A37:J37"/>
+  <autoFilter ref="A3:J3" xr:uid="{3BC65ED9-AB40-4CEB-B626-6A6F40CB9629}"/>
+  <mergeCells count="40">
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="A69:J69"/>
+    <mergeCell ref="A71:J71"/>
+    <mergeCell ref="A72:J72"/>
+    <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A60:J60"/>
+    <mergeCell ref="A62:J62"/>
+    <mergeCell ref="A63:J63"/>
+    <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A66:J66"/>
+    <mergeCell ref="A49:J49"/>
+    <mergeCell ref="A51:J51"/>
+    <mergeCell ref="A52:J52"/>
+    <mergeCell ref="A54:J54"/>
+    <mergeCell ref="A55:J55"/>
+    <mergeCell ref="A57:J57"/>
     <mergeCell ref="A38:J38"/>
     <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A41:J41"/>
-    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A42:J42"/>
     <mergeCell ref="A44:J44"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A30:J30"/>
-    <mergeCell ref="A32:J32"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="A27:J27"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A33:J33"/>
     <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A35:J35"/>
+    <mergeCell ref="A36:J36"/>
     <mergeCell ref="A16:J16"/>
     <mergeCell ref="A18:J18"/>
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A22:J22"/>
-    <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A25:J25"/>
+    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A26:J26"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A5:J5"/>
@@ -4366,7 +5736,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AE26777-ED2E-4BF7-8B7C-C8D146414D52}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9054266-593B-4E2E-B32B-BF49DDF1DCAB}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4382,7 +5752,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
-        <v>231</v>
+        <v>313</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -4393,7 +5763,7 @@
     </row>
     <row r="2" spans="1:7" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="35" t="s">
-        <v>232</v>
+        <v>314</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4413,259 +5783,259 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>233</v>
+        <v>315</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>234</v>
+        <v>316</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>235</v>
+        <v>317</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>236</v>
+        <v>318</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>237</v>
+        <v>319</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>238</v>
+        <v>320</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>239</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="36" t="s">
-        <v>240</v>
+        <v>322</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>241</v>
+        <v>323</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>242</v>
+        <v>324</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>243</v>
+        <v>325</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>244</v>
+        <v>326</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>245</v>
+        <v>327</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>246</v>
+        <v>328</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="37" t="s">
-        <v>247</v>
+        <v>329</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>248</v>
+        <v>330</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>249</v>
+        <v>331</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>250</v>
+        <v>332</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>251</v>
+        <v>333</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>252</v>
+        <v>334</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>253</v>
+        <v>335</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="36" t="s">
-        <v>254</v>
+        <v>336</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>255</v>
+        <v>337</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>256</v>
+        <v>338</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>257</v>
+        <v>339</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>258</v>
+        <v>340</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>259</v>
+        <v>341</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>260</v>
+        <v>342</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="37" t="s">
-        <v>261</v>
+        <v>343</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>262</v>
+        <v>344</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>263</v>
+        <v>345</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>264</v>
+        <v>346</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>265</v>
+        <v>347</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>266</v>
+        <v>348</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>267</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="36" t="s">
-        <v>268</v>
+        <v>350</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>269</v>
+        <v>351</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>270</v>
+        <v>352</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>271</v>
+        <v>353</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>272</v>
+        <v>354</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>273</v>
+        <v>355</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>274</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="37" t="s">
-        <v>275</v>
+        <v>357</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>276</v>
+        <v>358</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>277</v>
+        <v>359</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>278</v>
+        <v>360</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>279</v>
+        <v>361</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>280</v>
+        <v>362</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>281</v>
+        <v>363</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="36" t="s">
-        <v>282</v>
+        <v>364</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>283</v>
+        <v>365</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>284</v>
+        <v>366</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>285</v>
+        <v>367</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>286</v>
+        <v>368</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>287</v>
+        <v>369</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>288</v>
+        <v>370</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="37" t="s">
-        <v>289</v>
+        <v>371</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>290</v>
+        <v>372</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>291</v>
+        <v>373</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>292</v>
+        <v>374</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>293</v>
+        <v>375</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>294</v>
+        <v>376</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>295</v>
+        <v>377</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="36" t="s">
-        <v>296</v>
+        <v>378</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>297</v>
+        <v>379</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>298</v>
+        <v>380</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>299</v>
+        <v>381</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>300</v>
+        <v>382</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>301</v>
+        <v>383</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>302</v>
+        <v>384</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="37" t="s">
-        <v>303</v>
+        <v>385</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>304</v>
+        <v>386</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>305</v>
+        <v>387</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>305</v>
+        <v>387</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>305</v>
+        <v>387</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>306</v>
+        <v>388</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>307</v>
+        <v>389</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G4" xr:uid="{3AE26777-ED2E-4BF7-8B7C-C8D146414D52}"/>
+  <autoFilter ref="A4:G4" xr:uid="{F9054266-593B-4E2E-B32B-BF49DDF1DCAB}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
@@ -4680,7 +6050,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C6719FA-186E-473F-AA2D-A47A5225302C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF21DF10-3E91-4AA7-9EF9-574E98687091}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4694,7 +6064,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
-        <v>308</v>
+        <v>390</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -4706,120 +6076,120 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>309</v>
+        <v>391</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>310</v>
+        <v>392</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>311</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="36" t="s">
-        <v>312</v>
+        <v>394</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>313</v>
+        <v>395</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>314</v>
+        <v>396</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="37" t="s">
-        <v>315</v>
+        <v>397</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>316</v>
+        <v>398</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>317</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="36" t="s">
-        <v>318</v>
+        <v>400</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>319</v>
+        <v>401</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>320</v>
+        <v>402</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="37" t="s">
-        <v>321</v>
+        <v>403</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>322</v>
+        <v>404</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>323</v>
+        <v>405</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="36" t="s">
-        <v>324</v>
+        <v>406</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>325</v>
+        <v>407</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>326</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="37" t="s">
-        <v>327</v>
+        <v>409</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>328</v>
+        <v>410</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>329</v>
+        <v>411</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="36" t="s">
-        <v>330</v>
+        <v>412</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>331</v>
+        <v>413</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>332</v>
+        <v>414</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="37" t="s">
-        <v>333</v>
+        <v>415</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>334</v>
+        <v>416</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>335</v>
+        <v>417</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="36" t="s">
-        <v>336</v>
+        <v>418</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>337</v>
+        <v>419</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>338</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="37" t="s">
-        <v>339</v>
+        <v>421</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>340</v>
+        <v>422</v>
       </c>
       <c r="C13" s="28" t="s">
         <v>24</v>
@@ -4827,10 +6197,10 @@
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="36" t="s">
-        <v>341</v>
+        <v>423</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>342</v>
+        <v>424</v>
       </c>
       <c r="C14" s="23" t="s">
         <v>21</v>
@@ -4850,7 +6220,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5345DFC6-3946-46A0-9538-73D9EFE38E84}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E378176A-A299-40DE-BA06-ECD1DFCFE810}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4863,7 +6233,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
-        <v>343</v>
+        <v>425</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -4875,32 +6245,32 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>344</v>
+        <v>426</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>345</v>
+        <v>427</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>346</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
-        <v>347</v>
+        <v>429</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>349</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="28" t="s">
-        <v>350</v>
+        <v>432</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>351</v>
+        <v>433</v>
       </c>
       <c r="C5" s="28" t="s">
         <v>24</v>
@@ -4908,10 +6278,10 @@
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
-        <v>352</v>
+        <v>434</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>353</v>
+        <v>435</v>
       </c>
       <c r="C6" s="23" t="s">
         <v>18</v>
@@ -4919,10 +6289,10 @@
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="28" t="s">
-        <v>354</v>
+        <v>436</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>355</v>
+        <v>437</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>21</v>
@@ -4930,46 +6300,46 @@
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
-        <v>356</v>
+        <v>438</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>357</v>
+        <v>439</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>329</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="28" t="s">
-        <v>358</v>
+        <v>440</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>359</v>
+        <v>441</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>360</v>
+        <v>442</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
-        <v>361</v>
+        <v>443</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>362</v>
+        <v>444</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>363</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
-        <v>364</v>
+        <v>446</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>365</v>
+        <v>447</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>366</v>
+        <v>448</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -4979,7 +6349,7 @@
     </row>
     <row r="13" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="35" t="s">
-        <v>367</v>
+        <v>449</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>

--- a/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
+++ b/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7E790EFA-9655-410E-9196-A74AAB69829A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{55A0B0EC-1611-434F-BF11-AC921E0F3A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="2472" windowWidth="17280" windowHeight="8880" xr2:uid="{E041A09E-B47F-4181-9BFC-06F97AE019C5}"/>
+    <workbookView xWindow="5604" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{F5A6BB3A-89A6-4021-B029-5C8BC4A1C3B8}"/>
   </bookViews>
   <sheets>
     <sheet name="Mode d'emploi" sheetId="1" r:id="rId1"/>
@@ -29,8 +29,8 @@
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Depannage niveau 1'!$A$1:$C$13</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Espace central d''echange'!$A$1:$G$14</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Glossaire Control-M'!$A$1:$C$14</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Jobs et cycles'!$A$1:$J$75</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Jobs par type de traitement'!$A$1:$J$73</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Jobs et cycles'!$A$1:$J$79</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Jobs par type de traitement'!$A$1:$J$79</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Mode d''emploi'!$A$1:$D$33</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="472">
   <si>
     <t>Dossier d'exploitation quotidien - ERP_CRM_FACTORY</t>
   </si>
@@ -324,7 +324,7 @@
     <t>Automatique - repetitif toutes les 15 min (8h-18h)</t>
   </si>
   <si>
-    <t>Comptabilite - 5 traitement(s) (deplier pour voir le detail)</t>
+    <t>Comptabilite - 7 traitement(s) (deplier pour voir le detail)</t>
   </si>
   <si>
     <t xml:space="preserve">   TFJ - 2 traitements</t>
@@ -369,6 +369,66 @@
     <t>Automatique - des que ECFCCPRB1 a reussi</t>
   </si>
   <si>
+    <t xml:space="preserve">   INTRADAY - 1 traitement</t>
+  </si>
+  <si>
+    <t>ECFJINTCP1</t>
+  </si>
+  <si>
+    <t>Export comptable a heures fixes (Comptabilite)</t>
+  </si>
+  <si>
+    <t>INTRADAY</t>
+  </si>
+  <si>
+    <t>3 fois par jour - 10h/14h/16h</t>
+  </si>
+  <si>
+    <t>Exporte les ecritures comptables du moment vers un systeme externe</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/snd/export_intraday_AAAAMMJJ_HHh.csv</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFJINTCP1</t>
+  </si>
+  <si>
+    <t>Rien a faire - se relance seul au prochain creneau</t>
+  </si>
+  <si>
+    <t>Automatique - 3 creneaux fixes par jour (10h/14h/16h)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   DIFFERE - 1 traitement</t>
+  </si>
+  <si>
+    <t>ECFJDIFCP1</t>
+  </si>
+  <si>
+    <t>Releves de compte clients (Comptabilite)</t>
+  </si>
+  <si>
+    <t>DIFFERE</t>
+  </si>
+  <si>
+    <t>Chaque nuit - 1h a 5h (heures creuses)</t>
+  </si>
+  <si>
+    <t>Genere les releves de compte du mois pour chaque client - traitement lourd decale</t>
+  </si>
+  <si>
+    <t>$OPERATIONS_DIR/cp/snd/releves_comptes_AAAAMMJJ.txt</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFJDIFCP1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFJDIFCP1 "raison"</t>
+  </si>
+  <si>
+    <t>Automatique - plage horaire creuse (1h-5h) - une fois par jour</t>
+  </si>
+  <si>
     <t xml:space="preserve">   EOQ - 1 traitement</t>
   </si>
   <si>
@@ -399,6 +459,36 @@
     <t>Automatique - fenetre calendaire trimestrielle</t>
   </si>
   <si>
+    <t xml:space="preserve">   EOD - 1 traitement</t>
+  </si>
+  <si>
+    <t>ECFCCLOCP1</t>
+  </si>
+  <si>
+    <t>Bascule comptable du jour (Comptabilite)</t>
+  </si>
+  <si>
+    <t>EOD</t>
+  </si>
+  <si>
+    <t>Chaque soir a 23h50 (minuteur dedie)</t>
+  </si>
+  <si>
+    <t>Fait passer la date comptable de reference au jour suivant</t>
+  </si>
+  <si>
+    <t>$STATE_DIR/valeur_comptable_courante.txt (juste la date - pas un rapport)</t>
+  </si>
+  <si>
+    <t>./bin/view_history.sh ECFCCLOCP1</t>
+  </si>
+  <si>
+    <t>./bin/rerun_job.sh ECFCCLOCP1 "raison"</t>
+  </si>
+  <si>
+    <t>Automatique - minuteur dedie 23h50</t>
+  </si>
+  <si>
     <t>ECFCCLOCP2</t>
   </si>
   <si>
@@ -417,36 +507,6 @@
     <t>./bin/rerun_job.sh ECFCCLOCP2 "raison"</t>
   </si>
   <si>
-    <t xml:space="preserve">   EOD - 1 traitement</t>
-  </si>
-  <si>
-    <t>ECFCCLOCP1</t>
-  </si>
-  <si>
-    <t>Bascule comptable du jour (Comptabilite)</t>
-  </si>
-  <si>
-    <t>EOD</t>
-  </si>
-  <si>
-    <t>Chaque soir a 23h50 (minuteur dedie)</t>
-  </si>
-  <si>
-    <t>Fait passer la date comptable de reference au jour suivant</t>
-  </si>
-  <si>
-    <t>$STATE_DIR/valeur_comptable_courante.txt (juste la date - pas un rapport)</t>
-  </si>
-  <si>
-    <t>./bin/view_history.sh ECFCCLOCP1</t>
-  </si>
-  <si>
-    <t>./bin/rerun_job.sh ECFCCLOCP1 "raison"</t>
-  </si>
-  <si>
-    <t>Automatique - minuteur dedie 23h50</t>
-  </si>
-  <si>
     <t>Achat - 2 traitement(s) (deplier pour voir le detail)</t>
   </si>
   <si>
@@ -991,6 +1051,12 @@
   </si>
   <si>
     <t>EOY - 1 traitement (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>INTRADAY - 1 traitement (deplier pour voir le detail)</t>
+  </si>
+  <si>
+    <t>DIFFERE - 1 traitement (deplier pour voir le detail)</t>
   </si>
   <si>
     <t>Espace central d'echange ($OPERATIONS_DIR) - meme logique qu'un espace SM2/ADI bancaire (RCV/SND/TMP/ARC)</t>
@@ -1460,7 +1526,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFBE82F0"/>
+      <color rgb="FF9669EB"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1515,13 +1581,13 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FF64D296"/>
+      <color rgb="FF2ECC71"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFA5AABE"/>
+      <color rgb="FFA5AAC8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1549,14 +1615,14 @@
     <font>
       <i/>
       <sz val="11"/>
-      <color rgb="FFA5AABE"/>
+      <color rgb="FFA5AAC8"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFBE82F0"/>
+      <color rgb="FF9669EB"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -1570,13 +1636,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E0F32"/>
+        <fgColor rgb="FF181240"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0F111A"/>
+        <fgColor rgb="FF14103A"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1588,25 +1654,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF161925"/>
+        <fgColor rgb="FF1A1646"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D2130"/>
+        <fgColor rgb="FF221C58"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBE82F0"/>
+        <fgColor rgb="FF9669EB"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF5A3C82"/>
+        <fgColor rgb="FF4078E6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1997,7 +2063,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5221FC86-28DB-407E-9D30-F735C2D16DE8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0BF25B-CC6D-4354-8C36-4A1631E81F68}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2252,7 +2318,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B347097-CDBD-40D7-8709-33823CD79C10}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{445F5AAB-F7E3-4E1A-B00F-F65CE4CD40E4}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2366,12 +2432,12 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19B72177-293A-429E-8666-97D11F8E143D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79BEE6B-D6FC-435E-AC94-A0B33E844ABC}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J75"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
@@ -2800,7 +2866,7 @@
     </row>
     <row r="19" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A19" s="21" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -2814,31 +2880,31 @@
     </row>
     <row r="20" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A20" s="24" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B20" s="22" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C20" s="25" t="s">
-        <v>72</v>
+        <v>118</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>73</v>
+        <v>119</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F20" s="23" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G20" s="23" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H20" s="23" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I20" s="23" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="J20" s="26" t="s">
         <v>79</v>
@@ -2846,7 +2912,7 @@
     </row>
     <row r="21" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A21" s="21" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B21" s="19"/>
       <c r="C21" s="19"/>
@@ -2860,251 +2926,251 @@
     </row>
     <row r="22" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A22" s="24" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B22" s="22" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D22" s="22" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="E22" s="23" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="F22" s="23" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G22" s="23" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="H22" s="23" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="I22" s="23" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="J22" s="26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
-      <c r="G23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
-    </row>
-    <row r="24" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-    </row>
-    <row r="25" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A25" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="C25" s="25" t="s">
+    <row r="23" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+    </row>
+    <row r="24" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A24" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="B24" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>142</v>
+      </c>
+      <c r="H24" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="I24" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="J24" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+    </row>
+    <row r="26" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A26" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="B26" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D26" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="F26" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="G26" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="H26" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="I26" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J26" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="17"/>
+      <c r="F27" s="17"/>
+      <c r="G27" s="17"/>
+      <c r="H27" s="17"/>
+      <c r="I27" s="17"/>
+      <c r="J27" s="17"/>
+    </row>
+    <row r="28" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+    </row>
+    <row r="29" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A29" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>154</v>
+      </c>
+      <c r="C29" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D29" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="F25" s="23" t="s">
-        <v>136</v>
-      </c>
-      <c r="G25" s="23" t="s">
-        <v>137</v>
-      </c>
-      <c r="H25" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="I25" s="23" t="s">
+      <c r="E29" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="F29" s="23" t="s">
+        <v>156</v>
+      </c>
+      <c r="G29" s="23" t="s">
+        <v>157</v>
+      </c>
+      <c r="H29" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="I29" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J25" s="26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="B26" s="19"/>
-      <c r="C26" s="19"/>
-      <c r="D26" s="19"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-    </row>
-    <row r="27" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A27" s="24" t="s">
-        <v>141</v>
-      </c>
-      <c r="B27" s="22" t="s">
-        <v>142</v>
-      </c>
-      <c r="C27" s="25" t="s">
-        <v>143</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="E27" s="23" t="s">
-        <v>145</v>
-      </c>
-      <c r="F27" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="G27" s="23" t="s">
-        <v>147</v>
-      </c>
-      <c r="H27" s="23" t="s">
-        <v>148</v>
-      </c>
-      <c r="I27" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="J27" s="26" t="s">
+      <c r="J29" s="26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="B30" s="19"/>
+      <c r="C30" s="19"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
+      <c r="G30" s="20"/>
+      <c r="H30" s="20"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+    </row>
+    <row r="31" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A31" s="24" t="s">
+        <v>161</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>162</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="D31" s="22" t="s">
+        <v>164</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="F31" s="23" t="s">
+        <v>166</v>
+      </c>
+      <c r="G31" s="23" t="s">
+        <v>167</v>
+      </c>
+      <c r="H31" s="23" t="s">
+        <v>168</v>
+      </c>
+      <c r="I31" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="J31" s="26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="18" t="s">
-        <v>150</v>
-      </c>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="17"/>
-      <c r="F28" s="17"/>
-      <c r="G28" s="17"/>
-      <c r="H28" s="17"/>
-      <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
-    </row>
-    <row r="29" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="20"/>
-      <c r="F29" s="20"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="20"/>
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-    </row>
-    <row r="30" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A30" s="24" t="s">
-        <v>152</v>
-      </c>
-      <c r="B30" s="22" t="s">
-        <v>153</v>
-      </c>
-      <c r="C30" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="D30" s="22" t="s">
-        <v>155</v>
-      </c>
-      <c r="E30" s="23" t="s">
-        <v>156</v>
-      </c>
-      <c r="F30" s="23" t="s">
-        <v>157</v>
-      </c>
-      <c r="G30" s="23" t="s">
-        <v>158</v>
-      </c>
-      <c r="H30" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="I30" s="23" t="s">
-        <v>160</v>
-      </c>
-      <c r="J30" s="26" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-    </row>
-    <row r="32" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A32" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="B32" s="22" t="s">
-        <v>163</v>
-      </c>
-      <c r="C32" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="E32" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="F32" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="G32" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="H32" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="I32" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="J32" s="26" t="s">
-        <v>79</v>
-      </c>
+    <row r="32" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="B32" s="16"/>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="17"/>
+      <c r="F32" s="17"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="17"/>
+      <c r="I32" s="17"/>
+      <c r="J32" s="17"/>
     </row>
     <row r="33" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="B33" s="19"/>
       <c r="C33" s="19"/>
@@ -3118,357 +3184,357 @@
     </row>
     <row r="34" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A34" s="24" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B34" s="22" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C34" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="D34" s="22" t="s">
+        <v>175</v>
+      </c>
+      <c r="E34" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="F34" s="23" t="s">
+        <v>177</v>
+      </c>
+      <c r="G34" s="23" t="s">
+        <v>178</v>
+      </c>
+      <c r="H34" s="23" t="s">
+        <v>179</v>
+      </c>
+      <c r="I34" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="J34" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="19"/>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
+      <c r="G35" s="20"/>
+      <c r="H35" s="20"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+    </row>
+    <row r="36" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A36" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="B36" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="D36" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="F36" s="23" t="s">
+        <v>187</v>
+      </c>
+      <c r="G36" s="23" t="s">
+        <v>188</v>
+      </c>
+      <c r="H36" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="I36" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="J36" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B37" s="19"/>
+      <c r="C37" s="19"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
+      <c r="G37" s="20"/>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+    </row>
+    <row r="38" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A38" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="B38" s="22" t="s">
+        <v>191</v>
+      </c>
+      <c r="C38" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D34" s="22" t="s">
+      <c r="D38" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="E34" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="F34" s="23" t="s">
-        <v>173</v>
-      </c>
-      <c r="G34" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="H34" s="23" t="s">
-        <v>175</v>
-      </c>
-      <c r="I34" s="23" t="s">
+      <c r="E38" s="23" t="s">
+        <v>192</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>193</v>
+      </c>
+      <c r="G38" s="23" t="s">
+        <v>194</v>
+      </c>
+      <c r="H38" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="I38" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J34" s="26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="18" t="s">
-        <v>176</v>
-      </c>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
-      <c r="D35" s="16"/>
-      <c r="E35" s="17"/>
-      <c r="F35" s="17"/>
-      <c r="G35" s="17"/>
-      <c r="H35" s="17"/>
-      <c r="I35" s="17"/>
-      <c r="J35" s="17"/>
-    </row>
-    <row r="36" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
-      <c r="D36" s="19"/>
-      <c r="E36" s="20"/>
-      <c r="F36" s="20"/>
-      <c r="G36" s="20"/>
-      <c r="H36" s="20"/>
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-    </row>
-    <row r="37" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A37" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="B37" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="C37" s="25" t="s">
+      <c r="J38" s="26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
+      <c r="H39" s="17"/>
+      <c r="I39" s="17"/>
+      <c r="J39" s="17"/>
+    </row>
+    <row r="40" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B40" s="19"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="19"/>
+      <c r="E40" s="20"/>
+      <c r="F40" s="20"/>
+      <c r="G40" s="20"/>
+      <c r="H40" s="20"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+    </row>
+    <row r="41" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A41" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="B41" s="22" t="s">
+        <v>198</v>
+      </c>
+      <c r="C41" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="D41" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="E37" s="23" t="s">
-        <v>179</v>
-      </c>
-      <c r="F37" s="23" t="s">
-        <v>180</v>
-      </c>
-      <c r="G37" s="23" t="s">
+      <c r="E41" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="F41" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="G41" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="H41" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="I41" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="J41" s="26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="H37" s="23" t="s">
-        <v>182</v>
-      </c>
-      <c r="I37" s="23" t="s">
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="20"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+    </row>
+    <row r="43" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A43" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="C43" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="D43" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="E43" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="F43" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="G43" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="H43" s="23" t="s">
+        <v>88</v>
+      </c>
+      <c r="I43" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="J43" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B44" s="16"/>
+      <c r="C44" s="16"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="17"/>
+      <c r="F44" s="17"/>
+      <c r="G44" s="17"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+    </row>
+    <row r="45" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+    </row>
+    <row r="46" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A46" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="B46" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="C46" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D46" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E46" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="F46" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="G46" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="H46" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="I46" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J46" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B47" s="19"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="20"/>
+      <c r="F47" s="20"/>
+      <c r="G47" s="20"/>
+      <c r="H47" s="20"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+    </row>
+    <row r="48" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A48" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="B48" s="22" t="s">
+        <v>216</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="D48" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="E48" s="23" t="s">
+        <v>217</v>
+      </c>
+      <c r="F48" s="23" t="s">
+        <v>218</v>
+      </c>
+      <c r="G48" s="23" t="s">
+        <v>219</v>
+      </c>
+      <c r="H48" s="23" t="s">
+        <v>220</v>
+      </c>
+      <c r="I48" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J37" s="26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="21" t="s">
-        <v>161</v>
-      </c>
-      <c r="B38" s="19"/>
-      <c r="C38" s="19"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-    </row>
-    <row r="39" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A39" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="B39" s="22" t="s">
-        <v>184</v>
-      </c>
-      <c r="C39" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="D39" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>185</v>
-      </c>
-      <c r="F39" s="23" t="s">
-        <v>186</v>
-      </c>
-      <c r="G39" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="H39" s="23" t="s">
-        <v>88</v>
-      </c>
-      <c r="I39" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="J39" s="26" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="18" t="s">
-        <v>188</v>
-      </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="17"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-    </row>
-    <row r="41" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="20"/>
-      <c r="F41" s="20"/>
-      <c r="G41" s="20"/>
-      <c r="H41" s="20"/>
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-    </row>
-    <row r="42" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A42" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="B42" s="22" t="s">
-        <v>190</v>
-      </c>
-      <c r="C42" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="E42" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="F42" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="G42" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="H42" s="23" t="s">
-        <v>194</v>
-      </c>
-      <c r="I42" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="J42" s="26" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="20"/>
-      <c r="F43" s="20"/>
-      <c r="G43" s="20"/>
-      <c r="H43" s="20"/>
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-    </row>
-    <row r="44" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A44" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="B44" s="22" t="s">
-        <v>196</v>
-      </c>
-      <c r="C44" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="D44" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="E44" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="F44" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="G44" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="H44" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="I44" s="23" t="s">
-        <v>52</v>
-      </c>
-      <c r="J44" s="26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="18" t="s">
-        <v>201</v>
-      </c>
-      <c r="B45" s="16"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="17"/>
-      <c r="F45" s="17"/>
-      <c r="G45" s="17"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-    </row>
-    <row r="46" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="20"/>
-      <c r="F46" s="20"/>
-      <c r="G46" s="20"/>
-      <c r="H46" s="20"/>
-      <c r="I46" s="20"/>
-      <c r="J46" s="20"/>
-    </row>
-    <row r="47" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A47" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="B47" s="22" t="s">
-        <v>204</v>
-      </c>
-      <c r="C47" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="D47" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="E47" s="23" t="s">
-        <v>207</v>
-      </c>
-      <c r="F47" s="23" t="s">
-        <v>208</v>
-      </c>
-      <c r="G47" s="23" t="s">
-        <v>209</v>
-      </c>
-      <c r="H47" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="I47" s="23" t="s">
-        <v>211</v>
-      </c>
-      <c r="J47" s="26" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="B48" s="19"/>
-      <c r="C48" s="19"/>
-      <c r="D48" s="19"/>
-      <c r="E48" s="20"/>
-      <c r="F48" s="20"/>
-      <c r="G48" s="20"/>
-      <c r="H48" s="20"/>
-      <c r="I48" s="20"/>
-      <c r="J48" s="20"/>
-    </row>
-    <row r="49" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A49" s="24" t="s">
-        <v>212</v>
-      </c>
-      <c r="B49" s="22" t="s">
-        <v>213</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>72</v>
-      </c>
-      <c r="D49" s="22" t="s">
-        <v>73</v>
-      </c>
-      <c r="E49" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="F49" s="23" t="s">
-        <v>215</v>
-      </c>
-      <c r="G49" s="23" t="s">
-        <v>216</v>
-      </c>
-      <c r="H49" s="23" t="s">
-        <v>217</v>
-      </c>
-      <c r="I49" s="23" t="s">
-        <v>78</v>
-      </c>
-      <c r="J49" s="26" t="s">
-        <v>79</v>
-      </c>
+      <c r="J48" s="26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="B49" s="16"/>
+      <c r="C49" s="16"/>
+      <c r="D49" s="16"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+      <c r="H49" s="17"/>
+      <c r="I49" s="17"/>
+      <c r="J49" s="17"/>
     </row>
     <row r="50" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A50" s="21" t="s">
-        <v>132</v>
+        <v>222</v>
       </c>
       <c r="B50" s="19"/>
       <c r="C50" s="19"/>
@@ -3482,565 +3548,659 @@
     </row>
     <row r="51" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A51" s="24" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B51" s="22" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C51" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="D51" s="22" t="s">
+        <v>226</v>
+      </c>
+      <c r="E51" s="23" t="s">
+        <v>227</v>
+      </c>
+      <c r="F51" s="23" t="s">
+        <v>228</v>
+      </c>
+      <c r="G51" s="23" t="s">
+        <v>229</v>
+      </c>
+      <c r="H51" s="23" t="s">
+        <v>230</v>
+      </c>
+      <c r="I51" s="23" t="s">
+        <v>231</v>
+      </c>
+      <c r="J51" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+    </row>
+    <row r="53" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A53" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="B53" s="22" t="s">
+        <v>233</v>
+      </c>
+      <c r="C53" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>234</v>
+      </c>
+      <c r="F53" s="23" t="s">
+        <v>235</v>
+      </c>
+      <c r="G53" s="23" t="s">
+        <v>236</v>
+      </c>
+      <c r="H53" s="23" t="s">
+        <v>237</v>
+      </c>
+      <c r="I53" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="J53" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B54" s="19"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="20"/>
+      <c r="F54" s="20"/>
+      <c r="G54" s="20"/>
+      <c r="H54" s="20"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
+    </row>
+    <row r="55" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A55" s="24" t="s">
+        <v>238</v>
+      </c>
+      <c r="B55" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="C55" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D51" s="22" t="s">
+      <c r="D55" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="E51" s="23" t="s">
-        <v>220</v>
-      </c>
-      <c r="F51" s="23" t="s">
-        <v>221</v>
-      </c>
-      <c r="G51" s="23" t="s">
-        <v>222</v>
-      </c>
-      <c r="H51" s="23" t="s">
-        <v>223</v>
-      </c>
-      <c r="I51" s="23" t="s">
+      <c r="E55" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="F55" s="23" t="s">
+        <v>241</v>
+      </c>
+      <c r="G55" s="23" t="s">
+        <v>242</v>
+      </c>
+      <c r="H55" s="23" t="s">
+        <v>243</v>
+      </c>
+      <c r="I55" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J51" s="26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="18" t="s">
-        <v>224</v>
-      </c>
-      <c r="B52" s="16"/>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
-      <c r="H52" s="17"/>
-      <c r="I52" s="17"/>
-      <c r="J52" s="17"/>
-    </row>
-    <row r="53" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="21" t="s">
+      <c r="J55" s="26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="B56" s="16"/>
+      <c r="C56" s="16"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="17"/>
+      <c r="F56" s="17"/>
+      <c r="G56" s="17"/>
+      <c r="H56" s="17"/>
+      <c r="I56" s="17"/>
+      <c r="J56" s="17"/>
+    </row>
+    <row r="57" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B53" s="19"/>
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20"/>
-      <c r="G53" s="20"/>
-      <c r="H53" s="20"/>
-      <c r="I53" s="20"/>
-      <c r="J53" s="20"/>
-    </row>
-    <row r="54" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A54" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="B54" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="C54" s="25" t="s">
+      <c r="B57" s="19"/>
+      <c r="C57" s="19"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="20"/>
+      <c r="F57" s="20"/>
+      <c r="G57" s="20"/>
+      <c r="H57" s="20"/>
+      <c r="I57" s="20"/>
+      <c r="J57" s="20"/>
+    </row>
+    <row r="58" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A58" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="B58" s="22" t="s">
+        <v>246</v>
+      </c>
+      <c r="C58" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="D54" s="22" t="s">
+      <c r="D58" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="E54" s="23" t="s">
-        <v>227</v>
-      </c>
-      <c r="F54" s="23" t="s">
-        <v>228</v>
-      </c>
-      <c r="G54" s="23" t="s">
-        <v>229</v>
-      </c>
-      <c r="H54" s="23" t="s">
-        <v>230</v>
-      </c>
-      <c r="I54" s="23" t="s">
+      <c r="E58" s="23" t="s">
+        <v>247</v>
+      </c>
+      <c r="F58" s="23" t="s">
+        <v>248</v>
+      </c>
+      <c r="G58" s="23" t="s">
+        <v>249</v>
+      </c>
+      <c r="H58" s="23" t="s">
+        <v>250</v>
+      </c>
+      <c r="I58" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="J54" s="26" t="s">
+      <c r="J58" s="26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
-      <c r="D55" s="16"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="17"/>
-      <c r="G55" s="17"/>
-      <c r="H55" s="17"/>
-      <c r="I55" s="17"/>
-      <c r="J55" s="17"/>
-    </row>
-    <row r="56" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="21" t="s">
+    <row r="59" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="18" t="s">
+        <v>251</v>
+      </c>
+      <c r="B59" s="16"/>
+      <c r="C59" s="16"/>
+      <c r="D59" s="16"/>
+      <c r="E59" s="17"/>
+      <c r="F59" s="17"/>
+      <c r="G59" s="17"/>
+      <c r="H59" s="17"/>
+      <c r="I59" s="17"/>
+      <c r="J59" s="17"/>
+    </row>
+    <row r="60" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B56" s="19"/>
-      <c r="C56" s="19"/>
-      <c r="D56" s="19"/>
-      <c r="E56" s="20"/>
-      <c r="F56" s="20"/>
-      <c r="G56" s="20"/>
-      <c r="H56" s="20"/>
-      <c r="I56" s="20"/>
-      <c r="J56" s="20"/>
-    </row>
-    <row r="57" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A57" s="24" t="s">
-        <v>232</v>
-      </c>
-      <c r="B57" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="C57" s="25" t="s">
+      <c r="B60" s="19"/>
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="20"/>
+      <c r="F60" s="20"/>
+      <c r="G60" s="20"/>
+      <c r="H60" s="20"/>
+      <c r="I60" s="20"/>
+      <c r="J60" s="20"/>
+    </row>
+    <row r="61" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A61" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="B61" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="C61" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="D57" s="22" t="s">
+      <c r="D61" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="E57" s="23" t="s">
-        <v>234</v>
-      </c>
-      <c r="F57" s="23" t="s">
-        <v>235</v>
-      </c>
-      <c r="G57" s="23" t="s">
-        <v>236</v>
-      </c>
-      <c r="H57" s="23" t="s">
-        <v>237</v>
-      </c>
-      <c r="I57" s="23" t="s">
+      <c r="E61" s="23" t="s">
+        <v>254</v>
+      </c>
+      <c r="F61" s="23" t="s">
+        <v>255</v>
+      </c>
+      <c r="G61" s="23" t="s">
+        <v>256</v>
+      </c>
+      <c r="H61" s="23" t="s">
+        <v>257</v>
+      </c>
+      <c r="I61" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="J57" s="26" t="s">
+      <c r="J61" s="26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="B58" s="16"/>
-      <c r="C58" s="16"/>
-      <c r="D58" s="16"/>
-      <c r="E58" s="17"/>
-      <c r="F58" s="17"/>
-      <c r="G58" s="17"/>
-      <c r="H58" s="17"/>
-      <c r="I58" s="17"/>
-      <c r="J58" s="17"/>
-    </row>
-    <row r="59" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
-      <c r="J59" s="20"/>
-    </row>
-    <row r="60" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A60" s="24" t="s">
-        <v>240</v>
-      </c>
-      <c r="B60" s="22" t="s">
-        <v>241</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>242</v>
-      </c>
-      <c r="D60" s="22" t="s">
+    <row r="62" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="18" t="s">
+        <v>258</v>
+      </c>
+      <c r="B62" s="16"/>
+      <c r="C62" s="16"/>
+      <c r="D62" s="16"/>
+      <c r="E62" s="17"/>
+      <c r="F62" s="17"/>
+      <c r="G62" s="17"/>
+      <c r="H62" s="17"/>
+      <c r="I62" s="17"/>
+      <c r="J62" s="17"/>
+    </row>
+    <row r="63" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="B63" s="19"/>
+      <c r="C63" s="19"/>
+      <c r="D63" s="19"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+    </row>
+    <row r="64" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A64" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="B64" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="C64" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="D64" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="E60" s="23" t="s">
-        <v>243</v>
-      </c>
-      <c r="F60" s="23" t="s">
-        <v>244</v>
-      </c>
-      <c r="G60" s="23" t="s">
-        <v>245</v>
-      </c>
-      <c r="H60" s="23" t="s">
-        <v>246</v>
-      </c>
-      <c r="I60" s="23" t="s">
+      <c r="E64" s="23" t="s">
+        <v>263</v>
+      </c>
+      <c r="F64" s="23" t="s">
+        <v>264</v>
+      </c>
+      <c r="G64" s="23" t="s">
+        <v>265</v>
+      </c>
+      <c r="H64" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="I64" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="J60" s="26" t="s">
+      <c r="J64" s="26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="B61" s="16"/>
-      <c r="C61" s="16"/>
-      <c r="D61" s="16"/>
-      <c r="E61" s="17"/>
-      <c r="F61" s="17"/>
-      <c r="G61" s="17"/>
-      <c r="H61" s="17"/>
-      <c r="I61" s="17"/>
-      <c r="J61" s="17"/>
-    </row>
-    <row r="62" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B62" s="19"/>
-      <c r="C62" s="19"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="20"/>
-      <c r="F62" s="20"/>
-      <c r="G62" s="20"/>
-      <c r="H62" s="20"/>
-      <c r="I62" s="20"/>
-      <c r="J62" s="20"/>
-    </row>
-    <row r="63" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A63" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="B63" s="22" t="s">
-        <v>249</v>
-      </c>
-      <c r="C63" s="25" t="s">
+    <row r="65" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="B65" s="16"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="16"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="17"/>
+      <c r="G65" s="17"/>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
+      <c r="J65" s="17"/>
+    </row>
+    <row r="66" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B66" s="19"/>
+      <c r="C66" s="19"/>
+      <c r="D66" s="19"/>
+      <c r="E66" s="20"/>
+      <c r="F66" s="20"/>
+      <c r="G66" s="20"/>
+      <c r="H66" s="20"/>
+      <c r="I66" s="20"/>
+      <c r="J66" s="20"/>
+    </row>
+    <row r="67" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A67" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="B67" s="22" t="s">
+        <v>269</v>
+      </c>
+      <c r="C67" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D63" s="22" t="s">
+      <c r="D67" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="E63" s="23" t="s">
-        <v>250</v>
-      </c>
-      <c r="F63" s="23" t="s">
-        <v>251</v>
-      </c>
-      <c r="G63" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="H63" s="23" t="s">
-        <v>253</v>
-      </c>
-      <c r="I63" s="23" t="s">
+      <c r="E67" s="23" t="s">
+        <v>270</v>
+      </c>
+      <c r="F67" s="23" t="s">
+        <v>271</v>
+      </c>
+      <c r="G67" s="23" t="s">
+        <v>272</v>
+      </c>
+      <c r="H67" s="23" t="s">
+        <v>273</v>
+      </c>
+      <c r="I67" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J63" s="26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="64" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="21" t="s">
+      <c r="J67" s="26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="68" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="B64" s="19"/>
-      <c r="C64" s="19"/>
-      <c r="D64" s="19"/>
-      <c r="E64" s="20"/>
-      <c r="F64" s="20"/>
-      <c r="G64" s="20"/>
-      <c r="H64" s="20"/>
-      <c r="I64" s="20"/>
-      <c r="J64" s="20"/>
-    </row>
-    <row r="65" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A65" s="24" t="s">
-        <v>254</v>
-      </c>
-      <c r="B65" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="C65" s="25" t="s">
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="20"/>
+      <c r="G68" s="20"/>
+      <c r="H68" s="20"/>
+      <c r="I68" s="20"/>
+      <c r="J68" s="20"/>
+    </row>
+    <row r="69" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A69" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="B69" s="22" t="s">
+        <v>275</v>
+      </c>
+      <c r="C69" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="D65" s="22" t="s">
+      <c r="D69" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="E65" s="23" t="s">
-        <v>256</v>
-      </c>
-      <c r="F65" s="23" t="s">
-        <v>257</v>
-      </c>
-      <c r="G65" s="23" t="s">
-        <v>258</v>
-      </c>
-      <c r="H65" s="23" t="s">
+      <c r="E69" s="23" t="s">
+        <v>276</v>
+      </c>
+      <c r="F69" s="23" t="s">
+        <v>277</v>
+      </c>
+      <c r="G69" s="23" t="s">
+        <v>278</v>
+      </c>
+      <c r="H69" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="I65" s="23" t="s">
+      <c r="I69" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="J65" s="26" t="s">
+      <c r="J69" s="26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="18" t="s">
-        <v>259</v>
-      </c>
-      <c r="B66" s="16"/>
-      <c r="C66" s="16"/>
-      <c r="D66" s="16"/>
-      <c r="E66" s="17"/>
-      <c r="F66" s="17"/>
-      <c r="G66" s="17"/>
-      <c r="H66" s="17"/>
-      <c r="I66" s="17"/>
-      <c r="J66" s="17"/>
-    </row>
-    <row r="67" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="21" t="s">
+    <row r="70" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B70" s="16"/>
+      <c r="C70" s="16"/>
+      <c r="D70" s="16"/>
+      <c r="E70" s="17"/>
+      <c r="F70" s="17"/>
+      <c r="G70" s="17"/>
+      <c r="H70" s="17"/>
+      <c r="I70" s="17"/>
+      <c r="J70" s="17"/>
+    </row>
+    <row r="71" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="B67" s="19"/>
-      <c r="C67" s="19"/>
-      <c r="D67" s="19"/>
-      <c r="E67" s="20"/>
-      <c r="F67" s="20"/>
-      <c r="G67" s="20"/>
-      <c r="H67" s="20"/>
-      <c r="I67" s="20"/>
-      <c r="J67" s="20"/>
-    </row>
-    <row r="68" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A68" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="B68" s="22" t="s">
-        <v>261</v>
-      </c>
-      <c r="C68" s="25" t="s">
+      <c r="B71" s="19"/>
+      <c r="C71" s="19"/>
+      <c r="D71" s="19"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="20"/>
+      <c r="G71" s="20"/>
+      <c r="H71" s="20"/>
+      <c r="I71" s="20"/>
+      <c r="J71" s="20"/>
+    </row>
+    <row r="72" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A72" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="B72" s="22" t="s">
+        <v>281</v>
+      </c>
+      <c r="C72" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="D68" s="22" t="s">
+      <c r="D72" s="22" t="s">
         <v>73</v>
       </c>
-      <c r="E68" s="23" t="s">
-        <v>262</v>
-      </c>
-      <c r="F68" s="23" t="s">
-        <v>263</v>
-      </c>
-      <c r="G68" s="23" t="s">
-        <v>264</v>
-      </c>
-      <c r="H68" s="23" t="s">
-        <v>265</v>
-      </c>
-      <c r="I68" s="23" t="s">
+      <c r="E72" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="F72" s="23" t="s">
+        <v>283</v>
+      </c>
+      <c r="G72" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="H72" s="23" t="s">
+        <v>285</v>
+      </c>
+      <c r="I72" s="23" t="s">
         <v>78</v>
       </c>
-      <c r="J68" s="26" t="s">
+      <c r="J72" s="26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="21" t="s">
-        <v>266</v>
-      </c>
-      <c r="B69" s="19"/>
-      <c r="C69" s="19"/>
-      <c r="D69" s="19"/>
-      <c r="E69" s="20"/>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="20"/>
-      <c r="I69" s="20"/>
-      <c r="J69" s="20"/>
-    </row>
-    <row r="70" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A70" s="24" t="s">
-        <v>267</v>
-      </c>
-      <c r="B70" s="22" t="s">
-        <v>268</v>
-      </c>
-      <c r="C70" s="25" t="s">
-        <v>269</v>
-      </c>
-      <c r="D70" s="22" t="s">
+    <row r="73" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="B73" s="19"/>
+      <c r="C73" s="19"/>
+      <c r="D73" s="19"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="20"/>
+      <c r="G73" s="20"/>
+      <c r="H73" s="20"/>
+      <c r="I73" s="20"/>
+      <c r="J73" s="20"/>
+    </row>
+    <row r="74" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A74" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="B74" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="D74" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="E70" s="23" t="s">
-        <v>270</v>
-      </c>
-      <c r="F70" s="23" t="s">
-        <v>271</v>
-      </c>
-      <c r="G70" s="23" t="s">
-        <v>272</v>
-      </c>
-      <c r="H70" s="23" t="s">
-        <v>273</v>
-      </c>
-      <c r="I70" s="23" t="s">
+      <c r="E74" s="23" t="s">
+        <v>290</v>
+      </c>
+      <c r="F74" s="23" t="s">
+        <v>291</v>
+      </c>
+      <c r="G74" s="23" t="s">
+        <v>292</v>
+      </c>
+      <c r="H74" s="23" t="s">
+        <v>293</v>
+      </c>
+      <c r="I74" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J70" s="26" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="18" t="s">
-        <v>274</v>
-      </c>
-      <c r="B71" s="16"/>
-      <c r="C71" s="16"/>
-      <c r="D71" s="16"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="17"/>
-      <c r="G71" s="17"/>
-      <c r="H71" s="17"/>
-      <c r="I71" s="17"/>
-      <c r="J71" s="17"/>
-    </row>
-    <row r="72" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="21" t="s">
+      <c r="J74" s="26" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="B75" s="16"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="16"/>
+      <c r="E75" s="17"/>
+      <c r="F75" s="17"/>
+      <c r="G75" s="17"/>
+      <c r="H75" s="17"/>
+      <c r="I75" s="17"/>
+      <c r="J75" s="17"/>
+    </row>
+    <row r="76" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="B72" s="19"/>
-      <c r="C72" s="19"/>
-      <c r="D72" s="19"/>
-      <c r="E72" s="20"/>
-      <c r="F72" s="20"/>
-      <c r="G72" s="20"/>
-      <c r="H72" s="20"/>
-      <c r="I72" s="20"/>
-      <c r="J72" s="20"/>
-    </row>
-    <row r="73" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A73" s="24" t="s">
-        <v>275</v>
-      </c>
-      <c r="B73" s="22" t="s">
-        <v>276</v>
-      </c>
-      <c r="C73" s="25" t="s">
+      <c r="B76" s="19"/>
+      <c r="C76" s="19"/>
+      <c r="D76" s="19"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="20"/>
+      <c r="G76" s="20"/>
+      <c r="H76" s="20"/>
+      <c r="I76" s="20"/>
+      <c r="J76" s="20"/>
+    </row>
+    <row r="77" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A77" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="B77" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="C77" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="D73" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="E73" s="23" t="s">
-        <v>277</v>
-      </c>
-      <c r="F73" s="23" t="s">
-        <v>278</v>
-      </c>
-      <c r="G73" s="23" t="s">
-        <v>279</v>
-      </c>
-      <c r="H73" s="23" t="s">
+      <c r="D77" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="E77" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="F77" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="G77" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="H77" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="I73" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="J73" s="26" t="s">
+      <c r="I77" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="J77" s="26" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="B74" s="19"/>
-      <c r="C74" s="19"/>
-      <c r="D74" s="19"/>
-      <c r="E74" s="20"/>
-      <c r="F74" s="20"/>
-      <c r="G74" s="20"/>
-      <c r="H74" s="20"/>
-      <c r="I74" s="20"/>
-      <c r="J74" s="20"/>
-    </row>
-    <row r="75" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
-      <c r="A75" s="24" t="s">
-        <v>280</v>
-      </c>
-      <c r="B75" s="22" t="s">
-        <v>281</v>
-      </c>
-      <c r="C75" s="25" t="s">
+    <row r="78" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="B78" s="19"/>
+      <c r="C78" s="19"/>
+      <c r="D78" s="19"/>
+      <c r="E78" s="20"/>
+      <c r="F78" s="20"/>
+      <c r="G78" s="20"/>
+      <c r="H78" s="20"/>
+      <c r="I78" s="20"/>
+      <c r="J78" s="20"/>
+    </row>
+    <row r="79" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A79" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="B79" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="C79" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="D75" s="22" t="s">
+      <c r="D79" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="E75" s="23" t="s">
-        <v>282</v>
-      </c>
-      <c r="F75" s="23" t="s">
-        <v>283</v>
-      </c>
-      <c r="G75" s="23" t="s">
-        <v>284</v>
-      </c>
-      <c r="H75" s="23" t="s">
-        <v>285</v>
-      </c>
-      <c r="I75" s="23" t="s">
+      <c r="E79" s="23" t="s">
+        <v>302</v>
+      </c>
+      <c r="F79" s="23" t="s">
+        <v>303</v>
+      </c>
+      <c r="G79" s="23" t="s">
+        <v>304</v>
+      </c>
+      <c r="H79" s="23" t="s">
+        <v>305</v>
+      </c>
+      <c r="I79" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="J75" s="26" t="s">
-        <v>139</v>
+      <c r="J79" s="26" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J3" xr:uid="{19B72177-293A-429E-8666-97D11F8E143D}"/>
-  <mergeCells count="42">
+  <autoFilter ref="A3:J3" xr:uid="{C79BEE6B-D6FC-435E-AC94-A0B33E844ABC}"/>
+  <mergeCells count="44">
+    <mergeCell ref="A76:J76"/>
+    <mergeCell ref="A78:J78"/>
     <mergeCell ref="A66:J66"/>
-    <mergeCell ref="A67:J67"/>
-    <mergeCell ref="A69:J69"/>
+    <mergeCell ref="A68:J68"/>
+    <mergeCell ref="A70:J70"/>
     <mergeCell ref="A71:J71"/>
-    <mergeCell ref="A72:J72"/>
-    <mergeCell ref="A74:J74"/>
-    <mergeCell ref="A56:J56"/>
-    <mergeCell ref="A58:J58"/>
+    <mergeCell ref="A73:J73"/>
+    <mergeCell ref="A75:J75"/>
+    <mergeCell ref="A57:J57"/>
     <mergeCell ref="A59:J59"/>
-    <mergeCell ref="A61:J61"/>
+    <mergeCell ref="A60:J60"/>
     <mergeCell ref="A62:J62"/>
-    <mergeCell ref="A64:J64"/>
-    <mergeCell ref="A46:J46"/>
-    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="A63:J63"/>
+    <mergeCell ref="A65:J65"/>
+    <mergeCell ref="A47:J47"/>
+    <mergeCell ref="A49:J49"/>
     <mergeCell ref="A50:J50"/>
     <mergeCell ref="A52:J52"/>
-    <mergeCell ref="A53:J53"/>
-    <mergeCell ref="A55:J55"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="A38:J38"/>
+    <mergeCell ref="A54:J54"/>
+    <mergeCell ref="A56:J56"/>
+    <mergeCell ref="A37:J37"/>
+    <mergeCell ref="A39:J39"/>
     <mergeCell ref="A40:J40"/>
-    <mergeCell ref="A41:J41"/>
-    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A42:J42"/>
+    <mergeCell ref="A44:J44"/>
     <mergeCell ref="A45:J45"/>
-    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A27:J27"/>
     <mergeCell ref="A28:J28"/>
-    <mergeCell ref="A29:J29"/>
-    <mergeCell ref="A31:J31"/>
+    <mergeCell ref="A30:J30"/>
+    <mergeCell ref="A32:J32"/>
     <mergeCell ref="A33:J33"/>
     <mergeCell ref="A35:J35"/>
     <mergeCell ref="A14:J14"/>
@@ -4048,7 +4208,7 @@
     <mergeCell ref="A19:J19"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A25:J25"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A4:J4"/>
     <mergeCell ref="A5:J5"/>
@@ -4066,12 +4226,12 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BC65ED9-AB40-4CEB-B626-6A6F40CB9629}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BC87A21-33BD-4679-99E2-8BD7169C6A34}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J73"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" outlineLevelRow="2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.77734375" customWidth="1"/>
@@ -4088,7 +4248,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>286</v>
+        <v>306</v>
       </c>
       <c r="B1" s="13"/>
       <c r="C1" s="13"/>
@@ -4146,7 +4306,7 @@
     </row>
     <row r="4" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -4160,7 +4320,7 @@
     </row>
     <row r="5" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A5" s="21" t="s">
-        <v>288</v>
+        <v>308</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
@@ -4270,7 +4430,7 @@
     </row>
     <row r="9" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A9" s="21" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="B9" s="19"/>
       <c r="C9" s="19"/>
@@ -4348,7 +4508,7 @@
     </row>
     <row r="12" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A12" s="21" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -4362,10 +4522,10 @@
     </row>
     <row r="13" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A13" s="24" t="s">
-        <v>218</v>
+        <v>238</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>219</v>
+        <v>239</v>
       </c>
       <c r="C13" s="25" t="s">
         <v>46</v>
@@ -4374,27 +4534,27 @@
         <v>47</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>220</v>
+        <v>240</v>
       </c>
       <c r="F13" s="23" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="G13" s="23" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
       <c r="H13" s="23" t="s">
-        <v>223</v>
+        <v>243</v>
       </c>
       <c r="I13" s="23" t="s">
         <v>52</v>
       </c>
       <c r="J13" s="26" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A14" s="21" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -4408,10 +4568,10 @@
     </row>
     <row r="15" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A15" s="24" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
       <c r="B15" s="22" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="C15" s="25" t="s">
         <v>46</v>
@@ -4420,27 +4580,27 @@
         <v>47</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="F15" s="23" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="G15" s="23" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="H15" s="23" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="I15" s="23" t="s">
         <v>52</v>
       </c>
       <c r="J15" s="26" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A16" s="21" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -4454,10 +4614,10 @@
     </row>
     <row r="17" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A17" s="24" t="s">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="B17" s="22" t="s">
-        <v>281</v>
+        <v>301</v>
       </c>
       <c r="C17" s="25" t="s">
         <v>46</v>
@@ -4466,27 +4626,27 @@
         <v>47</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>282</v>
+        <v>302</v>
       </c>
       <c r="F17" s="23" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="G17" s="23" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="H17" s="23" t="s">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="I17" s="23" t="s">
         <v>52</v>
       </c>
       <c r="J17" s="26" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A18" s="21" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -4500,10 +4660,10 @@
     </row>
     <row r="19" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A19" s="24" t="s">
-        <v>195</v>
+        <v>215</v>
       </c>
       <c r="B19" s="22" t="s">
-        <v>196</v>
+        <v>216</v>
       </c>
       <c r="C19" s="25" t="s">
         <v>46</v>
@@ -4512,27 +4672,27 @@
         <v>47</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="F19" s="23" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="G19" s="23" t="s">
-        <v>199</v>
+        <v>219</v>
       </c>
       <c r="H19" s="23" t="s">
-        <v>200</v>
+        <v>220</v>
       </c>
       <c r="I19" s="23" t="s">
         <v>52</v>
       </c>
       <c r="J19" s="26" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A20" s="21" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="19"/>
@@ -4546,10 +4706,10 @@
     </row>
     <row r="21" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A21" s="24" t="s">
-        <v>133</v>
+        <v>153</v>
       </c>
       <c r="B21" s="22" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="C21" s="25" t="s">
         <v>46</v>
@@ -4558,27 +4718,27 @@
         <v>47</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>135</v>
+        <v>155</v>
       </c>
       <c r="F21" s="23" t="s">
-        <v>136</v>
+        <v>156</v>
       </c>
       <c r="G21" s="23" t="s">
-        <v>137</v>
+        <v>157</v>
       </c>
       <c r="H21" s="23" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="I21" s="23" t="s">
         <v>52</v>
       </c>
       <c r="J21" s="26" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A22" s="21" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="B22" s="19"/>
       <c r="C22" s="19"/>
@@ -4592,10 +4752,10 @@
     </row>
     <row r="23" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A23" s="24" t="s">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="B23" s="22" t="s">
-        <v>171</v>
+        <v>191</v>
       </c>
       <c r="C23" s="25" t="s">
         <v>46</v>
@@ -4604,27 +4764,27 @@
         <v>47</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="F23" s="23" t="s">
-        <v>173</v>
+        <v>193</v>
       </c>
       <c r="G23" s="23" t="s">
-        <v>174</v>
+        <v>194</v>
       </c>
       <c r="H23" s="23" t="s">
-        <v>175</v>
+        <v>195</v>
       </c>
       <c r="I23" s="23" t="s">
         <v>52</v>
       </c>
       <c r="J23" s="26" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A24" s="21" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
@@ -4638,10 +4798,10 @@
     </row>
     <row r="25" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A25" s="24" t="s">
-        <v>177</v>
+        <v>197</v>
       </c>
       <c r="B25" s="22" t="s">
-        <v>178</v>
+        <v>198</v>
       </c>
       <c r="C25" s="25" t="s">
         <v>46</v>
@@ -4650,27 +4810,27 @@
         <v>47</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>179</v>
+        <v>199</v>
       </c>
       <c r="F25" s="23" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="G25" s="23" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="H25" s="23" t="s">
-        <v>182</v>
+        <v>202</v>
       </c>
       <c r="I25" s="23" t="s">
         <v>52</v>
       </c>
       <c r="J25" s="26" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="18" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="16"/>
@@ -4684,7 +4844,7 @@
     </row>
     <row r="27" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
-        <v>292</v>
+        <v>312</v>
       </c>
       <c r="B27" s="19"/>
       <c r="C27" s="19"/>
@@ -4698,31 +4858,31 @@
     </row>
     <row r="28" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A28" s="24" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="B28" s="22" t="s">
-        <v>276</v>
+        <v>296</v>
       </c>
       <c r="C28" s="25" t="s">
         <v>83</v>
       </c>
       <c r="D28" s="22" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="E28" s="23" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>278</v>
+        <v>298</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>279</v>
+        <v>299</v>
       </c>
       <c r="H28" s="23" t="s">
         <v>88</v>
       </c>
       <c r="I28" s="23" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="J28" s="26" t="s">
         <v>79</v>
@@ -4730,7 +4890,7 @@
     </row>
     <row r="29" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A29" s="21" t="s">
-        <v>291</v>
+        <v>311</v>
       </c>
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
@@ -4744,10 +4904,10 @@
     </row>
     <row r="30" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A30" s="24" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
       <c r="B30" s="22" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="C30" s="25" t="s">
         <v>83</v>
@@ -4756,13 +4916,13 @@
         <v>84</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="F30" s="23" t="s">
-        <v>257</v>
+        <v>277</v>
       </c>
       <c r="G30" s="23" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="H30" s="23" t="s">
         <v>88</v>
@@ -4776,7 +4936,7 @@
     </row>
     <row r="31" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A31" s="21" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="B31" s="19"/>
       <c r="C31" s="19"/>
@@ -4822,7 +4982,7 @@
     </row>
     <row r="33" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="18" t="s">
-        <v>299</v>
+        <v>319</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -4836,7 +4996,7 @@
     </row>
     <row r="34" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A34" s="21" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="B34" s="19"/>
       <c r="C34" s="19"/>
@@ -4850,10 +5010,10 @@
     </row>
     <row r="35" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A35" s="24" t="s">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="B35" s="22" t="s">
-        <v>261</v>
+        <v>281</v>
       </c>
       <c r="C35" s="25" t="s">
         <v>72</v>
@@ -4862,16 +5022,16 @@
         <v>73</v>
       </c>
       <c r="E35" s="23" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="F35" s="23" t="s">
-        <v>263</v>
+        <v>283</v>
       </c>
       <c r="G35" s="23" t="s">
-        <v>264</v>
+        <v>284</v>
       </c>
       <c r="H35" s="23" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="I35" s="23" t="s">
         <v>78</v>
@@ -4882,7 +5042,7 @@
     </row>
     <row r="36" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A36" s="21" t="s">
-        <v>293</v>
+        <v>313</v>
       </c>
       <c r="B36" s="19"/>
       <c r="C36" s="19"/>
@@ -4896,10 +5056,10 @@
     </row>
     <row r="37" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A37" s="24" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="B37" s="22" t="s">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="C37" s="25" t="s">
         <v>72</v>
@@ -4908,16 +5068,16 @@
         <v>73</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="F37" s="23" t="s">
-        <v>192</v>
+        <v>212</v>
       </c>
       <c r="G37" s="23" t="s">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="H37" s="23" t="s">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="I37" s="23" t="s">
         <v>78</v>
@@ -4928,7 +5088,7 @@
     </row>
     <row r="38" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A38" s="21" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="B38" s="19"/>
       <c r="C38" s="19"/>
@@ -4942,10 +5102,10 @@
     </row>
     <row r="39" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A39" s="24" t="s">
-        <v>212</v>
+        <v>232</v>
       </c>
       <c r="B39" s="22" t="s">
-        <v>213</v>
+        <v>233</v>
       </c>
       <c r="C39" s="25" t="s">
         <v>72</v>
@@ -4954,16 +5114,16 @@
         <v>73</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>214</v>
+        <v>234</v>
       </c>
       <c r="F39" s="23" t="s">
-        <v>215</v>
+        <v>235</v>
       </c>
       <c r="G39" s="23" t="s">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="H39" s="23" t="s">
-        <v>217</v>
+        <v>237</v>
       </c>
       <c r="I39" s="23" t="s">
         <v>78</v>
@@ -4974,7 +5134,7 @@
     </row>
     <row r="40" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A40" s="21" t="s">
-        <v>301</v>
+        <v>321</v>
       </c>
       <c r="B40" s="19"/>
       <c r="C40" s="19"/>
@@ -4988,10 +5148,10 @@
     </row>
     <row r="41" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A41" s="24" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="B41" s="22" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="C41" s="25" t="s">
         <v>72</v>
@@ -5000,16 +5160,16 @@
         <v>73</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="F41" s="23" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="G41" s="23" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="H41" s="23" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="I41" s="23" t="s">
         <v>78</v>
@@ -5020,7 +5180,7 @@
     </row>
     <row r="42" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A42" s="21" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
       <c r="B42" s="19"/>
       <c r="C42" s="19"/>
@@ -5066,7 +5226,7 @@
     </row>
     <row r="44" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A44" s="21" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="B44" s="19"/>
       <c r="C44" s="19"/>
@@ -5080,10 +5240,10 @@
     </row>
     <row r="45" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A45" s="24" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
       <c r="B45" s="22" t="s">
-        <v>116</v>
+        <v>146</v>
       </c>
       <c r="C45" s="25" t="s">
         <v>72</v>
@@ -5092,16 +5252,16 @@
         <v>73</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>118</v>
+        <v>148</v>
       </c>
       <c r="G45" s="23" t="s">
-        <v>119</v>
+        <v>149</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="I45" s="23" t="s">
         <v>78</v>
@@ -5112,7 +5272,7 @@
     </row>
     <row r="46" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A46" s="21" t="s">
-        <v>303</v>
+        <v>323</v>
       </c>
       <c r="B46" s="19"/>
       <c r="C46" s="19"/>
@@ -5126,10 +5286,10 @@
     </row>
     <row r="47" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A47" s="24" t="s">
-        <v>225</v>
+        <v>245</v>
       </c>
       <c r="B47" s="22" t="s">
-        <v>226</v>
+        <v>246</v>
       </c>
       <c r="C47" s="25" t="s">
         <v>72</v>
@@ -5138,16 +5298,16 @@
         <v>73</v>
       </c>
       <c r="E47" s="23" t="s">
-        <v>227</v>
+        <v>247</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="I47" s="23" t="s">
         <v>78</v>
@@ -5158,7 +5318,7 @@
     </row>
     <row r="48" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="18" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
@@ -5172,7 +5332,7 @@
     </row>
     <row r="49" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A49" s="21" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="B49" s="19"/>
       <c r="C49" s="19"/>
@@ -5186,31 +5346,31 @@
     </row>
     <row r="50" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A50" s="24" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="B50" s="22" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="C50" s="25" t="s">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="F50" s="23" t="s">
-        <v>127</v>
+        <v>141</v>
       </c>
       <c r="G50" s="23" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="I50" s="23" t="s">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="J50" s="26" t="s">
         <v>79</v>
@@ -5218,7 +5378,7 @@
     </row>
     <row r="51" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="18" t="s">
-        <v>305</v>
+        <v>325</v>
       </c>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -5232,7 +5392,7 @@
     </row>
     <row r="52" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A52" s="21" t="s">
-        <v>302</v>
+        <v>322</v>
       </c>
       <c r="B52" s="19"/>
       <c r="C52" s="19"/>
@@ -5246,31 +5406,31 @@
     </row>
     <row r="53" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A53" s="24" t="s">
-        <v>106</v>
+        <v>126</v>
       </c>
       <c r="B53" s="22" t="s">
-        <v>107</v>
+        <v>127</v>
       </c>
       <c r="C53" s="25" t="s">
-        <v>108</v>
+        <v>128</v>
       </c>
       <c r="D53" s="22" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="E53" s="23" t="s">
-        <v>110</v>
+        <v>130</v>
       </c>
       <c r="F53" s="23" t="s">
-        <v>111</v>
+        <v>131</v>
       </c>
       <c r="G53" s="23" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="H53" s="23" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="I53" s="23" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="J53" s="26" t="s">
         <v>79</v>
@@ -5278,7 +5438,7 @@
     </row>
     <row r="54" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="18" t="s">
-        <v>306</v>
+        <v>326</v>
       </c>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
@@ -5292,7 +5452,7 @@
     </row>
     <row r="55" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A55" s="21" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
@@ -5306,31 +5466,31 @@
     </row>
     <row r="56" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A56" s="24" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="B56" s="22" t="s">
-        <v>142</v>
+        <v>162</v>
       </c>
       <c r="C56" s="25" t="s">
-        <v>143</v>
+        <v>163</v>
       </c>
       <c r="D56" s="22" t="s">
-        <v>144</v>
+        <v>164</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="F56" s="23" t="s">
-        <v>146</v>
+        <v>166</v>
       </c>
       <c r="G56" s="23" t="s">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>148</v>
+        <v>168</v>
       </c>
       <c r="I56" s="23" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="J56" s="26" t="s">
         <v>79</v>
@@ -5338,7 +5498,7 @@
     </row>
     <row r="57" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="18" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="B57" s="16"/>
       <c r="C57" s="16"/>
@@ -5352,7 +5512,7 @@
     </row>
     <row r="58" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A58" s="21" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="B58" s="19"/>
       <c r="C58" s="19"/>
@@ -5366,31 +5526,31 @@
     </row>
     <row r="59" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A59" s="24" t="s">
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="B59" s="22" t="s">
-        <v>163</v>
+        <v>183</v>
       </c>
       <c r="C59" s="25" t="s">
-        <v>164</v>
+        <v>184</v>
       </c>
       <c r="D59" s="22" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="E59" s="23" t="s">
-        <v>166</v>
+        <v>186</v>
       </c>
       <c r="F59" s="23" t="s">
-        <v>167</v>
+        <v>187</v>
       </c>
       <c r="G59" s="23" t="s">
-        <v>168</v>
+        <v>188</v>
       </c>
       <c r="H59" s="23" t="s">
         <v>88</v>
       </c>
       <c r="I59" s="23" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="J59" s="26" t="s">
         <v>79</v>
@@ -5398,7 +5558,7 @@
     </row>
     <row r="60" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A60" s="21" t="s">
-        <v>296</v>
+        <v>316</v>
       </c>
       <c r="B60" s="19"/>
       <c r="C60" s="19"/>
@@ -5412,31 +5572,31 @@
     </row>
     <row r="61" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A61" s="24" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="B61" s="22" t="s">
+        <v>204</v>
+      </c>
+      <c r="C61" s="25" t="s">
         <v>184</v>
       </c>
-      <c r="C61" s="25" t="s">
-        <v>164</v>
-      </c>
       <c r="D61" s="22" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="E61" s="23" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
       <c r="F61" s="23" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="G61" s="23" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="H61" s="23" t="s">
         <v>88</v>
       </c>
       <c r="I61" s="23" t="s">
-        <v>169</v>
+        <v>189</v>
       </c>
       <c r="J61" s="26" t="s">
         <v>79</v>
@@ -5444,7 +5604,7 @@
     </row>
     <row r="62" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="18" t="s">
-        <v>308</v>
+        <v>328</v>
       </c>
       <c r="B62" s="16"/>
       <c r="C62" s="16"/>
@@ -5458,7 +5618,7 @@
     </row>
     <row r="63" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A63" s="21" t="s">
-        <v>309</v>
+        <v>329</v>
       </c>
       <c r="B63" s="19"/>
       <c r="C63" s="19"/>
@@ -5472,28 +5632,28 @@
     </row>
     <row r="64" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A64" s="24" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="B64" s="22" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="C64" s="25" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="D64" s="22" t="s">
         <v>73</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="F64" s="23" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="G64" s="23" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
       <c r="H64" s="23" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
       <c r="I64" s="23" t="s">
         <v>78</v>
@@ -5504,7 +5664,7 @@
     </row>
     <row r="65" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="18" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="B65" s="16"/>
       <c r="C65" s="16"/>
@@ -5518,7 +5678,7 @@
     </row>
     <row r="66" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A66" s="21" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="B66" s="19"/>
       <c r="C66" s="19"/>
@@ -5532,31 +5692,31 @@
     </row>
     <row r="67" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A67" s="24" t="s">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="B67" s="22" t="s">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="C67" s="25" t="s">
-        <v>154</v>
+        <v>174</v>
       </c>
       <c r="D67" s="22" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="E67" s="23" t="s">
-        <v>156</v>
+        <v>176</v>
       </c>
       <c r="F67" s="23" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="G67" s="23" t="s">
-        <v>158</v>
+        <v>178</v>
       </c>
       <c r="H67" s="23" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="I67" s="23" t="s">
-        <v>160</v>
+        <v>180</v>
       </c>
       <c r="J67" s="26" t="s">
         <v>79</v>
@@ -5564,7 +5724,7 @@
     </row>
     <row r="68" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="18" t="s">
-        <v>311</v>
+        <v>331</v>
       </c>
       <c r="B68" s="16"/>
       <c r="C68" s="16"/>
@@ -5578,7 +5738,7 @@
     </row>
     <row r="69" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A69" s="21" t="s">
-        <v>300</v>
+        <v>320</v>
       </c>
       <c r="B69" s="19"/>
       <c r="C69" s="19"/>
@@ -5592,39 +5752,39 @@
     </row>
     <row r="70" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A70" s="24" t="s">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="B70" s="22" t="s">
-        <v>268</v>
+        <v>288</v>
       </c>
       <c r="C70" s="25" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="D70" s="22" t="s">
         <v>47</v>
       </c>
       <c r="E70" s="23" t="s">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="F70" s="23" t="s">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="G70" s="23" t="s">
-        <v>272</v>
+        <v>292</v>
       </c>
       <c r="H70" s="23" t="s">
-        <v>273</v>
+        <v>293</v>
       </c>
       <c r="I70" s="23" t="s">
         <v>52</v>
       </c>
       <c r="J70" s="26" t="s">
-        <v>139</v>
+        <v>159</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="18" t="s">
-        <v>312</v>
+        <v>332</v>
       </c>
       <c r="B71" s="16"/>
       <c r="C71" s="16"/>
@@ -5638,7 +5798,7 @@
     </row>
     <row r="72" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
       <c r="A72" s="21" t="s">
-        <v>290</v>
+        <v>310</v>
       </c>
       <c r="B72" s="19"/>
       <c r="C72" s="19"/>
@@ -5652,43 +5812,167 @@
     </row>
     <row r="73" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
       <c r="A73" s="24" t="s">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="B73" s="22" t="s">
-        <v>204</v>
+        <v>224</v>
       </c>
       <c r="C73" s="25" t="s">
-        <v>205</v>
+        <v>225</v>
       </c>
       <c r="D73" s="22" t="s">
-        <v>206</v>
+        <v>226</v>
       </c>
       <c r="E73" s="23" t="s">
-        <v>207</v>
+        <v>227</v>
       </c>
       <c r="F73" s="23" t="s">
-        <v>208</v>
+        <v>228</v>
       </c>
       <c r="G73" s="23" t="s">
-        <v>209</v>
+        <v>229</v>
       </c>
       <c r="H73" s="23" t="s">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="I73" s="23" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="J73" s="26" t="s">
         <v>79</v>
       </c>
     </row>
+    <row r="74" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="18" t="s">
+        <v>333</v>
+      </c>
+      <c r="B74" s="16"/>
+      <c r="C74" s="16"/>
+      <c r="D74" s="16"/>
+      <c r="E74" s="17"/>
+      <c r="F74" s="17"/>
+      <c r="G74" s="17"/>
+      <c r="H74" s="17"/>
+      <c r="I74" s="17"/>
+      <c r="J74" s="17"/>
+    </row>
+    <row r="75" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="B75" s="19"/>
+      <c r="C75" s="19"/>
+      <c r="D75" s="19"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="20"/>
+      <c r="G75" s="20"/>
+      <c r="H75" s="20"/>
+      <c r="I75" s="20"/>
+      <c r="J75" s="20"/>
+    </row>
+    <row r="76" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A76" s="24" t="s">
+        <v>106</v>
+      </c>
+      <c r="B76" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="C76" s="25" t="s">
+        <v>108</v>
+      </c>
+      <c r="D76" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="E76" s="23" t="s">
+        <v>110</v>
+      </c>
+      <c r="F76" s="23" t="s">
+        <v>111</v>
+      </c>
+      <c r="G76" s="23" t="s">
+        <v>112</v>
+      </c>
+      <c r="H76" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="I76" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="J76" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" spans="1:10" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="B77" s="16"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="16"/>
+      <c r="E77" s="17"/>
+      <c r="F77" s="17"/>
+      <c r="G77" s="17"/>
+      <c r="H77" s="17"/>
+      <c r="I77" s="17"/>
+      <c r="J77" s="17"/>
+    </row>
+    <row r="78" spans="1:10" ht="40.049999999999997" customHeight="1" outlineLevel="1" collapsed="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="B78" s="19"/>
+      <c r="C78" s="19"/>
+      <c r="D78" s="19"/>
+      <c r="E78" s="20"/>
+      <c r="F78" s="20"/>
+      <c r="G78" s="20"/>
+      <c r="H78" s="20"/>
+      <c r="I78" s="20"/>
+      <c r="J78" s="20"/>
+    </row>
+    <row r="79" spans="1:10" ht="40.049999999999997" hidden="1" customHeight="1" outlineLevel="2" x14ac:dyDescent="0.3">
+      <c r="A79" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="B79" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="C79" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="D79" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="E79" s="23" t="s">
+        <v>120</v>
+      </c>
+      <c r="F79" s="23" t="s">
+        <v>121</v>
+      </c>
+      <c r="G79" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="H79" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="I79" s="23" t="s">
+        <v>124</v>
+      </c>
+      <c r="J79" s="26" t="s">
+        <v>79</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:J3" xr:uid="{3BC65ED9-AB40-4CEB-B626-6A6F40CB9629}"/>
-  <mergeCells count="40">
+  <autoFilter ref="A3:J3" xr:uid="{5BC87A21-33BD-4679-99E2-8BD7169C6A34}"/>
+  <mergeCells count="44">
+    <mergeCell ref="A77:J77"/>
+    <mergeCell ref="A78:J78"/>
     <mergeCell ref="A68:J68"/>
     <mergeCell ref="A69:J69"/>
     <mergeCell ref="A71:J71"/>
     <mergeCell ref="A72:J72"/>
+    <mergeCell ref="A74:J74"/>
+    <mergeCell ref="A75:J75"/>
     <mergeCell ref="A58:J58"/>
     <mergeCell ref="A60:J60"/>
     <mergeCell ref="A62:J62"/>
@@ -5736,7 +6020,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F9054266-593B-4E2E-B32B-BF49DDF1DCAB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C905C3-0765-4BAE-A530-E9FF0A9CFE10}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -5752,7 +6036,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
-        <v>313</v>
+        <v>335</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -5763,7 +6047,7 @@
     </row>
     <row r="2" spans="1:7" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="35" t="s">
-        <v>314</v>
+        <v>336</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5783,259 +6067,259 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="15" t="s">
-        <v>315</v>
+        <v>337</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>316</v>
+        <v>338</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>317</v>
+        <v>339</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>318</v>
+        <v>340</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>319</v>
+        <v>341</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>320</v>
+        <v>342</v>
       </c>
       <c r="G4" s="15" t="s">
-        <v>321</v>
+        <v>343</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="36" t="s">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>323</v>
+        <v>345</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>324</v>
+        <v>346</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>326</v>
+        <v>348</v>
       </c>
       <c r="F5" s="22" t="s">
-        <v>327</v>
+        <v>349</v>
       </c>
       <c r="G5" s="22" t="s">
-        <v>328</v>
+        <v>350</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="37" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="36" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="B7" s="22" t="s">
-        <v>337</v>
+        <v>359</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="F7" s="22" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="G7" s="22" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="37" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>348</v>
+        <v>370</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="36" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="B9" s="22" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>353</v>
+        <v>375</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>354</v>
+        <v>376</v>
       </c>
       <c r="F9" s="22" t="s">
-        <v>355</v>
+        <v>377</v>
       </c>
       <c r="G9" s="22" t="s">
-        <v>356</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="37" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>358</v>
+        <v>380</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>359</v>
+        <v>381</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>360</v>
+        <v>382</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>361</v>
+        <v>383</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>363</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="36" t="s">
-        <v>364</v>
+        <v>386</v>
       </c>
       <c r="B11" s="22" t="s">
-        <v>365</v>
+        <v>387</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>366</v>
+        <v>388</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>367</v>
+        <v>389</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>368</v>
+        <v>390</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>369</v>
+        <v>391</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>370</v>
+        <v>392</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="37" t="s">
-        <v>371</v>
+        <v>393</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>372</v>
+        <v>394</v>
       </c>
       <c r="C12" s="27" t="s">
-        <v>373</v>
+        <v>395</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>374</v>
+        <v>396</v>
       </c>
       <c r="E12" s="27" t="s">
-        <v>375</v>
+        <v>397</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>376</v>
+        <v>398</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>377</v>
+        <v>399</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="36" t="s">
-        <v>378</v>
+        <v>400</v>
       </c>
       <c r="B13" s="22" t="s">
-        <v>379</v>
+        <v>401</v>
       </c>
       <c r="C13" s="22" t="s">
-        <v>380</v>
+        <v>402</v>
       </c>
       <c r="D13" s="22" t="s">
-        <v>381</v>
+        <v>403</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>382</v>
+        <v>404</v>
       </c>
       <c r="F13" s="22" t="s">
-        <v>383</v>
+        <v>405</v>
       </c>
       <c r="G13" s="22" t="s">
-        <v>384</v>
+        <v>406</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="37" t="s">
-        <v>385</v>
+        <v>407</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>386</v>
+        <v>408</v>
       </c>
       <c r="C14" s="27" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="E14" s="27" t="s">
-        <v>387</v>
+        <v>409</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>388</v>
+        <v>410</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>389</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G4" xr:uid="{F9054266-593B-4E2E-B32B-BF49DDF1DCAB}"/>
+  <autoFilter ref="A4:G4" xr:uid="{31C905C3-0765-4BAE-A530-E9FF0A9CFE10}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
@@ -6050,7 +6334,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF21DF10-3E91-4AA7-9EF9-574E98687091}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8959E6DB-B7C6-44D9-BAA3-F78703DCC6B0}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6064,7 +6348,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
-        <v>390</v>
+        <v>412</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -6076,120 +6360,120 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>391</v>
+        <v>413</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>392</v>
+        <v>414</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>393</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="36" t="s">
-        <v>394</v>
+        <v>416</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>396</v>
+        <v>418</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="37" t="s">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>398</v>
+        <v>420</v>
       </c>
       <c r="C5" s="28" t="s">
-        <v>399</v>
+        <v>421</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="36" t="s">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>401</v>
+        <v>423</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>402</v>
+        <v>424</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="37" t="s">
-        <v>403</v>
+        <v>425</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>404</v>
+        <v>426</v>
       </c>
       <c r="C7" s="28" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="36" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>407</v>
+        <v>429</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>408</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="37" t="s">
-        <v>409</v>
+        <v>431</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>410</v>
+        <v>432</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="36" t="s">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="37" t="s">
-        <v>415</v>
+        <v>437</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>416</v>
+        <v>438</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>417</v>
+        <v>439</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="36" t="s">
-        <v>418</v>
+        <v>440</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>419</v>
+        <v>441</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>420</v>
+        <v>442</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="37" t="s">
-        <v>421</v>
+        <v>443</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>422</v>
+        <v>444</v>
       </c>
       <c r="C13" s="28" t="s">
         <v>24</v>
@@ -6197,10 +6481,10 @@
     </row>
     <row r="14" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="36" t="s">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>424</v>
+        <v>446</v>
       </c>
       <c r="C14" s="23" t="s">
         <v>21</v>
@@ -6220,7 +6504,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E378176A-A299-40DE-BA06-ECD1DFCFE810}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{063B856D-FD6C-46FC-A0CA-5BA267856166}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6233,7 +6517,7 @@
   <sheetData>
     <row r="1" spans="1:3" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A1" s="34" t="s">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
@@ -6245,32 +6529,32 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
-        <v>426</v>
+        <v>448</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>427</v>
+        <v>449</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>428</v>
+        <v>450</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="23" t="s">
-        <v>429</v>
+        <v>451</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>430</v>
+        <v>452</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>431</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="28" t="s">
-        <v>432</v>
+        <v>454</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>433</v>
+        <v>455</v>
       </c>
       <c r="C5" s="28" t="s">
         <v>24</v>
@@ -6278,10 +6562,10 @@
     </row>
     <row r="6" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23" t="s">
-        <v>434</v>
+        <v>456</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>435</v>
+        <v>457</v>
       </c>
       <c r="C6" s="23" t="s">
         <v>18</v>
@@ -6289,10 +6573,10 @@
     </row>
     <row r="7" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="28" t="s">
-        <v>436</v>
+        <v>458</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>437</v>
+        <v>459</v>
       </c>
       <c r="C7" s="28" t="s">
         <v>21</v>
@@ -6300,46 +6584,46 @@
     </row>
     <row r="8" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="23" t="s">
-        <v>438</v>
+        <v>460</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>411</v>
+        <v>433</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="28" t="s">
-        <v>440</v>
+        <v>462</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>441</v>
+        <v>463</v>
       </c>
       <c r="C9" s="28" t="s">
-        <v>442</v>
+        <v>464</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="23" t="s">
-        <v>443</v>
+        <v>465</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>444</v>
+        <v>466</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>445</v>
+        <v>467</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="28" t="s">
-        <v>446</v>
+        <v>468</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>447</v>
+        <v>469</v>
       </c>
       <c r="C11" s="28" t="s">
-        <v>448</v>
+        <v>470</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -6349,7 +6633,7 @@
     </row>
     <row r="13" spans="1:3" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="35" t="s">
-        <v>449</v>
+        <v>471</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>

--- a/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
+++ b/docs/DOSSIER_EXPLOITATION_QUOTIDIEN.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP PROBOOK\Documents\ECF\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{55A0B0EC-1611-434F-BF11-AC921E0F3A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3768F71B-70F7-4774-9977-CF391CACC44E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5604" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{F5A6BB3A-89A6-4021-B029-5C8BC4A1C3B8}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="8880" xr2:uid="{419C3045-35AF-4F04-A9CB-D6E2301278CA}"/>
   </bookViews>
   <sheets>
     <sheet name="Mode d'emploi" sheetId="1" r:id="rId1"/>
@@ -1666,7 +1666,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF9669EB"/>
+        <fgColor rgb="FFD35400"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2063,7 +2063,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0BF25B-CC6D-4354-8C36-4A1631E81F68}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32E09FAD-AEFF-46A6-9E0A-A10B5D150AFE}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2318,7 +2318,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{445F5AAB-F7E3-4E1A-B00F-F65CE4CD40E4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6624E96-2FB4-4E48-845A-6860D0FB2F3A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -2432,7 +2432,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79BEE6B-D6FC-435E-AC94-A0B33E844ABC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD676AB5-3BD1-4B39-9235-68C643B6E648}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -4169,7 +4169,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J3" xr:uid="{C79BEE6B-D6FC-435E-AC94-A0B33E844ABC}"/>
+  <autoFilter ref="A3:J3" xr:uid="{BD676AB5-3BD1-4B39-9235-68C643B6E648}"/>
   <mergeCells count="44">
     <mergeCell ref="A76:J76"/>
     <mergeCell ref="A78:J78"/>
@@ -4226,7 +4226,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BC87A21-33BD-4679-99E2-8BD7169C6A34}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F3EA0A5-0216-4FD8-A081-439BA5DD2F0A}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
     <pageSetUpPr fitToPage="1"/>
@@ -5963,7 +5963,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:J3" xr:uid="{5BC87A21-33BD-4679-99E2-8BD7169C6A34}"/>
+  <autoFilter ref="A3:J3" xr:uid="{2F3EA0A5-0216-4FD8-A081-439BA5DD2F0A}"/>
   <mergeCells count="44">
     <mergeCell ref="A77:J77"/>
     <mergeCell ref="A78:J78"/>
@@ -6020,7 +6020,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31C905C3-0765-4BAE-A530-E9FF0A9CFE10}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46BF38C8-876A-4552-8523-55F5659BFB65}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6319,7 +6319,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:G4" xr:uid="{31C905C3-0765-4BAE-A530-E9FF0A9CFE10}"/>
+  <autoFilter ref="A4:G4" xr:uid="{46BF38C8-876A-4552-8523-55F5659BFB65}"/>
   <mergeCells count="2">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
@@ -6334,7 +6334,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8959E6DB-B7C6-44D9-BAA3-F78703DCC6B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87F88ED2-2D74-4345-A588-4083D685D007}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6504,7 +6504,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{063B856D-FD6C-46FC-A0CA-5BA267856166}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51AFEDCC-C966-48B3-AEAC-B51127CB52F3}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
